--- a/daily/2026-04-12.xlsx
+++ b/daily/2026-04-12.xlsx
@@ -558,7 +558,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Jalen Johnson</t>
+          <t>Bam Adebayo</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -568,79 +568,79 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Forward</t>
+          <t>Center</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>22.5</v>
+        <v>21.5</v>
       </c>
       <c r="E2" t="n">
         <v>17</v>
       </c>
       <c r="F2" t="n">
-        <v>17.4</v>
+        <v>18.8</v>
       </c>
       <c r="G2" t="n">
-        <v>20.3</v>
+        <v>18.1</v>
       </c>
       <c r="H2" t="n">
-        <v>20.4</v>
+        <v>24.1</v>
       </c>
       <c r="I2" t="n">
-        <v>21.6</v>
+        <v>22.7</v>
       </c>
       <c r="J2" t="n">
-        <v>34.4</v>
+        <v>34.2</v>
       </c>
       <c r="K2" t="n">
-        <v>34.6</v>
+        <v>33.9</v>
       </c>
       <c r="L2" t="n">
-        <v>46.3</v>
+        <v>39.3</v>
       </c>
       <c r="M2" t="n">
-        <v>46</v>
+        <v>43.9</v>
       </c>
       <c r="N2" t="n">
-        <v>5.6</v>
+        <v>6.2</v>
       </c>
       <c r="O2" t="n">
         <v>30</v>
       </c>
       <c r="P2" t="n">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="Q2" t="n">
-        <v>-0.9</v>
+        <v>1.2</v>
       </c>
       <c r="R2" t="n">
-        <v>-4.2</v>
+        <v>-3.9</v>
       </c>
       <c r="S2" t="n">
+        <v>-4.6</v>
+      </c>
+      <c r="T2" t="n">
         <v>0.3</v>
       </c>
-      <c r="T2" t="n">
-        <v>-0.2</v>
-      </c>
       <c r="U2" t="n">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="V2" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>24.2 (4g)</t>
+          <t>16.0 (6g)</t>
         </is>
       </c>
       <c r="X2" t="n">
-        <v>0.3</v>
+        <v>-1.5</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Nickeil Alexander-Walker</t>
+          <t>Jalen Johnson</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -650,73 +650,73 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Guard</t>
+          <t>Forward</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>24.5</v>
+        <v>22.5</v>
       </c>
       <c r="E3" t="n">
-        <v>26.3</v>
+        <v>17</v>
       </c>
       <c r="F3" t="n">
-        <v>26.4</v>
+        <v>17.4</v>
       </c>
       <c r="G3" t="n">
-        <v>24.3</v>
+        <v>20.3</v>
       </c>
       <c r="H3" t="n">
-        <v>23.6</v>
+        <v>20.4</v>
       </c>
       <c r="I3" t="n">
         <v>21.6</v>
       </c>
       <c r="J3" t="n">
-        <v>35.4</v>
+        <v>34.4</v>
       </c>
       <c r="K3" t="n">
-        <v>34</v>
+        <v>34.6</v>
       </c>
       <c r="L3" t="n">
-        <v>54.5</v>
+        <v>46.3</v>
       </c>
       <c r="M3" t="n">
-        <v>48.6</v>
+        <v>46</v>
       </c>
       <c r="N3" t="n">
-        <v>6.1</v>
+        <v>5.6</v>
       </c>
       <c r="O3" t="n">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="P3" t="n">
+        <v>43</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>-0.9</v>
+      </c>
+      <c r="R3" t="n">
+        <v>-4.2</v>
+      </c>
+      <c r="S3" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="T3" t="n">
+        <v>-0.2</v>
+      </c>
+      <c r="U3" t="n">
         <v>23</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>-2.9</v>
-      </c>
-      <c r="R3" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="S3" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="T3" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="U3" t="n">
-        <v>22</v>
       </c>
       <c r="V3" t="n">
         <v>4</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>15.6 (5g)</t>
+          <t>24.2 (4g)</t>
         </is>
       </c>
       <c r="X3" t="n">
-        <v>-3.9</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="4">
@@ -886,7 +886,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Bam Adebayo</t>
+          <t>Nickeil Alexander-Walker</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -896,79 +896,79 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Center</t>
+          <t>Guard</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>23.5</v>
+        <v>22.5</v>
       </c>
       <c r="E6" t="n">
-        <v>17</v>
+        <v>26.3</v>
       </c>
       <c r="F6" t="n">
-        <v>18.8</v>
+        <v>26.4</v>
       </c>
       <c r="G6" t="n">
-        <v>18.1</v>
+        <v>24.3</v>
       </c>
       <c r="H6" t="n">
-        <v>24.1</v>
+        <v>23.6</v>
       </c>
       <c r="I6" t="n">
-        <v>22.7</v>
+        <v>21.6</v>
       </c>
       <c r="J6" t="n">
-        <v>34.2</v>
+        <v>35.4</v>
       </c>
       <c r="K6" t="n">
-        <v>33.9</v>
+        <v>34</v>
       </c>
       <c r="L6" t="n">
-        <v>39.3</v>
+        <v>54.5</v>
       </c>
       <c r="M6" t="n">
-        <v>43.9</v>
+        <v>48.6</v>
       </c>
       <c r="N6" t="n">
-        <v>6.2</v>
+        <v>6.1</v>
       </c>
       <c r="O6" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="P6" t="n">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="Q6" t="n">
-        <v>-0.8</v>
+        <v>-0.9</v>
       </c>
       <c r="R6" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="S6" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="T6" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="U6" t="n">
+        <v>22</v>
+      </c>
+      <c r="V6" t="n">
+        <v>4</v>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>15.6 (5g)</t>
+        </is>
+      </c>
+      <c r="X6" t="n">
         <v>-3.9</v>
-      </c>
-      <c r="S6" t="n">
-        <v>-4.6</v>
-      </c>
-      <c r="T6" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="U6" t="n">
-        <v>17</v>
-      </c>
-      <c r="V6" t="n">
-        <v>8</v>
-      </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>16.0 (6g)</t>
-        </is>
-      </c>
-      <c r="X6" t="n">
-        <v>-1.5</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Andrew Wiggins</t>
+          <t>Dyson Daniels</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -978,84 +978,84 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Forward</t>
+          <t>Guard</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>18.5</v>
+        <v>12.5</v>
       </c>
       <c r="E7" t="n">
-        <v>13.3</v>
+        <v>12</v>
       </c>
       <c r="F7" t="n">
-        <v>14.8</v>
+        <v>12.4</v>
       </c>
       <c r="G7" t="n">
-        <v>13.6</v>
+        <v>14.2</v>
       </c>
       <c r="H7" t="n">
-        <v>15.3</v>
+        <v>13.1</v>
       </c>
       <c r="I7" t="n">
-        <v>15.2</v>
+        <v>12</v>
       </c>
       <c r="J7" t="n">
-        <v>27.2</v>
+        <v>33</v>
       </c>
       <c r="K7" t="n">
-        <v>28.8</v>
+        <v>31.6</v>
       </c>
       <c r="L7" t="n">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="M7" t="n">
-        <v>50.2</v>
+        <v>52.3</v>
       </c>
       <c r="N7" t="n">
-        <v>5.5</v>
+        <v>5.8</v>
       </c>
       <c r="O7" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="P7" t="n">
-        <v>20</v>
+        <v>47</v>
       </c>
       <c r="Q7" t="n">
-        <v>-3.3</v>
+        <v>-0.5</v>
       </c>
       <c r="R7" t="n">
-        <v>-0.4</v>
+        <v>0.4</v>
       </c>
       <c r="S7" t="n">
-        <v>1.8</v>
+        <v>2.7</v>
       </c>
       <c r="T7" t="n">
-        <v>-1.5</v>
+        <v>1.4</v>
       </c>
       <c r="U7" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="V7" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>18.7 (6g)</t>
+          <t>8.5 (6g)</t>
         </is>
       </c>
       <c r="X7" t="n">
-        <v>3.1</v>
+        <v>-3.6</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Paolo Banchero</t>
+          <t>Onyeka Okongwu</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>ORL @ BOS</t>
+          <t>ATL @ MIA</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1064,157 +1064,157 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>20.5</v>
+        <v>15.5</v>
       </c>
       <c r="E8" t="n">
-        <v>21.7</v>
+        <v>10.7</v>
       </c>
       <c r="F8" t="n">
-        <v>19.6</v>
+        <v>12.6</v>
       </c>
       <c r="G8" t="n">
-        <v>20.3</v>
+        <v>12.4</v>
       </c>
       <c r="H8" t="n">
-        <v>22.8</v>
+        <v>12.9</v>
       </c>
       <c r="I8" t="n">
-        <v>22.9</v>
+        <v>13.8</v>
       </c>
       <c r="J8" t="n">
-        <v>33.4</v>
+        <v>29.8</v>
       </c>
       <c r="K8" t="n">
-        <v>35.1</v>
+        <v>29.7</v>
       </c>
       <c r="L8" t="n">
-        <v>46.8</v>
+        <v>47.6</v>
       </c>
       <c r="M8" t="n">
-        <v>45.5</v>
+        <v>47.7</v>
       </c>
       <c r="N8" t="n">
-        <v>9.6</v>
+        <v>5.7</v>
       </c>
       <c r="O8" t="n">
         <v>40</v>
       </c>
       <c r="P8" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.4</v>
+        <v>-1.7</v>
       </c>
       <c r="R8" t="n">
-        <v>-3.3</v>
+        <v>-1.2</v>
       </c>
       <c r="S8" t="n">
-        <v>1.3</v>
+        <v>-0.1</v>
       </c>
       <c r="T8" t="n">
-        <v>-1.7</v>
+        <v>0.1</v>
       </c>
       <c r="U8" t="n">
-        <v>2</v>
+        <v>23</v>
       </c>
       <c r="V8" t="n">
-        <v>24</v>
+        <v>4</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>19.8 (4g)</t>
+          <t>15.8 (5g)</t>
         </is>
       </c>
       <c r="X8" t="n">
-        <v>-2.9</v>
+        <v>-3.5</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Desmond Bane</t>
+          <t>Andrew Wiggins</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>ORL @ BOS</t>
+          <t>ATL @ MIA</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Guard</t>
+          <t>Forward</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>19.5</v>
+        <v>15.5</v>
       </c>
       <c r="E9" t="n">
-        <v>15</v>
+        <v>13.3</v>
       </c>
       <c r="F9" t="n">
-        <v>19.8</v>
+        <v>14.8</v>
       </c>
       <c r="G9" t="n">
-        <v>19.1</v>
+        <v>13.6</v>
       </c>
       <c r="H9" t="n">
-        <v>20.2</v>
+        <v>15.3</v>
       </c>
       <c r="I9" t="n">
-        <v>21.8</v>
+        <v>15.2</v>
       </c>
       <c r="J9" t="n">
-        <v>31.1</v>
+        <v>27.2</v>
       </c>
       <c r="K9" t="n">
-        <v>33.6</v>
+        <v>28.8</v>
       </c>
       <c r="L9" t="n">
-        <v>45.4</v>
+        <v>52</v>
       </c>
       <c r="M9" t="n">
-        <v>51.5</v>
+        <v>50.2</v>
       </c>
       <c r="N9" t="n">
-        <v>7.5</v>
+        <v>5.5</v>
       </c>
       <c r="O9" t="n">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="P9" t="n">
-        <v>57</v>
+        <v>40</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.3</v>
+        <v>-0.3</v>
       </c>
       <c r="R9" t="n">
-        <v>-2</v>
+        <v>-0.4</v>
       </c>
       <c r="S9" t="n">
-        <v>-6.1</v>
+        <v>1.8</v>
       </c>
       <c r="T9" t="n">
-        <v>-2.5</v>
+        <v>-1.5</v>
       </c>
       <c r="U9" t="n">
-        <v>2</v>
+        <v>24</v>
       </c>
       <c r="V9" t="n">
-        <v>24</v>
+        <v>8</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>15.0 (5g)</t>
+          <t>18.7 (6g)</t>
         </is>
       </c>
       <c r="X9" t="n">
-        <v>-3.2</v>
+        <v>3.1</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Wendell Carter Jr.</t>
+          <t>Paolo Banchero</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1224,494 +1224,494 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Center</t>
+          <t>Forward</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>11.5</v>
+        <v>20.5</v>
       </c>
       <c r="E10" t="n">
-        <v>9</v>
+        <v>21.7</v>
       </c>
       <c r="F10" t="n">
-        <v>13.6</v>
+        <v>19.6</v>
       </c>
       <c r="G10" t="n">
-        <v>12.6</v>
+        <v>20.3</v>
       </c>
       <c r="H10" t="n">
-        <v>13.2</v>
+        <v>22.8</v>
       </c>
       <c r="I10" t="n">
-        <v>11.7</v>
+        <v>22.9</v>
       </c>
       <c r="J10" t="n">
-        <v>27.5</v>
+        <v>33.4</v>
       </c>
       <c r="K10" t="n">
-        <v>28.6</v>
+        <v>35.1</v>
       </c>
       <c r="L10" t="n">
-        <v>55.1</v>
+        <v>46.8</v>
       </c>
       <c r="M10" t="n">
-        <v>53.7</v>
+        <v>45.5</v>
       </c>
       <c r="N10" t="n">
-        <v>6.7</v>
+        <v>9.6</v>
       </c>
       <c r="O10" t="n">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="P10" t="n">
         <v>50</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.2</v>
+        <v>2.4</v>
       </c>
       <c r="R10" t="n">
-        <v>1.9</v>
+        <v>-3.3</v>
       </c>
       <c r="S10" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="T10" t="n">
-        <v>-1.1</v>
+        <v>-1.7</v>
       </c>
       <c r="U10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V10" t="n">
         <v>24</v>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>12.8 (5g)</t>
+          <t>19.8 (4g)</t>
         </is>
       </c>
       <c r="X10" t="n">
-        <v>2.4</v>
+        <v>-2.9</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Immanuel Quickley</t>
+          <t>Wendell Carter Jr.</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>BKN @ TOR</t>
+          <t>ORL @ BOS</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Guard</t>
+          <t>Center</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>14.5</v>
+        <v>10.5</v>
       </c>
       <c r="E11" t="n">
-        <v>8.300000000000001</v>
+        <v>9</v>
       </c>
       <c r="F11" t="n">
-        <v>10</v>
+        <v>13.6</v>
       </c>
       <c r="G11" t="n">
-        <v>12</v>
+        <v>12.6</v>
       </c>
       <c r="H11" t="n">
-        <v>15.8</v>
+        <v>13.2</v>
       </c>
       <c r="I11" t="n">
-        <v>16.8</v>
+        <v>11.7</v>
       </c>
       <c r="J11" t="n">
-        <v>29.7</v>
+        <v>27.5</v>
       </c>
       <c r="K11" t="n">
-        <v>31.6</v>
+        <v>28.6</v>
       </c>
       <c r="L11" t="n">
-        <v>38</v>
+        <v>55.1</v>
       </c>
       <c r="M11" t="n">
-        <v>46.6</v>
+        <v>53.7</v>
       </c>
       <c r="N11" t="n">
-        <v>6.1</v>
+        <v>6.7</v>
       </c>
       <c r="O11" t="n">
-        <v>30</v>
+        <v>70</v>
       </c>
       <c r="P11" t="n">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.3</v>
+        <v>1.2</v>
       </c>
       <c r="R11" t="n">
-        <v>-6.8</v>
+        <v>1.9</v>
       </c>
       <c r="S11" t="n">
-        <v>-8.6</v>
+        <v>1.4</v>
       </c>
       <c r="T11" t="n">
-        <v>-1.9</v>
+        <v>-1.1</v>
       </c>
       <c r="U11" t="n">
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="V11" t="n">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>18.8 (4g)</t>
+          <t>12.8 (5g)</t>
         </is>
       </c>
       <c r="X11" t="n">
-        <v>-0.6</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Scottie Barnes</t>
+          <t>Jalen Suggs</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>BKN @ TOR</t>
+          <t>ORL @ BOS</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Forward</t>
+          <t>Guard</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>19.5</v>
+        <v>12.5</v>
       </c>
       <c r="E12" t="n">
-        <v>17.7</v>
+        <v>11.7</v>
       </c>
       <c r="F12" t="n">
-        <v>14.6</v>
+        <v>13</v>
       </c>
       <c r="G12" t="n">
-        <v>14.7</v>
+        <v>12.7</v>
       </c>
       <c r="H12" t="n">
-        <v>15.6</v>
+        <v>13.7</v>
       </c>
       <c r="I12" t="n">
-        <v>15.9</v>
+        <v>12.9</v>
       </c>
       <c r="J12" t="n">
-        <v>30.3</v>
+        <v>30.2</v>
       </c>
       <c r="K12" t="n">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="L12" t="n">
-        <v>51</v>
+        <v>45.3</v>
       </c>
       <c r="M12" t="n">
-        <v>52.3</v>
+        <v>43.1</v>
       </c>
       <c r="N12" t="n">
-        <v>6.8</v>
+        <v>4.2</v>
       </c>
       <c r="O12" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="P12" t="n">
-        <v>23</v>
+        <v>50</v>
       </c>
       <c r="Q12" t="n">
-        <v>-3.6</v>
+        <v>0.4</v>
       </c>
       <c r="R12" t="n">
-        <v>-1.3</v>
+        <v>0.1</v>
       </c>
       <c r="S12" t="n">
-        <v>-1.3</v>
+        <v>2.2</v>
       </c>
       <c r="T12" t="n">
-        <v>-1.7</v>
+        <v>1.2</v>
       </c>
       <c r="U12" t="n">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="V12" t="n">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>17.0 (6g)</t>
+          <t>16.7 (3g)</t>
         </is>
       </c>
       <c r="X12" t="n">
-        <v>3.8</v>
+        <v>17</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Brandon Ingram</t>
+          <t>Desmond Bane</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>BKN @ TOR</t>
+          <t>ORL @ BOS</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Forward</t>
+          <t>Guard</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>20.5</v>
+        <v>17.5</v>
       </c>
       <c r="E13" t="n">
-        <v>25.7</v>
+        <v>15</v>
       </c>
       <c r="F13" t="n">
+        <v>19.8</v>
+      </c>
+      <c r="G13" t="n">
+        <v>19.1</v>
+      </c>
+      <c r="H13" t="n">
+        <v>20.2</v>
+      </c>
+      <c r="I13" t="n">
         <v>21.8</v>
       </c>
-      <c r="G13" t="n">
-        <v>18.7</v>
-      </c>
-      <c r="H13" t="n">
-        <v>20.3</v>
-      </c>
-      <c r="I13" t="n">
-        <v>21.3</v>
-      </c>
       <c r="J13" t="n">
-        <v>32.1</v>
+        <v>31.1</v>
       </c>
       <c r="K13" t="n">
-        <v>33.5</v>
+        <v>33.6</v>
       </c>
       <c r="L13" t="n">
-        <v>48.5</v>
+        <v>45.4</v>
       </c>
       <c r="M13" t="n">
-        <v>49.4</v>
+        <v>51.5</v>
       </c>
       <c r="N13" t="n">
-        <v>8.300000000000001</v>
+        <v>7.5</v>
       </c>
       <c r="O13" t="n">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="P13" t="n">
-        <v>47</v>
+        <v>67</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.8</v>
+        <v>4.3</v>
       </c>
       <c r="R13" t="n">
-        <v>0.5</v>
+        <v>-2</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.9</v>
+        <v>-6.1</v>
       </c>
       <c r="T13" t="n">
-        <v>-1.4</v>
+        <v>-2.5</v>
       </c>
       <c r="U13" t="n">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="V13" t="n">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>20.5 (4g)</t>
+          <t>15.0 (5g)</t>
         </is>
       </c>
       <c r="X13" t="n">
-        <v>-7.1</v>
+        <v>-3.2</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>LaMelo Ball</t>
+          <t>Franz Wagner</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>CHA @ NYK</t>
+          <t>ORL @ BOS</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Guard</t>
+          <t>Forward</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>22.5</v>
+        <v>16.5</v>
       </c>
       <c r="E14" t="n">
-        <v>32.7</v>
+        <v>17.7</v>
       </c>
       <c r="F14" t="n">
-        <v>26.2</v>
+        <v>16.6</v>
       </c>
       <c r="G14" t="n">
-        <v>22.6</v>
+        <v>14.1</v>
       </c>
       <c r="H14" t="n">
-        <v>22.1</v>
+        <v>19.2</v>
       </c>
       <c r="I14" t="n">
-        <v>21.4</v>
+        <v>20.4</v>
       </c>
       <c r="J14" t="n">
-        <v>30.6</v>
+        <v>20</v>
       </c>
       <c r="K14" t="n">
-        <v>28.7</v>
+        <v>29.6</v>
       </c>
       <c r="L14" t="n">
-        <v>42.1</v>
+        <v>48.6</v>
       </c>
       <c r="M14" t="n">
-        <v>41.3</v>
+        <v>48.4</v>
       </c>
       <c r="N14" t="n">
-        <v>7.7</v>
+        <v>5.8</v>
       </c>
       <c r="O14" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="P14" t="n">
-        <v>27</v>
+        <v>77</v>
       </c>
       <c r="Q14" t="n">
-        <v>-1.1</v>
+        <v>3.9</v>
       </c>
       <c r="R14" t="n">
-        <v>4.8</v>
+        <v>-3.8</v>
       </c>
       <c r="S14" t="n">
-        <v>0.8</v>
+        <v>0.2</v>
       </c>
       <c r="T14" t="n">
-        <v>1.8</v>
+        <v>-9.6</v>
       </c>
       <c r="U14" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="V14" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>23.0 (4g)</t>
+          <t>21.2 (4g)</t>
         </is>
       </c>
       <c r="X14" t="n">
-        <v>1.2</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Miles Bridges</t>
+          <t>Immanuel Quickley</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>CHA @ NYK</t>
+          <t>BKN @ TOR</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Forward</t>
+          <t>Guard</t>
         </is>
       </c>
       <c r="D15" t="n">
         <v>14.5</v>
       </c>
       <c r="E15" t="n">
-        <v>16</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="F15" t="n">
-        <v>18.4</v>
+        <v>10</v>
       </c>
       <c r="G15" t="n">
-        <v>16.2</v>
+        <v>12</v>
       </c>
       <c r="H15" t="n">
-        <v>15.3</v>
+        <v>15.8</v>
       </c>
       <c r="I15" t="n">
-        <v>15.1</v>
+        <v>16.8</v>
       </c>
       <c r="J15" t="n">
-        <v>28</v>
+        <v>29.7</v>
       </c>
       <c r="K15" t="n">
-        <v>29</v>
+        <v>31.6</v>
       </c>
       <c r="L15" t="n">
-        <v>54.3</v>
+        <v>38</v>
       </c>
       <c r="M15" t="n">
-        <v>48.5</v>
+        <v>46.6</v>
       </c>
       <c r="N15" t="n">
-        <v>5.8</v>
+        <v>6.1</v>
       </c>
       <c r="O15" t="n">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="P15" t="n">
-        <v>43</v>
+        <v>57</v>
       </c>
       <c r="Q15" t="n">
-        <v>0.6</v>
+        <v>2.3</v>
       </c>
       <c r="R15" t="n">
-        <v>3.3</v>
+        <v>-6.8</v>
       </c>
       <c r="S15" t="n">
-        <v>5.8</v>
+        <v>-8.6</v>
       </c>
       <c r="T15" t="n">
-        <v>-1</v>
+        <v>-1.9</v>
       </c>
       <c r="U15" t="n">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="V15" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>14.2 (4g)</t>
+          <t>18.8 (4g)</t>
         </is>
       </c>
       <c r="X15" t="n">
-        <v>-11.2</v>
+        <v>-0.6</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Brandon Miller</t>
+          <t>Brandon Ingram</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>CHA @ NYK</t>
+          <t>BKN @ TOR</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1720,80 +1720,80 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>20.5</v>
+        <v>19.5</v>
       </c>
       <c r="E16" t="n">
-        <v>16.3</v>
+        <v>25.7</v>
       </c>
       <c r="F16" t="n">
-        <v>17.6</v>
+        <v>21.8</v>
       </c>
       <c r="G16" t="n">
-        <v>18.9</v>
+        <v>18.7</v>
       </c>
       <c r="H16" t="n">
-        <v>18.4</v>
+        <v>20.3</v>
       </c>
       <c r="I16" t="n">
-        <v>19.7</v>
+        <v>21.3</v>
       </c>
       <c r="J16" t="n">
-        <v>31.4</v>
+        <v>32.1</v>
       </c>
       <c r="K16" t="n">
-        <v>30.3</v>
+        <v>33.5</v>
       </c>
       <c r="L16" t="n">
-        <v>44.9</v>
+        <v>48.5</v>
       </c>
       <c r="M16" t="n">
-        <v>45.1</v>
+        <v>49.4</v>
       </c>
       <c r="N16" t="n">
-        <v>6.5</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="O16" t="n">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="P16" t="n">
         <v>50</v>
       </c>
       <c r="Q16" t="n">
-        <v>-0.8</v>
+        <v>1.8</v>
       </c>
       <c r="R16" t="n">
-        <v>-2.1</v>
+        <v>0.5</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.2</v>
+        <v>-0.9</v>
       </c>
       <c r="T16" t="n">
-        <v>1.1</v>
+        <v>-1.4</v>
       </c>
       <c r="U16" t="n">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="V16" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>21.2 (4g)</t>
+          <t>20.5 (4g)</t>
         </is>
       </c>
       <c r="X16" t="n">
-        <v>0.5</v>
+        <v>-7.1</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Moussa Diabaté</t>
+          <t>Scottie Barnes</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>CHA @ NYK</t>
+          <t>BKN @ TOR</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1802,75 +1802,75 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>7.5</v>
+        <v>16.5</v>
       </c>
       <c r="E17" t="n">
-        <v>6</v>
+        <v>17.7</v>
       </c>
       <c r="F17" t="n">
-        <v>6.4</v>
+        <v>14.6</v>
       </c>
       <c r="G17" t="n">
-        <v>7.6</v>
+        <v>14.7</v>
       </c>
       <c r="H17" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="I17" t="n">
+        <v>15.9</v>
+      </c>
+      <c r="J17" t="n">
+        <v>30.3</v>
+      </c>
+      <c r="K17" t="n">
+        <v>32</v>
+      </c>
+      <c r="L17" t="n">
+        <v>51</v>
+      </c>
+      <c r="M17" t="n">
+        <v>52.3</v>
+      </c>
+      <c r="N17" t="n">
         <v>6.8</v>
       </c>
-      <c r="I17" t="n">
-        <v>7.7</v>
-      </c>
-      <c r="J17" t="n">
-        <v>27</v>
-      </c>
-      <c r="K17" t="n">
-        <v>28</v>
-      </c>
-      <c r="L17" t="n">
-        <v>72.59999999999999</v>
-      </c>
-      <c r="M17" t="n">
-        <v>61.4</v>
-      </c>
-      <c r="N17" t="n">
-        <v>4.7</v>
-      </c>
       <c r="O17" t="n">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="P17" t="n">
-        <v>53</v>
+        <v>40</v>
       </c>
       <c r="Q17" t="n">
-        <v>0.2</v>
+        <v>-0.6</v>
       </c>
       <c r="R17" t="n">
         <v>-1.3</v>
       </c>
       <c r="S17" t="n">
-        <v>11.2</v>
+        <v>-1.3</v>
       </c>
       <c r="T17" t="n">
-        <v>-1</v>
+        <v>-1.7</v>
       </c>
       <c r="U17" t="n">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="V17" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>4.2 (6g)</t>
+          <t>17.0 (6g)</t>
         </is>
       </c>
       <c r="X17" t="n">
-        <v>1.7</v>
+        <v>3.8</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Kon Knueppel</t>
+          <t>LaMelo Ball</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1884,55 +1884,55 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>17.5</v>
+        <v>22.5</v>
       </c>
       <c r="E18" t="n">
-        <v>11.3</v>
+        <v>32.7</v>
       </c>
       <c r="F18" t="n">
-        <v>14.8</v>
+        <v>26.2</v>
       </c>
       <c r="G18" t="n">
-        <v>14.6</v>
+        <v>22.6</v>
       </c>
       <c r="H18" t="n">
-        <v>16.4</v>
+        <v>22.1</v>
       </c>
       <c r="I18" t="n">
-        <v>18.3</v>
+        <v>21.4</v>
       </c>
       <c r="J18" t="n">
-        <v>30.9</v>
+        <v>30.6</v>
       </c>
       <c r="K18" t="n">
-        <v>30.6</v>
+        <v>28.7</v>
       </c>
       <c r="L18" t="n">
-        <v>40.1</v>
+        <v>42.1</v>
       </c>
       <c r="M18" t="n">
-        <v>46.2</v>
+        <v>41.3</v>
       </c>
       <c r="N18" t="n">
-        <v>5.6</v>
+        <v>7.7</v>
       </c>
       <c r="O18" t="n">
         <v>30</v>
       </c>
       <c r="P18" t="n">
-        <v>53</v>
+        <v>27</v>
       </c>
       <c r="Q18" t="n">
+        <v>-1.1</v>
+      </c>
+      <c r="R18" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="S18" t="n">
         <v>0.8</v>
       </c>
-      <c r="R18" t="n">
-        <v>-3.5</v>
-      </c>
-      <c r="S18" t="n">
-        <v>-6.1</v>
-      </c>
       <c r="T18" t="n">
-        <v>0.3</v>
+        <v>1.8</v>
       </c>
       <c r="U18" t="n">
         <v>4</v>
@@ -1942,100 +1942,104 @@
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>15.0 (3g)</t>
+          <t>23.0 (4g)</t>
         </is>
       </c>
       <c r="X18" t="n">
-        <v>-14.5</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Quenton Jackson</t>
+          <t>Miles Bridges</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>DET @ IND</t>
+          <t>CHA @ NYK</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Guard</t>
+          <t>Forward</t>
         </is>
       </c>
       <c r="D19" t="n">
         <v>14.5</v>
       </c>
       <c r="E19" t="n">
-        <v>12.3</v>
+        <v>16</v>
       </c>
       <c r="F19" t="n">
-        <v>13.6</v>
+        <v>18.4</v>
       </c>
       <c r="G19" t="n">
-        <v>9.9</v>
+        <v>16.2</v>
       </c>
       <c r="H19" t="n">
-        <v>8.9</v>
+        <v>15.3</v>
       </c>
       <c r="I19" t="n">
-        <v>9.800000000000001</v>
+        <v>15.1</v>
       </c>
       <c r="J19" t="n">
-        <v>20.6</v>
+        <v>28</v>
       </c>
       <c r="K19" t="n">
-        <v>19.4</v>
+        <v>29</v>
       </c>
       <c r="L19" t="n">
-        <v>45.8</v>
+        <v>54.3</v>
       </c>
       <c r="M19" t="n">
-        <v>46.7</v>
+        <v>48.5</v>
       </c>
       <c r="N19" t="n">
-        <v>5.1</v>
+        <v>5.8</v>
       </c>
       <c r="O19" t="n">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="P19" t="n">
-        <v>23</v>
+        <v>43</v>
       </c>
       <c r="Q19" t="n">
-        <v>-4.7</v>
+        <v>0.6</v>
       </c>
       <c r="R19" t="n">
-        <v>3.8</v>
+        <v>3.3</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.9</v>
+        <v>5.8</v>
       </c>
       <c r="T19" t="n">
-        <v>1.2</v>
+        <v>-1</v>
       </c>
       <c r="U19" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="V19" t="n">
-        <v>22</v>
-      </c>
-      <c r="W19" t="inlineStr"/>
+        <v>26</v>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>14.2 (4g)</t>
+        </is>
+      </c>
       <c r="X19" t="n">
-        <v>-4.8</v>
+        <v>-11.2</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Ausar Thompson</t>
+          <t>Kon Knueppel</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>DET @ IND</t>
+          <t>CHA @ NYK</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -2044,157 +2048,157 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>9.5</v>
+        <v>17.5</v>
       </c>
       <c r="E20" t="n">
-        <v>10</v>
+        <v>11.3</v>
       </c>
       <c r="F20" t="n">
-        <v>10.2</v>
+        <v>14.8</v>
       </c>
       <c r="G20" t="n">
-        <v>9.9</v>
+        <v>14.6</v>
       </c>
       <c r="H20" t="n">
-        <v>9.300000000000001</v>
+        <v>16.4</v>
       </c>
       <c r="I20" t="n">
-        <v>8.800000000000001</v>
+        <v>18.3</v>
       </c>
       <c r="J20" t="n">
-        <v>27.8</v>
+        <v>30.9</v>
       </c>
       <c r="K20" t="n">
-        <v>26.6</v>
+        <v>30.6</v>
       </c>
       <c r="L20" t="n">
-        <v>64.8</v>
+        <v>40.1</v>
       </c>
       <c r="M20" t="n">
-        <v>54.2</v>
+        <v>46.2</v>
       </c>
       <c r="N20" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="O20" t="n">
+        <v>30</v>
+      </c>
+      <c r="P20" t="n">
+        <v>53</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="R20" t="n">
+        <v>-3.5</v>
+      </c>
+      <c r="S20" t="n">
+        <v>-6.1</v>
+      </c>
+      <c r="T20" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="U20" t="n">
         <v>4</v>
       </c>
-      <c r="O20" t="n">
-        <v>50</v>
-      </c>
-      <c r="P20" t="n">
-        <v>40</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>-0.7</v>
-      </c>
-      <c r="R20" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="S20" t="n">
-        <v>10.6</v>
-      </c>
-      <c r="T20" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="U20" t="n">
-        <v>22</v>
-      </c>
       <c r="V20" t="n">
-        <v>11</v>
+        <v>26</v>
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>8.6 (5g)</t>
+          <t>15.0 (3g)</t>
         </is>
       </c>
       <c r="X20" t="n">
-        <v>-0.2</v>
+        <v>-14.5</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Cade Cunningham</t>
+          <t>Brandon Miller</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>DET @ IND</t>
+          <t>CHA @ NYK</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Guard</t>
+          <t>Forward</t>
         </is>
       </c>
       <c r="D21" t="n">
         <v>19.5</v>
       </c>
       <c r="E21" t="n">
-        <v>11</v>
+        <v>16.3</v>
       </c>
       <c r="F21" t="n">
-        <v>16.6</v>
+        <v>17.6</v>
       </c>
       <c r="G21" t="n">
-        <v>17.4</v>
+        <v>18.9</v>
       </c>
       <c r="H21" t="n">
-        <v>21.8</v>
+        <v>18.4</v>
       </c>
       <c r="I21" t="n">
-        <v>21.4</v>
+        <v>19.7</v>
       </c>
       <c r="J21" t="n">
-        <v>29.3</v>
+        <v>31.4</v>
       </c>
       <c r="K21" t="n">
-        <v>32.4</v>
+        <v>30.3</v>
       </c>
       <c r="L21" t="n">
-        <v>52.3</v>
+        <v>44.9</v>
       </c>
       <c r="M21" t="n">
-        <v>47.8</v>
+        <v>45.1</v>
       </c>
       <c r="N21" t="n">
-        <v>8.9</v>
+        <v>6.5</v>
       </c>
       <c r="O21" t="n">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="P21" t="n">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="Q21" t="n">
-        <v>1.9</v>
+        <v>0.2</v>
       </c>
       <c r="R21" t="n">
-        <v>-4.8</v>
+        <v>-2.1</v>
       </c>
       <c r="S21" t="n">
-        <v>4.5</v>
+        <v>-0.2</v>
       </c>
       <c r="T21" t="n">
-        <v>-3.1</v>
+        <v>1.1</v>
       </c>
       <c r="U21" t="n">
-        <v>22</v>
+        <v>8</v>
       </c>
       <c r="V21" t="n">
-        <v>11</v>
+        <v>26</v>
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>24.0 (6g)</t>
+          <t>21.2 (4g)</t>
         </is>
       </c>
       <c r="X21" t="n">
-        <v>-2.2</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Tobias Harris</t>
+          <t>Jarace Walker</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2208,75 +2212,75 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>10.5</v>
+        <v>19.5</v>
       </c>
       <c r="E22" t="n">
-        <v>12.3</v>
+        <v>14</v>
       </c>
       <c r="F22" t="n">
-        <v>10.2</v>
+        <v>12.4</v>
       </c>
       <c r="G22" t="n">
-        <v>13</v>
+        <v>14.3</v>
       </c>
       <c r="H22" t="n">
-        <v>13.3</v>
+        <v>14.2</v>
       </c>
       <c r="I22" t="n">
-        <v>12.5</v>
+        <v>14.7</v>
       </c>
       <c r="J22" t="n">
-        <v>26</v>
+        <v>28.4</v>
       </c>
       <c r="K22" t="n">
-        <v>27.9</v>
+        <v>29.4</v>
       </c>
       <c r="L22" t="n">
-        <v>55.6</v>
+        <v>49.8</v>
       </c>
       <c r="M22" t="n">
-        <v>46.9</v>
+        <v>48.1</v>
       </c>
       <c r="N22" t="n">
-        <v>5.8</v>
+        <v>4.8</v>
       </c>
       <c r="O22" t="n">
-        <v>70</v>
+        <v>20</v>
       </c>
       <c r="P22" t="n">
-        <v>73</v>
+        <v>17</v>
       </c>
       <c r="Q22" t="n">
-        <v>2</v>
+        <v>-4.8</v>
       </c>
       <c r="R22" t="n">
         <v>-2.3</v>
       </c>
       <c r="S22" t="n">
-        <v>8.699999999999999</v>
+        <v>1.7</v>
       </c>
       <c r="T22" t="n">
-        <v>-1.9</v>
+        <v>-1</v>
       </c>
       <c r="U22" t="n">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="V22" t="n">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>12.8 (6g)</t>
+          <t>9.4 (7g)</t>
         </is>
       </c>
       <c r="X22" t="n">
-        <v>-0.2</v>
+        <v>13.1</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Micah Potter</t>
+          <t>Quenton Jackson</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2286,75 +2290,75 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Center</t>
+          <t>Guard</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>12.5</v>
+        <v>14.5</v>
       </c>
       <c r="E23" t="n">
-        <v>14</v>
+        <v>12.3</v>
       </c>
       <c r="F23" t="n">
-        <v>13.4</v>
+        <v>13.6</v>
       </c>
       <c r="G23" t="n">
-        <v>11.9</v>
+        <v>9.9</v>
       </c>
       <c r="H23" t="n">
-        <v>11</v>
+        <v>8.9</v>
       </c>
       <c r="I23" t="n">
-        <v>11.1</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="J23" t="n">
-        <v>20.2</v>
+        <v>20.6</v>
       </c>
       <c r="K23" t="n">
-        <v>19.7</v>
+        <v>19.4</v>
       </c>
       <c r="L23" t="n">
-        <v>59.5</v>
+        <v>45.8</v>
       </c>
       <c r="M23" t="n">
-        <v>57.8</v>
+        <v>46.7</v>
       </c>
       <c r="N23" t="n">
-        <v>6.5</v>
+        <v>5.1</v>
       </c>
       <c r="O23" t="n">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="P23" t="n">
-        <v>40</v>
+        <v>23</v>
       </c>
       <c r="Q23" t="n">
-        <v>-1.4</v>
+        <v>-4.7</v>
       </c>
       <c r="R23" t="n">
-        <v>2.3</v>
+        <v>3.8</v>
       </c>
       <c r="S23" t="n">
-        <v>1.7</v>
+        <v>-0.9</v>
       </c>
       <c r="T23" t="n">
-        <v>0.5</v>
+        <v>1.2</v>
       </c>
       <c r="U23" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="V23" t="n">
         <v>22</v>
       </c>
       <c r="W23" t="inlineStr"/>
       <c r="X23" t="n">
-        <v>-23.3</v>
+        <v>-4.8</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Jarace Walker</t>
+          <t>Ausar Thompson</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2364,161 +2368,157 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Forward</t>
+          <t>Guard</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>19.5</v>
+        <v>9.5</v>
       </c>
       <c r="E24" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="F24" t="n">
-        <v>12.4</v>
+        <v>10.2</v>
       </c>
       <c r="G24" t="n">
-        <v>14.3</v>
+        <v>9.9</v>
       </c>
       <c r="H24" t="n">
-        <v>14.2</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="I24" t="n">
-        <v>14.7</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J24" t="n">
-        <v>28.4</v>
+        <v>27.8</v>
       </c>
       <c r="K24" t="n">
-        <v>29.4</v>
+        <v>26.6</v>
       </c>
       <c r="L24" t="n">
-        <v>49.8</v>
+        <v>64.8</v>
       </c>
       <c r="M24" t="n">
-        <v>48.1</v>
+        <v>54.2</v>
       </c>
       <c r="N24" t="n">
-        <v>4.8</v>
+        <v>4</v>
       </c>
       <c r="O24" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="P24" t="n">
-        <v>17</v>
+        <v>40</v>
       </c>
       <c r="Q24" t="n">
-        <v>-4.8</v>
+        <v>-0.7</v>
       </c>
       <c r="R24" t="n">
-        <v>-2.3</v>
+        <v>1.4</v>
       </c>
       <c r="S24" t="n">
-        <v>1.7</v>
+        <v>10.6</v>
       </c>
       <c r="T24" t="n">
-        <v>-1</v>
+        <v>1.2</v>
       </c>
       <c r="U24" t="n">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="V24" t="n">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="W24" t="inlineStr">
         <is>
-          <t>9.4 (7g)</t>
+          <t>8.6 (5g)</t>
         </is>
       </c>
       <c r="X24" t="n">
-        <v>13.1</v>
+        <v>-0.2</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Tyrese Maxey</t>
+          <t>Micah Potter</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>MIL @ PHI</t>
+          <t>DET @ IND</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Guard</t>
+          <t>Center</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>28.5</v>
+        <v>13.5</v>
       </c>
       <c r="E25" t="n">
-        <v>23.3</v>
+        <v>14</v>
       </c>
       <c r="F25" t="n">
-        <v>22.8</v>
+        <v>13.4</v>
       </c>
       <c r="G25" t="n">
-        <v>24.7</v>
+        <v>11.9</v>
       </c>
       <c r="H25" t="n">
-        <v>27.3</v>
+        <v>11</v>
       </c>
       <c r="I25" t="n">
-        <v>26</v>
+        <v>11.1</v>
       </c>
       <c r="J25" t="n">
-        <v>37.6</v>
+        <v>20.2</v>
       </c>
       <c r="K25" t="n">
-        <v>36.6</v>
+        <v>19.7</v>
       </c>
       <c r="L25" t="n">
-        <v>46.4</v>
+        <v>59.5</v>
       </c>
       <c r="M25" t="n">
-        <v>44.2</v>
+        <v>57.8</v>
       </c>
       <c r="N25" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="O25" t="n">
+        <v>30</v>
+      </c>
+      <c r="P25" t="n">
+        <v>30</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>-2.4</v>
+      </c>
+      <c r="R25" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="S25" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="T25" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="U25" t="n">
         <v>5</v>
       </c>
-      <c r="O25" t="n">
-        <v>20</v>
-      </c>
-      <c r="P25" t="n">
-        <v>37</v>
-      </c>
-      <c r="Q25" t="n">
-        <v>-2.5</v>
-      </c>
-      <c r="R25" t="n">
-        <v>-3.2</v>
-      </c>
-      <c r="S25" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="T25" t="n">
-        <v>1</v>
-      </c>
-      <c r="U25" t="n">
-        <v>24</v>
-      </c>
       <c r="V25" t="n">
-        <v>14</v>
-      </c>
-      <c r="W25" t="inlineStr">
-        <is>
-          <t>31.5 (6g)</t>
-        </is>
-      </c>
+        <v>22</v>
+      </c>
+      <c r="W25" t="inlineStr"/>
       <c r="X25" t="n">
-        <v>3</v>
+        <v>-23.3</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>AJ Green</t>
+          <t>Tyrese Maxey</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2532,75 +2532,75 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>19.5</v>
+        <v>28.5</v>
       </c>
       <c r="E26" t="n">
-        <v>22.7</v>
+        <v>23.3</v>
       </c>
       <c r="F26" t="n">
-        <v>17.8</v>
+        <v>22.8</v>
       </c>
       <c r="G26" t="n">
-        <v>14.8</v>
+        <v>24.7</v>
       </c>
       <c r="H26" t="n">
-        <v>10.8</v>
+        <v>27.3</v>
       </c>
       <c r="I26" t="n">
-        <v>9.699999999999999</v>
+        <v>26</v>
       </c>
       <c r="J26" t="n">
-        <v>33</v>
+        <v>37.6</v>
       </c>
       <c r="K26" t="n">
-        <v>27.4</v>
+        <v>36.6</v>
       </c>
       <c r="L26" t="n">
-        <v>42.7</v>
+        <v>46.4</v>
       </c>
       <c r="M26" t="n">
-        <v>37</v>
+        <v>44.2</v>
       </c>
       <c r="N26" t="n">
-        <v>8.699999999999999</v>
+        <v>5</v>
       </c>
       <c r="O26" t="n">
         <v>20</v>
       </c>
       <c r="P26" t="n">
-        <v>7</v>
+        <v>37</v>
       </c>
       <c r="Q26" t="n">
-        <v>-9.800000000000001</v>
+        <v>-2.5</v>
       </c>
       <c r="R26" t="n">
-        <v>8.1</v>
+        <v>-3.2</v>
       </c>
       <c r="S26" t="n">
-        <v>5.7</v>
+        <v>2.2</v>
       </c>
       <c r="T26" t="n">
-        <v>5.6</v>
+        <v>1</v>
       </c>
       <c r="U26" t="n">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="V26" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="W26" t="inlineStr">
         <is>
-          <t>6.7 (6g)</t>
+          <t>31.5 (6g)</t>
         </is>
       </c>
       <c r="X26" t="n">
-        <v>10.1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Paul George</t>
+          <t>AJ Green</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2610,79 +2610,79 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Forward</t>
+          <t>Guard</t>
         </is>
       </c>
       <c r="D27" t="n">
         <v>19.5</v>
       </c>
       <c r="E27" t="n">
-        <v>14.7</v>
+        <v>22.7</v>
       </c>
       <c r="F27" t="n">
-        <v>17.4</v>
+        <v>17.8</v>
       </c>
       <c r="G27" t="n">
-        <v>21.4</v>
+        <v>14.8</v>
       </c>
       <c r="H27" t="n">
-        <v>18.8</v>
+        <v>10.8</v>
       </c>
       <c r="I27" t="n">
-        <v>18.3</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="J27" t="n">
-        <v>32.6</v>
+        <v>33</v>
       </c>
       <c r="K27" t="n">
-        <v>32.7</v>
+        <v>27.4</v>
       </c>
       <c r="L27" t="n">
-        <v>44.7</v>
+        <v>42.7</v>
       </c>
       <c r="M27" t="n">
-        <v>42.6</v>
+        <v>37</v>
       </c>
       <c r="N27" t="n">
-        <v>8.6</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="O27" t="n">
-        <v>60</v>
+        <v>20</v>
       </c>
       <c r="P27" t="n">
-        <v>37</v>
+        <v>7</v>
       </c>
       <c r="Q27" t="n">
-        <v>-1.2</v>
+        <v>-9.800000000000001</v>
       </c>
       <c r="R27" t="n">
-        <v>-0.9</v>
+        <v>8.1</v>
       </c>
       <c r="S27" t="n">
-        <v>2.1</v>
+        <v>5.7</v>
       </c>
       <c r="T27" t="n">
-        <v>-0.1</v>
+        <v>5.6</v>
       </c>
       <c r="U27" t="n">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="V27" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="W27" t="inlineStr">
         <is>
-          <t>21.2 (4g)</t>
+          <t>6.7 (6g)</t>
         </is>
       </c>
       <c r="X27" t="n">
-        <v>14.8</v>
+        <v>10.1</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>VJ Edgecombe</t>
+          <t>Paul George</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2692,412 +2692,412 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Guard</t>
+          <t>Forward</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>18.5</v>
+        <v>19.5</v>
       </c>
       <c r="E28" t="n">
-        <v>17</v>
+        <v>14.7</v>
       </c>
       <c r="F28" t="n">
-        <v>15.6</v>
+        <v>17.4</v>
       </c>
       <c r="G28" t="n">
-        <v>18.4</v>
+        <v>21.4</v>
       </c>
       <c r="H28" t="n">
+        <v>18.8</v>
+      </c>
+      <c r="I28" t="n">
         <v>18.3</v>
       </c>
-      <c r="I28" t="n">
-        <v>17.5</v>
-      </c>
       <c r="J28" t="n">
-        <v>35.5</v>
+        <v>32.6</v>
       </c>
       <c r="K28" t="n">
-        <v>34.2</v>
+        <v>32.7</v>
       </c>
       <c r="L28" t="n">
-        <v>51.7</v>
+        <v>44.7</v>
       </c>
       <c r="M28" t="n">
-        <v>44.7</v>
+        <v>42.6</v>
       </c>
       <c r="N28" t="n">
-        <v>7.5</v>
+        <v>8.6</v>
       </c>
       <c r="O28" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="P28" t="n">
-        <v>50</v>
+        <v>37</v>
       </c>
       <c r="Q28" t="n">
-        <v>-1</v>
+        <v>-1.2</v>
       </c>
       <c r="R28" t="n">
-        <v>-1.9</v>
+        <v>-0.9</v>
       </c>
       <c r="S28" t="n">
-        <v>7</v>
+        <v>2.1</v>
       </c>
       <c r="T28" t="n">
-        <v>1.3</v>
+        <v>-0.1</v>
       </c>
       <c r="U28" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="V28" t="n">
         <v>14</v>
       </c>
       <c r="W28" t="inlineStr">
         <is>
-          <t>12.0 (3g)</t>
+          <t>21.2 (4g)</t>
         </is>
       </c>
       <c r="X28" t="n">
-        <v>3.8</v>
+        <v>14.8</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Kawhi Leonard</t>
+          <t>VJ Edgecombe</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>GSW @ LAC</t>
+          <t>MIL @ PHI</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Forward</t>
+          <t>Guard</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>29.5</v>
+        <v>18.5</v>
       </c>
       <c r="E29" t="n">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="F29" t="n">
-        <v>25.6</v>
+        <v>15.6</v>
       </c>
       <c r="G29" t="n">
-        <v>25.4</v>
+        <v>18.4</v>
       </c>
       <c r="H29" t="n">
-        <v>27.8</v>
+        <v>18.3</v>
       </c>
       <c r="I29" t="n">
-        <v>28.2</v>
+        <v>17.5</v>
       </c>
       <c r="J29" t="n">
-        <v>30.7</v>
+        <v>35.5</v>
       </c>
       <c r="K29" t="n">
-        <v>31.1</v>
+        <v>34.2</v>
       </c>
       <c r="L29" t="n">
-        <v>50.3</v>
+        <v>51.7</v>
       </c>
       <c r="M29" t="n">
-        <v>52.1</v>
+        <v>44.7</v>
       </c>
       <c r="N29" t="n">
-        <v>4.2</v>
+        <v>7.5</v>
       </c>
       <c r="O29" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="P29" t="n">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="Q29" t="n">
-        <v>-1.3</v>
+        <v>-1</v>
       </c>
       <c r="R29" t="n">
-        <v>-2.6</v>
+        <v>-1.9</v>
       </c>
       <c r="S29" t="n">
-        <v>-1.8</v>
+        <v>7</v>
       </c>
       <c r="T29" t="n">
-        <v>-0.4</v>
+        <v>1.3</v>
       </c>
       <c r="U29" t="n">
+        <v>24</v>
+      </c>
+      <c r="V29" t="n">
         <v>14</v>
       </c>
-      <c r="V29" t="n">
-        <v>13</v>
-      </c>
       <c r="W29" t="inlineStr">
         <is>
-          <t>24.5 (4g)</t>
+          <t>12.0 (3g)</t>
         </is>
       </c>
       <c r="X29" t="n">
-        <v>-1.8</v>
+        <v>3.8</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Darius Garland</t>
+          <t>Nikola Jokić</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>GSW @ LAC</t>
+          <t>DEN @ SAS</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Guard</t>
+          <t>Center</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>19.5</v>
+        <v>16.5</v>
       </c>
       <c r="E30" t="n">
-        <v>18.3</v>
+        <v>29.7</v>
       </c>
       <c r="F30" t="n">
-        <v>17.2</v>
+        <v>25.8</v>
       </c>
       <c r="G30" t="n">
-        <v>21.1</v>
+        <v>25.2</v>
       </c>
       <c r="H30" t="n">
-        <v>20.3</v>
+        <v>25.8</v>
       </c>
       <c r="I30" t="n">
-        <v>19.4</v>
+        <v>26</v>
       </c>
       <c r="J30" t="n">
-        <v>30.8</v>
+        <v>37.1</v>
       </c>
       <c r="K30" t="n">
-        <v>29.8</v>
+        <v>36.2</v>
       </c>
       <c r="L30" t="n">
-        <v>50</v>
+        <v>56.2</v>
       </c>
       <c r="M30" t="n">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="N30" t="n">
-        <v>8.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="O30" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="P30" t="n">
-        <v>50</v>
+        <v>87</v>
       </c>
       <c r="Q30" t="n">
-        <v>-0.1</v>
+        <v>9.5</v>
       </c>
       <c r="R30" t="n">
-        <v>-2.2</v>
+        <v>-0.2</v>
       </c>
       <c r="S30" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="T30" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="U30" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="V30" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="W30" t="inlineStr">
         <is>
-          <t>20.2 (4g)</t>
+          <t>35.8 (5g)</t>
         </is>
       </c>
       <c r="X30" t="n">
-        <v>2.7</v>
+        <v>-6</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Tari Eason</t>
+          <t>Bruce Brown</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>MEM @ HOU</t>
+          <t>DEN @ SAS</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Forward</t>
+          <t>Guard</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>14.5</v>
+        <v>8.5</v>
       </c>
       <c r="E31" t="n">
-        <v>9</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="F31" t="n">
         <v>9</v>
       </c>
       <c r="G31" t="n">
-        <v>10.1</v>
+        <v>9.5</v>
       </c>
       <c r="H31" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="I31" t="n">
-        <v>8.300000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="J31" t="n">
-        <v>25</v>
+        <v>22.3</v>
       </c>
       <c r="K31" t="n">
-        <v>26.8</v>
+        <v>24.1</v>
       </c>
       <c r="L31" t="n">
-        <v>38.2</v>
+        <v>49.5</v>
       </c>
       <c r="M31" t="n">
-        <v>34.8</v>
+        <v>47.7</v>
       </c>
       <c r="N31" t="n">
-        <v>6.8</v>
+        <v>3.5</v>
       </c>
       <c r="O31" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="P31" t="n">
-        <v>17</v>
+        <v>47</v>
       </c>
       <c r="Q31" t="n">
-        <v>-6.2</v>
+        <v>-0.1</v>
       </c>
       <c r="R31" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="S31" t="n">
-        <v>3.4</v>
+        <v>1.8</v>
       </c>
       <c r="T31" t="n">
         <v>-1.8</v>
       </c>
       <c r="U31" t="n">
-        <v>23</v>
+        <v>8</v>
       </c>
       <c r="V31" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="W31" t="inlineStr">
         <is>
-          <t>15.0 (5g)</t>
+          <t>7.2 (6g)</t>
         </is>
       </c>
       <c r="X31" t="n">
-        <v>2.8</v>
+        <v>-7.2</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>LeBron James</t>
+          <t>Julian Strawther</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>UTA @ LAL</t>
+          <t>DEN @ SAS</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Forward</t>
+          <t>Guard</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>27.5</v>
+        <v>15.5</v>
       </c>
       <c r="E32" t="n">
-        <v>28</v>
+        <v>14.3</v>
       </c>
       <c r="F32" t="n">
-        <v>22.2</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="G32" t="n">
-        <v>19.3</v>
+        <v>7.1</v>
       </c>
       <c r="H32" t="n">
-        <v>19.6</v>
+        <v>6.5</v>
       </c>
       <c r="I32" t="n">
+        <v>9</v>
+      </c>
+      <c r="J32" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="K32" t="n">
+        <v>17.8</v>
+      </c>
+      <c r="L32" t="n">
+        <v>38.6</v>
+      </c>
+      <c r="M32" t="n">
+        <v>43.6</v>
+      </c>
+      <c r="N32" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="O32" t="n">
+        <v>10</v>
+      </c>
+      <c r="P32" t="n">
         <v>20</v>
       </c>
-      <c r="J32" t="n">
-        <v>33.7</v>
-      </c>
-      <c r="K32" t="n">
-        <v>33.6</v>
-      </c>
-      <c r="L32" t="n">
-        <v>50.2</v>
-      </c>
-      <c r="M32" t="n">
-        <v>53.3</v>
-      </c>
-      <c r="N32" t="n">
-        <v>7.1</v>
-      </c>
-      <c r="O32" t="n">
-        <v>20</v>
-      </c>
-      <c r="P32" t="n">
-        <v>13</v>
-      </c>
       <c r="Q32" t="n">
-        <v>-7.5</v>
+        <v>-6.5</v>
       </c>
       <c r="R32" t="n">
-        <v>2.2</v>
+        <v>0.8</v>
       </c>
       <c r="S32" t="n">
-        <v>-3.1</v>
+        <v>-5</v>
       </c>
       <c r="T32" t="n">
-        <v>0.1</v>
+        <v>-4.3</v>
       </c>
       <c r="U32" t="n">
-        <v>27</v>
+        <v>8</v>
       </c>
       <c r="V32" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="W32" t="inlineStr">
         <is>
-          <t>21.6 (7g)</t>
+          <t>8.0 (4g)</t>
         </is>
       </c>
       <c r="X32" t="n">
-        <v>-3.6</v>
+        <v>4.7</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Brice Sensabaugh</t>
+          <t>Kawhi Leonard</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>UTA @ LAL</t>
+          <t>GSW @ LAC</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -3106,157 +3106,157 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>21.5</v>
+        <v>28.5</v>
       </c>
       <c r="E33" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="F33" t="n">
-        <v>23.6</v>
+        <v>25.6</v>
       </c>
       <c r="G33" t="n">
-        <v>24.4</v>
+        <v>25.4</v>
       </c>
       <c r="H33" t="n">
-        <v>21.4</v>
+        <v>27.8</v>
       </c>
       <c r="I33" t="n">
-        <v>19.4</v>
+        <v>28.2</v>
       </c>
       <c r="J33" t="n">
+        <v>30.7</v>
+      </c>
+      <c r="K33" t="n">
         <v>31.1</v>
       </c>
-      <c r="K33" t="n">
-        <v>27.5</v>
-      </c>
       <c r="L33" t="n">
-        <v>50.6</v>
+        <v>50.3</v>
       </c>
       <c r="M33" t="n">
-        <v>44.9</v>
+        <v>52.1</v>
       </c>
       <c r="N33" t="n">
-        <v>8.300000000000001</v>
+        <v>4.2</v>
       </c>
       <c r="O33" t="n">
-        <v>60</v>
+        <v>10</v>
       </c>
       <c r="P33" t="n">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="Q33" t="n">
-        <v>-2.1</v>
+        <v>-0.3</v>
       </c>
       <c r="R33" t="n">
-        <v>4.2</v>
+        <v>-2.6</v>
       </c>
       <c r="S33" t="n">
-        <v>5.7</v>
+        <v>-1.8</v>
       </c>
       <c r="T33" t="n">
-        <v>3.7</v>
+        <v>-0.4</v>
       </c>
       <c r="U33" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="V33" t="n">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="W33" t="inlineStr">
         <is>
-          <t>5.3 (6g)</t>
+          <t>24.5 (4g)</t>
         </is>
       </c>
       <c r="X33" t="n">
-        <v>-13.8</v>
+        <v>-1.8</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Cody Williams</t>
+          <t>Darius Garland</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>UTA @ LAL</t>
+          <t>GSW @ LAC</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Forward</t>
+          <t>Guard</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>17.5</v>
+        <v>20.5</v>
       </c>
       <c r="E34" t="n">
-        <v>13.7</v>
+        <v>18.3</v>
       </c>
       <c r="F34" t="n">
-        <v>15.4</v>
+        <v>17.2</v>
       </c>
       <c r="G34" t="n">
-        <v>16.6</v>
+        <v>21.1</v>
       </c>
       <c r="H34" t="n">
-        <v>15.4</v>
+        <v>20.3</v>
       </c>
       <c r="I34" t="n">
-        <v>12.2</v>
+        <v>19.4</v>
       </c>
       <c r="J34" t="n">
-        <v>34.8</v>
+        <v>30.8</v>
       </c>
       <c r="K34" t="n">
-        <v>31</v>
+        <v>29.8</v>
       </c>
       <c r="L34" t="n">
-        <v>40.7</v>
+        <v>50</v>
       </c>
       <c r="M34" t="n">
-        <v>48.2</v>
+        <v>50</v>
       </c>
       <c r="N34" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="O34" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="P34" t="n">
-        <v>27</v>
+        <v>40</v>
       </c>
       <c r="Q34" t="n">
-        <v>-5.3</v>
+        <v>-1.1</v>
       </c>
       <c r="R34" t="n">
-        <v>3.2</v>
+        <v>-2.2</v>
       </c>
       <c r="S34" t="n">
-        <v>-7.5</v>
+        <v>0</v>
       </c>
       <c r="T34" t="n">
-        <v>3.8</v>
+        <v>1</v>
       </c>
       <c r="U34" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="V34" t="n">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="W34" t="inlineStr">
         <is>
-          <t>2.8 (4g)</t>
+          <t>20.2 (4g)</t>
         </is>
       </c>
       <c r="X34" t="n">
-        <v>3.8</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Jake LaRavia</t>
+          <t>Brice Sensabaugh</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3270,69 +3270,69 @@
         </is>
       </c>
       <c r="D35" t="n">
-        <v>11.5</v>
+        <v>22.5</v>
       </c>
       <c r="E35" t="n">
-        <v>6.7</v>
+        <v>24</v>
       </c>
       <c r="F35" t="n">
-        <v>8</v>
+        <v>23.6</v>
       </c>
       <c r="G35" t="n">
-        <v>7.1</v>
+        <v>24.4</v>
       </c>
       <c r="H35" t="n">
-        <v>5.8</v>
+        <v>21.4</v>
       </c>
       <c r="I35" t="n">
-        <v>6.5</v>
+        <v>19.4</v>
       </c>
       <c r="J35" t="n">
-        <v>29.1</v>
+        <v>31.1</v>
       </c>
       <c r="K35" t="n">
-        <v>21.8</v>
+        <v>27.5</v>
       </c>
       <c r="L35" t="n">
-        <v>59.9</v>
+        <v>50.6</v>
       </c>
       <c r="M35" t="n">
-        <v>53.3</v>
+        <v>44.9</v>
       </c>
       <c r="N35" t="n">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="O35" t="n">
+        <v>50</v>
+      </c>
+      <c r="P35" t="n">
+        <v>30</v>
+      </c>
+      <c r="Q35" t="n">
+        <v>-3.1</v>
+      </c>
+      <c r="R35" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="S35" t="n">
         <v>5.7</v>
       </c>
-      <c r="O35" t="n">
-        <v>30</v>
-      </c>
-      <c r="P35" t="n">
-        <v>17</v>
-      </c>
-      <c r="Q35" t="n">
-        <v>-5</v>
-      </c>
-      <c r="R35" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="S35" t="n">
-        <v>6.6</v>
-      </c>
       <c r="T35" t="n">
-        <v>7.3</v>
+        <v>3.7</v>
       </c>
       <c r="U35" t="n">
-        <v>27</v>
+        <v>15</v>
       </c>
       <c r="V35" t="n">
-        <v>6</v>
+        <v>23</v>
       </c>
       <c r="W35" t="inlineStr">
         <is>
-          <t>7.6 (5g)</t>
+          <t>5.3 (6g)</t>
         </is>
       </c>
       <c r="X35" t="n">
-        <v>3.4</v>
+        <v>-13.8</v>
       </c>
     </row>
     <row r="36">
@@ -3352,7 +3352,7 @@
         </is>
       </c>
       <c r="D36" t="n">
-        <v>19.5</v>
+        <v>20.5</v>
       </c>
       <c r="E36" t="n">
         <v>19.7</v>
@@ -3388,10 +3388,10 @@
         <v>40</v>
       </c>
       <c r="P36" t="n">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="Q36" t="n">
-        <v>-2.4</v>
+        <v>-3.4</v>
       </c>
       <c r="R36" t="n">
         <v>0.9</v>
@@ -3420,172 +3420,176 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Luguentz Dort</t>
+          <t>Jake LaRavia</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>PHX @ OKC</t>
+          <t>UTA @ LAL</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Guard</t>
+          <t>Forward</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>7.5</v>
+        <v>12.5</v>
       </c>
       <c r="E37" t="n">
-        <v>6.3</v>
+        <v>6.7</v>
       </c>
       <c r="F37" t="n">
-        <v>9.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="G37" t="n">
-        <v>7.9</v>
+        <v>7.1</v>
       </c>
       <c r="H37" t="n">
-        <v>7.2</v>
+        <v>5.8</v>
       </c>
       <c r="I37" t="n">
-        <v>7.9</v>
+        <v>6.5</v>
       </c>
       <c r="J37" t="n">
-        <v>21.6</v>
+        <v>29.1</v>
       </c>
       <c r="K37" t="n">
-        <v>26</v>
+        <v>21.8</v>
       </c>
       <c r="L37" t="n">
-        <v>44.5</v>
+        <v>59.9</v>
       </c>
       <c r="M37" t="n">
-        <v>36.6</v>
+        <v>53.3</v>
       </c>
       <c r="N37" t="n">
-        <v>5</v>
+        <v>5.7</v>
       </c>
       <c r="O37" t="n">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="P37" t="n">
-        <v>47</v>
+        <v>17</v>
       </c>
       <c r="Q37" t="n">
-        <v>0.4</v>
+        <v>-6</v>
       </c>
       <c r="R37" t="n">
-        <v>1.3</v>
+        <v>1.5</v>
       </c>
       <c r="S37" t="n">
-        <v>7.9</v>
+        <v>6.6</v>
       </c>
       <c r="T37" t="n">
-        <v>-4.3</v>
+        <v>7.3</v>
       </c>
       <c r="U37" t="n">
-        <v>4</v>
+        <v>27</v>
       </c>
       <c r="V37" t="n">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="W37" t="inlineStr">
         <is>
-          <t>10.5 (6g)</t>
+          <t>7.6 (5g)</t>
         </is>
       </c>
       <c r="X37" t="n">
-        <v>4.1</v>
+        <v>3.4</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Nikola Topić</t>
+          <t>LeBron James</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>PHX @ OKC</t>
+          <t>UTA @ LAL</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Guard</t>
+          <t>Forward</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>14.5</v>
+        <v>26.5</v>
       </c>
       <c r="E38" t="n">
-        <v>5.3</v>
+        <v>28</v>
       </c>
       <c r="F38" t="n">
-        <v>3.6</v>
+        <v>22.2</v>
       </c>
       <c r="G38" t="n">
-        <v>3.8</v>
+        <v>19.3</v>
       </c>
       <c r="H38" t="n">
-        <v>3.8</v>
+        <v>19.6</v>
       </c>
       <c r="I38" t="n">
-        <v>3.8</v>
+        <v>20</v>
       </c>
       <c r="J38" t="n">
-        <v>13.3</v>
+        <v>33.7</v>
       </c>
       <c r="K38" t="n">
-        <v>13.3</v>
+        <v>33.6</v>
       </c>
       <c r="L38" t="n">
-        <v>33.3</v>
+        <v>50.2</v>
       </c>
       <c r="M38" t="n">
-        <v>33.3</v>
+        <v>53.3</v>
       </c>
       <c r="N38" t="n">
-        <v>4.7</v>
+        <v>7.1</v>
       </c>
       <c r="O38" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="P38" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="Q38" t="n">
-        <v>-10.7</v>
+        <v>-6.5</v>
       </c>
       <c r="R38" t="n">
-        <v>-0.2</v>
+        <v>2.2</v>
       </c>
       <c r="S38" t="n">
-        <v>0</v>
+        <v>-3.1</v>
       </c>
       <c r="T38" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="U38" t="n">
-        <v>4</v>
+        <v>27</v>
       </c>
       <c r="V38" t="n">
-        <v>20</v>
-      </c>
-      <c r="W38" t="inlineStr"/>
+        <v>6</v>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>21.6 (7g)</t>
+        </is>
+      </c>
       <c r="X38" t="n">
-        <v>0</v>
+        <v>-3.6</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Aaron Wiggins</t>
+          <t>Bronny James</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>PHX @ OKC</t>
+          <t>UTA @ LAL</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -3594,75 +3598,71 @@
         </is>
       </c>
       <c r="D39" t="n">
-        <v>17.5</v>
+        <v>10.5</v>
       </c>
       <c r="E39" t="n">
-        <v>8.300000000000001</v>
+        <v>5.7</v>
       </c>
       <c r="F39" t="n">
         <v>6.4</v>
       </c>
       <c r="G39" t="n">
-        <v>7.8</v>
+        <v>4.5</v>
       </c>
       <c r="H39" t="n">
-        <v>7.7</v>
+        <v>3.8</v>
       </c>
       <c r="I39" t="n">
-        <v>8.4</v>
+        <v>3</v>
       </c>
       <c r="J39" t="n">
-        <v>16.4</v>
+        <v>13.5</v>
       </c>
       <c r="K39" t="n">
-        <v>19.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="L39" t="n">
-        <v>51.1</v>
+        <v>36.6</v>
       </c>
       <c r="M39" t="n">
-        <v>42.2</v>
+        <v>30.5</v>
       </c>
       <c r="N39" t="n">
-        <v>5.1</v>
+        <v>3.5</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
       </c>
       <c r="P39" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="Q39" t="n">
-        <v>-9.1</v>
+        <v>-7.5</v>
       </c>
       <c r="R39" t="n">
-        <v>-2</v>
+        <v>3.4</v>
       </c>
       <c r="S39" t="n">
-        <v>8.9</v>
+        <v>6.1</v>
       </c>
       <c r="T39" t="n">
-        <v>-3</v>
+        <v>5.3</v>
       </c>
       <c r="U39" t="n">
-        <v>4</v>
+        <v>30</v>
       </c>
       <c r="V39" t="n">
-        <v>20</v>
-      </c>
-      <c r="W39" t="inlineStr">
-        <is>
-          <t>10.8 (6g)</t>
-        </is>
-      </c>
+        <v>6</v>
+      </c>
+      <c r="W39" t="inlineStr"/>
       <c r="X39" t="n">
-        <v>2</v>
+        <v>56</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Kenrich Williams</t>
+          <t>Luguentz Dort</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3676,52 +3676,52 @@
         </is>
       </c>
       <c r="D40" t="n">
-        <v>15.5</v>
+        <v>7.5</v>
       </c>
       <c r="E40" t="n">
-        <v>5.7</v>
+        <v>6.3</v>
       </c>
       <c r="F40" t="n">
-        <v>6.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="G40" t="n">
-        <v>5.2</v>
+        <v>7.9</v>
       </c>
       <c r="H40" t="n">
-        <v>5.4</v>
+        <v>7.2</v>
       </c>
       <c r="I40" t="n">
-        <v>6.8</v>
+        <v>7.9</v>
       </c>
       <c r="J40" t="n">
-        <v>11.2</v>
+        <v>21.6</v>
       </c>
       <c r="K40" t="n">
-        <v>15.5</v>
+        <v>26</v>
       </c>
       <c r="L40" t="n">
-        <v>35.8</v>
+        <v>44.5</v>
       </c>
       <c r="M40" t="n">
-        <v>40.7</v>
+        <v>36.6</v>
       </c>
       <c r="N40" t="n">
-        <v>5.5</v>
+        <v>5</v>
       </c>
       <c r="O40" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="P40" t="n">
-        <v>3</v>
+        <v>47</v>
       </c>
       <c r="Q40" t="n">
-        <v>-8.699999999999999</v>
+        <v>0.4</v>
       </c>
       <c r="R40" t="n">
-        <v>-0.4</v>
+        <v>1.3</v>
       </c>
       <c r="S40" t="n">
-        <v>-4.9</v>
+        <v>7.9</v>
       </c>
       <c r="T40" t="n">
         <v>-4.3</v>
@@ -3734,17 +3734,17 @@
       </c>
       <c r="W40" t="inlineStr">
         <is>
-          <t>6.6 (7g)</t>
+          <t>10.5 (6g)</t>
         </is>
       </c>
       <c r="X40" t="n">
-        <v>4.5</v>
+        <v>4.1</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Jared McCain</t>
+          <t>Nikola Topić</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3758,55 +3758,55 @@
         </is>
       </c>
       <c r="D41" t="n">
-        <v>18.5</v>
+        <v>14.5</v>
       </c>
       <c r="E41" t="n">
-        <v>11.3</v>
+        <v>5.3</v>
       </c>
       <c r="F41" t="n">
-        <v>9</v>
+        <v>3.6</v>
       </c>
       <c r="G41" t="n">
-        <v>7.1</v>
+        <v>3.8</v>
       </c>
       <c r="H41" t="n">
-        <v>9.800000000000001</v>
+        <v>3.8</v>
       </c>
       <c r="I41" t="n">
-        <v>10.1</v>
+        <v>3.8</v>
       </c>
       <c r="J41" t="n">
-        <v>14.8</v>
+        <v>13.3</v>
       </c>
       <c r="K41" t="n">
-        <v>17.4</v>
+        <v>13.3</v>
       </c>
       <c r="L41" t="n">
-        <v>43.1</v>
+        <v>33.3</v>
       </c>
       <c r="M41" t="n">
-        <v>43.2</v>
+        <v>33.3</v>
       </c>
       <c r="N41" t="n">
-        <v>5.7</v>
+        <v>4.7</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
       </c>
       <c r="P41" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>-8.4</v>
+        <v>-10.7</v>
       </c>
       <c r="R41" t="n">
-        <v>-1.1</v>
+        <v>-0.2</v>
       </c>
       <c r="S41" t="n">
-        <v>-0.1</v>
+        <v>0</v>
       </c>
       <c r="T41" t="n">
-        <v>-2.6</v>
+        <v>0</v>
       </c>
       <c r="U41" t="n">
         <v>4</v>
@@ -3816,18 +3816,18 @@
       </c>
       <c r="W41" t="inlineStr"/>
       <c r="X41" t="n">
-        <v>20.7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Jrue Holiday</t>
+          <t>Kenrich Williams</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>SAC @ POR</t>
+          <t>PHX @ OKC</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -3839,68 +3839,72 @@
         <v>15.5</v>
       </c>
       <c r="E42" t="n">
-        <v>13.7</v>
+        <v>5.7</v>
       </c>
       <c r="F42" t="n">
-        <v>19.6</v>
+        <v>6.4</v>
       </c>
       <c r="G42" t="n">
-        <v>16.5</v>
+        <v>5.2</v>
       </c>
       <c r="H42" t="n">
-        <v>16.8</v>
+        <v>5.4</v>
       </c>
       <c r="I42" t="n">
-        <v>17.5</v>
+        <v>6.8</v>
       </c>
       <c r="J42" t="n">
-        <v>31</v>
+        <v>11.2</v>
       </c>
       <c r="K42" t="n">
-        <v>30.2</v>
+        <v>15.5</v>
       </c>
       <c r="L42" t="n">
-        <v>42.3</v>
+        <v>35.8</v>
       </c>
       <c r="M42" t="n">
-        <v>46.1</v>
+        <v>40.7</v>
       </c>
       <c r="N42" t="n">
-        <v>7.7</v>
+        <v>5.5</v>
       </c>
       <c r="O42" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="P42" t="n">
-        <v>53</v>
+        <v>3</v>
       </c>
       <c r="Q42" t="n">
-        <v>2</v>
+        <v>-8.699999999999999</v>
       </c>
       <c r="R42" t="n">
-        <v>2.1</v>
+        <v>-0.4</v>
       </c>
       <c r="S42" t="n">
-        <v>-3.8</v>
+        <v>-4.9</v>
       </c>
       <c r="T42" t="n">
-        <v>0.8</v>
+        <v>-4.3</v>
       </c>
       <c r="U42" t="n">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="V42" t="n">
-        <v>15</v>
-      </c>
-      <c r="W42" t="inlineStr"/>
+        <v>20</v>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>6.6 (7g)</t>
+        </is>
+      </c>
       <c r="X42" t="n">
-        <v>-23.2</v>
+        <v>4.5</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Donovan Clingan</t>
+          <t>Jrue Holiday</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3910,41 +3914,41 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Center</t>
+          <t>Guard</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>13.5</v>
+        <v>15.5</v>
       </c>
       <c r="E43" t="n">
-        <v>15.7</v>
+        <v>13.7</v>
       </c>
       <c r="F43" t="n">
-        <v>11</v>
+        <v>19.6</v>
       </c>
       <c r="G43" t="n">
-        <v>10.6</v>
+        <v>16.5</v>
       </c>
       <c r="H43" t="n">
-        <v>13.1</v>
+        <v>16.8</v>
       </c>
       <c r="I43" t="n">
-        <v>13.7</v>
+        <v>17.5</v>
       </c>
       <c r="J43" t="n">
-        <v>26.4</v>
+        <v>31</v>
       </c>
       <c r="K43" t="n">
-        <v>27.1</v>
+        <v>30.2</v>
       </c>
       <c r="L43" t="n">
-        <v>47.4</v>
+        <v>42.3</v>
       </c>
       <c r="M43" t="n">
-        <v>51.6</v>
+        <v>46.1</v>
       </c>
       <c r="N43" t="n">
-        <v>5.9</v>
+        <v>7.7</v>
       </c>
       <c r="O43" t="n">
         <v>40</v>
@@ -3953,30 +3957,26 @@
         <v>53</v>
       </c>
       <c r="Q43" t="n">
-        <v>0.2</v>
+        <v>2</v>
       </c>
       <c r="R43" t="n">
-        <v>-2.7</v>
+        <v>2.1</v>
       </c>
       <c r="S43" t="n">
-        <v>-4.2</v>
+        <v>-3.8</v>
       </c>
       <c r="T43" t="n">
-        <v>-0.7</v>
+        <v>0.8</v>
       </c>
       <c r="U43" t="n">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="V43" t="n">
         <v>15</v>
       </c>
-      <c r="W43" t="inlineStr">
-        <is>
-          <t>9.7 (6g)</t>
-        </is>
-      </c>
+      <c r="W43" t="inlineStr"/>
       <c r="X43" t="n">
-        <v>10.7</v>
+        <v>-23.2</v>
       </c>
     </row>
     <row r="44">
@@ -3996,7 +3996,7 @@
         </is>
       </c>
       <c r="D44" t="n">
-        <v>25.5</v>
+        <v>26.5</v>
       </c>
       <c r="E44" t="n">
         <v>30</v>
@@ -4029,13 +4029,13 @@
         <v>5.5</v>
       </c>
       <c r="O44" t="n">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="P44" t="n">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="Q44" t="n">
-        <v>-2.9</v>
+        <v>-3.9</v>
       </c>
       <c r="R44" t="n">
         <v>6.2</v>
@@ -4064,7 +4064,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Scoot Henderson</t>
+          <t>Donovan Clingan</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4074,73 +4074,73 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Guard</t>
+          <t>Center</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="E45" t="n">
         <v>15.7</v>
       </c>
       <c r="F45" t="n">
-        <v>15.2</v>
+        <v>11</v>
       </c>
       <c r="G45" t="n">
-        <v>15.5</v>
+        <v>10.6</v>
       </c>
       <c r="H45" t="n">
-        <v>14.8</v>
+        <v>13.1</v>
       </c>
       <c r="I45" t="n">
-        <v>13.9</v>
+        <v>13.7</v>
       </c>
       <c r="J45" t="n">
-        <v>27.6</v>
+        <v>26.4</v>
       </c>
       <c r="K45" t="n">
-        <v>24.8</v>
+        <v>27.1</v>
       </c>
       <c r="L45" t="n">
-        <v>42.2</v>
+        <v>47.4</v>
       </c>
       <c r="M45" t="n">
-        <v>41.7</v>
+        <v>51.6</v>
       </c>
       <c r="N45" t="n">
-        <v>4.9</v>
+        <v>5.9</v>
       </c>
       <c r="O45" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="P45" t="n">
-        <v>40</v>
+        <v>53</v>
       </c>
       <c r="Q45" t="n">
-        <v>-0.6</v>
+        <v>0.2</v>
       </c>
       <c r="R45" t="n">
-        <v>1.3</v>
+        <v>-2.7</v>
       </c>
       <c r="S45" t="n">
-        <v>0.5</v>
+        <v>-4.2</v>
       </c>
       <c r="T45" t="n">
-        <v>2.8</v>
+        <v>-0.7</v>
       </c>
       <c r="U45" t="n">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="V45" t="n">
         <v>15</v>
       </c>
       <c r="W45" t="inlineStr">
         <is>
-          <t>9.7 (3g)</t>
+          <t>9.7 (6g)</t>
         </is>
       </c>
       <c r="X45" t="n">
-        <v>-3.5</v>
+        <v>10.7</v>
       </c>
     </row>
     <row r="46">
@@ -4470,7 +4470,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Precious Achiuwa</t>
+          <t>Scoot Henderson</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4480,73 +4480,73 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Forward</t>
+          <t>Guard</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>14.5</v>
+        <v>16.5</v>
       </c>
       <c r="E50" t="n">
-        <v>8.699999999999999</v>
+        <v>15.7</v>
       </c>
       <c r="F50" t="n">
-        <v>13.2</v>
+        <v>15.2</v>
       </c>
       <c r="G50" t="n">
-        <v>13.8</v>
+        <v>15.5</v>
       </c>
       <c r="H50" t="n">
-        <v>15.5</v>
+        <v>14.8</v>
       </c>
       <c r="I50" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="J50" t="n">
-        <v>29.2</v>
+        <v>27.6</v>
       </c>
       <c r="K50" t="n">
-        <v>27.4</v>
+        <v>24.8</v>
       </c>
       <c r="L50" t="n">
-        <v>52.6</v>
+        <v>42.2</v>
       </c>
       <c r="M50" t="n">
-        <v>51.8</v>
+        <v>41.7</v>
       </c>
       <c r="N50" t="n">
-        <v>6.1</v>
+        <v>4.9</v>
       </c>
       <c r="O50" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="P50" t="n">
         <v>30</v>
       </c>
       <c r="Q50" t="n">
-        <v>-1.3</v>
+        <v>-2.6</v>
       </c>
       <c r="R50" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="S50" t="n">
-        <v>0.8</v>
+        <v>0.5</v>
       </c>
       <c r="T50" t="n">
-        <v>1.9</v>
+        <v>2.8</v>
       </c>
       <c r="U50" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="V50" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="W50" t="inlineStr">
         <is>
-          <t>3.6 (5g)</t>
+          <t>9.7 (3g)</t>
         </is>
       </c>
       <c r="X50" t="n">
-        <v>-15.1</v>
+        <v>-3.5</v>
       </c>
     </row>
   </sheetData>
@@ -4631,7 +4631,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Jalen Johnson</t>
+          <t>Bam Adebayo</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -4641,7 +4641,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>OVER</t>
+          <t>UNDER</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -4650,7 +4650,7 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>0.536</v>
+        <v>0.592</v>
       </c>
       <c r="F2" t="n">
         <v>5</v>
@@ -4659,27 +4659,27 @@
         <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>23.4</v>
+        <v>18</v>
       </c>
       <c r="I2" t="n">
-        <v>0.9</v>
+        <v>3.5</v>
       </c>
       <c r="J2" t="n">
-        <v>1.893</v>
+        <v>1.877</v>
       </c>
       <c r="K2" t="n">
-        <v>1.87</v>
+        <v>1.877</v>
       </c>
       <c r="L2" s="2" t="inlineStr">
         <is>
-          <t>Recent scoring trending down 4.2 pts (L5 vs L30) — marginally supports the OVER. H2H avg 2.6 pts above season L30. Opponent is weak defense (#23) at fast pace (#4). Mixed signals: 5/10 agree (Context, Defense, H2H); counter-signals: Volume, HR L30, HR L10. Projection model targets 23.4 pts (0.9 pts above line; 53% blended confidence [T3]). Risk: L3 has dropped to 17.0 (4.6 below L30) — deepening slump makes the over vulnerable.</t>
+          <t>Adebayo averages 16.0 pts in 6 meetings (-5.5 vs line) — marginally supports the UNDER. H2H avg 6.7 pts below season L30; FG% -4.6% trending (L10 vs L30). Opponent is below-average defense (#17) at above-average pace (#8). Mixed signals: 5/10 agree (HR L30, HR L10, Trend); counter-signals: Volume, Context, Defense. Projection model targets 18.0 pts (3.5 pts below line; 59% blended confidence [T3]).</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Nickeil Alexander-Walker</t>
+          <t>Jalen Johnson</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -4689,7 +4689,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>UNDER</t>
+          <t>OVER</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -4698,29 +4698,29 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>0.54</v>
+        <v>0.536</v>
       </c>
       <c r="F3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>23.1</v>
+        <v>23.4</v>
       </c>
       <c r="I3" t="n">
-        <v>1.4</v>
+        <v>0.9</v>
       </c>
       <c r="J3" t="n">
-        <v>2.15</v>
+        <v>1.893</v>
       </c>
       <c r="K3" t="n">
-        <v>1.671</v>
+        <v>1.87</v>
       </c>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>Alexander-Walker averages 15.6 pts in 5 meetings (-8.9 vs line) — marginally supports the UNDER. H2H avg 6.0 pts below season L30; TS% shifts -3.9% in this matchup. Opponent is below-average defense (#22) at fast pace (#4). Mixed signals: 4/10 agree (Volume, HR L30, Context); counter-signals: HR L10, Trend, Defense. Projection model targets 23.1 pts (1.4 pts below line; 53% blended confidence [T3]). Risk: L3 has surged to 26.3 after a 15-pt outing (4.7 above L30) — momentum could push over the under line.</t>
+          <t>Recent scoring trending down 4.2 pts (L5 vs L30) — marginally supports the OVER. H2H avg 2.6 pts above season L30. Opponent is weak defense (#23) at fast pace (#4). Mixed signals: 5/10 agree (Context, Defense, H2H); counter-signals: Volume, HR L30, HR L10. Projection model targets 23.4 pts (0.9 pts above line; 53% blended confidence [T3]). Risk: L3 has dropped to 17.0 (4.6 below L30) — deepening slump makes the over vulnerable.</t>
         </is>
       </c>
     </row>
@@ -4761,10 +4761,10 @@
         <v>1</v>
       </c>
       <c r="J4" t="n">
-        <v>1.943</v>
+        <v>1.99</v>
       </c>
       <c r="K4" t="n">
-        <v>1.82</v>
+        <v>1.781</v>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
@@ -4809,10 +4809,10 @@
         <v>3.1</v>
       </c>
       <c r="J5" t="n">
-        <v>1.98</v>
+        <v>1.909</v>
       </c>
       <c r="K5" t="n">
-        <v>1.787</v>
+        <v>1.847</v>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
@@ -4823,7 +4823,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Bam Adebayo</t>
+          <t>Nickeil Alexander-Walker</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -4833,45 +4833,45 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>UNDER</t>
+          <t>OVER</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>T2</t>
+          <t>T3</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>0.663</v>
+        <v>0.525</v>
       </c>
       <c r="F6" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>17.9</v>
+        <v>23.1</v>
       </c>
       <c r="I6" t="n">
-        <v>5.6</v>
+        <v>0.6</v>
       </c>
       <c r="J6" t="n">
-        <v>1.952</v>
+        <v>1.862</v>
       </c>
       <c r="K6" t="n">
-        <v>1.813</v>
+        <v>1.901</v>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>Adebayo averages 16.0 pts in 6 meetings (-7.5 vs line) — supports the UNDER. H2H avg 6.7 pts below season L30; FG% -4.6% trending (L10 vs L30). Opponent is below-average defense (#17) at above-average pace (#8). 7/10 signals agree — Volume, HR L30, HR L10, Trend support the UNDER; Defense, Pace, Min Trend dissent. Projection model targets 17.9 pts (5.6 pts below line; 66% blended confidence [T2]).</t>
+          <t>Alexander-Walker averages 15.6 pts in 5 meetings (-6.9 vs line) — supports the OVER. H2H avg 6.0 pts below season L30; TS% shifts -3.9% in this matchup. Opponent is below-average defense (#22) at fast pace (#4). 6/10 signals agree — Trend, Context, Defense, Pace support the OVER; Volume, HR L30, HR L10 dissent. Projection model targets 23.1 pts (0.6 pts above line; 52% blended confidence [T3]). Risk: only 37% hit rate over L30 suggests the line may be set fairly.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Andrew Wiggins</t>
+          <t>Dyson Daniels</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -4890,41 +4890,41 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>0.607</v>
+        <v>0.602</v>
       </c>
       <c r="F7" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
       </c>
       <c r="H7" t="n">
-        <v>15.6</v>
+        <v>8.4</v>
       </c>
       <c r="I7" t="n">
-        <v>2.9</v>
+        <v>4.1</v>
       </c>
       <c r="J7" t="n">
-        <v>1.98</v>
+        <v>1.877</v>
       </c>
       <c r="K7" t="n">
-        <v>1.787</v>
+        <v>1.877</v>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>Wiggins's L30 of 15.2 pts sits 3.3 below the 18.5 line — supports the UNDER. H2H avg 3.5 pts above season L30; TS% shifts +3.1% in this matchup. Opponent is weak defense (#24) at above-average pace (#8). 6/10 signals agree — Volume, HR L30, HR L10, Trend support the UNDER; Defense, H2H, Pace dissent. Projection model targets 15.6 pts (2.9 pts below line; 60% blended confidence [T3]).</t>
+          <t>Daniels averages 8.5 pts in 6 meetings (-4.0 vs line) — marginally supports the UNDER. H2H avg 3.5 pts below season L30; TS% shifts -3.6% in this matchup. Opponent is below-average defense (#22) at fast pace (#4). Mixed signals: 4/10 agree (Volume, HR L30, Context); counter-signals: HR L10, Trend, Defense. Projection model targets 8.4 pts (4.1 pts below line; 60% blended confidence [T3]).</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Paolo Banchero</t>
+          <t>Onyeka Okongwu</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>ORL @ BOS</t>
+          <t>ATL @ MIA</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -4934,88 +4934,88 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>T3</t>
+          <t>T2</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>0.57</v>
+        <v>0.5620000000000001</v>
       </c>
       <c r="F8" t="n">
         <v>6</v>
       </c>
       <c r="G8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H8" t="n">
-        <v>17.4</v>
+        <v>13.4</v>
       </c>
       <c r="I8" t="n">
-        <v>3.1</v>
+        <v>2.1</v>
       </c>
       <c r="J8" t="n">
-        <v>1.943</v>
+        <v>1.877</v>
       </c>
       <c r="K8" t="n">
-        <v>1.82</v>
+        <v>1.877</v>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>Recent scoring trending down 3.3 pts (L5 vs L30) — supports the UNDER. H2H avg 3.1 pts below season L30. Opponent is elite defense (#2) at slow pace (#24). 6/10 signals agree — HR L10, Trend, Defense, H2H support the UNDER; Volume, HR L30, Context dissent. Projection model targets 17.4 pts (3.1 pts below line; 57% blended confidence [T3]). Risk: high variance (σ=9.6) makes the outcome difficult to call with confidence.</t>
+          <t>Okongwu's L30 average of 13.8 pts vs the 15.5 line — supports the UNDER. H2H avg 2.0 pts above season L30; TS% shifts -3.5% in this matchup. Opponent is weak defense (#23) at fast pace (#4). 6/10 signals agree — Volume, HR L30, HR L10, Trend support the UNDER; Defense, H2H, Pace dissent. Projection model targets 13.4 pts (2.1 pts below line; 56% blended confidence [T2]).</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Desmond Bane</t>
+          <t>Andrew Wiggins</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>ORL @ BOS</t>
+          <t>ATL @ MIA</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>UNDER</t>
+          <t>LEAN UNDER</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>T2</t>
+          <t>T3_LEAN</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>0.647</v>
+        <v>0.51</v>
       </c>
       <c r="F9" t="n">
         <v>6</v>
       </c>
       <c r="G9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H9" t="n">
-        <v>14.2</v>
+        <v>15.2</v>
       </c>
       <c r="I9" t="n">
-        <v>5.3</v>
+        <v>0.3</v>
       </c>
       <c r="J9" t="n">
-        <v>1.98</v>
+        <v>1.877</v>
       </c>
       <c r="K9" t="n">
-        <v>1.787</v>
+        <v>1.877</v>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>Bane averages 15.0 pts in 5 meetings (-4.5 vs line) — supports the UNDER. H2H avg 6.8 pts below season L30; TS% shifts -3.2% in this matchup. Opponent is elite defense (#2) at slow pace (#24). 6/10 signals agree — Trend, Defense, H2H, Pace support the UNDER; Volume, HR L30, HR L10 dissent. Projection model targets 14.2 pts (5.3 pts below line; 64% blended confidence [T2]). Risk: high variance (σ=7.5) makes the outcome difficult to call with confidence.</t>
+          <t>[Low conviction — lean only] Wiggins averages 18.7 pts in 6 meetings (+3.2 vs line) — supports the lean UNDER. H2H avg 3.5 pts above season L30; TS% shifts +3.1% in this matchup. Opponent is weak defense (#24) at above-average pace (#8). 6/10 signals agree — Volume, HR L30, HR L10, Trend support the UNDER; Defense, H2H, Pace dissent. Projection model targets 15.2 pts (0.3 pts below line; 50% blended confidence [T3_LEAN]).</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Wendell Carter Jr.</t>
+          <t>Paolo Banchero</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -5025,7 +5025,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>OVER</t>
+          <t>UNDER</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -5034,7 +5034,7 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>0.545</v>
+        <v>0.57</v>
       </c>
       <c r="F10" t="n">
         <v>6</v>
@@ -5043,32 +5043,32 @@
         <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>12.7</v>
+        <v>17.4</v>
       </c>
       <c r="I10" t="n">
-        <v>1.2</v>
+        <v>3.1</v>
       </c>
       <c r="J10" t="n">
-        <v>1.926</v>
+        <v>1.87</v>
       </c>
       <c r="K10" t="n">
-        <v>1.833</v>
+        <v>1.87</v>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>Jr.'s L30 average of 11.7 pts vs the 11.5 line — supports the OVER. Opponent is elite defense (#1) at slow pace (#24). 6/10 signals agree — Volume, HR L10, Trend, Context support the OVER; HR L30, Defense, Pace dissent. Projection model targets 12.7 pts (1.2 pts above line; 54% blended confidence [T3]).</t>
+          <t>Recent scoring trending down 3.3 pts (L5 vs L30) — supports the UNDER. H2H avg 3.1 pts below season L30. Opponent is elite defense (#2) at slow pace (#24). 6/10 signals agree — HR L10, Trend, Defense, H2H support the UNDER; Volume, HR L30, Context dissent. Projection model targets 17.4 pts (3.1 pts below line; 57% blended confidence [T3]). Risk: high variance (σ=9.6) makes the outcome difficult to call with confidence.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Immanuel Quickley</t>
+          <t>Wendell Carter Jr.</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>BKN @ TOR</t>
+          <t>ORL @ BOS</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -5078,45 +5078,45 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>T3</t>
+          <t>T2</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>0.537</v>
+        <v>0.555</v>
       </c>
       <c r="F11" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="G11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H11" t="n">
-        <v>15.6</v>
+        <v>12.7</v>
       </c>
       <c r="I11" t="n">
-        <v>1.1</v>
+        <v>2.2</v>
       </c>
       <c r="J11" t="n">
-        <v>2.07</v>
+        <v>1.87</v>
       </c>
       <c r="K11" t="n">
-        <v>1.719</v>
+        <v>1.87</v>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>Recent scoring trending down 6.8 pts (L5 vs L30) — marginally supports the OVER. H2H avg 2.0 pts above season L30; FG% -8.6% trending (L10 vs L30). Opponent is below-average defense (#18) at slow pace (#30). Mixed signals: 5/10 agree (Volume, HR L30, Context); counter-signals: HR L10, Trend, Pace. Projection model targets 15.6 pts (1.1 pts above line; 53% blended confidence [T3]). Risk: L3 has dropped to 8.3 (8.5 below L30) — deepening slump makes the over vulnerable.</t>
+          <t>Jr. averages 12.8 pts in 5 meetings (+2.3 vs line) — supports the OVER. Opponent is elite defense (#1) at slow pace (#24). 7/10 signals agree — Volume, HR L30, HR L10, Trend support the OVER; Defense, Pace, Min Trend dissent. Projection model targets 12.7 pts (2.2 pts above line; 55% blended confidence [T2]).</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Scottie Barnes</t>
+          <t>Jalen Suggs</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>BKN @ TOR</t>
+          <t>ORL @ BOS</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -5130,94 +5130,94 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>0.6870000000000001</v>
+        <v>0.542</v>
       </c>
       <c r="F12" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
       </c>
       <c r="H12" t="n">
-        <v>13.9</v>
+        <v>10.8</v>
       </c>
       <c r="I12" t="n">
-        <v>5.6</v>
+        <v>1.7</v>
       </c>
       <c r="J12" t="n">
-        <v>2.03</v>
+        <v>1.952</v>
       </c>
       <c r="K12" t="n">
-        <v>1.752</v>
+        <v>1.8</v>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>Barnes's L30 of 15.9 pts sits 3.6 below the 19.5 line — supports the UNDER. TS% shifts +3.8% in this matchup. Opponent is below-average defense (#20) at slow pace (#30). 9/10 signals agree — Volume, HR L30, HR L10, Trend support the UNDER; Defense dissents. Projection model targets 13.9 pts (5.6 pts below line; 68% blended confidence [T3]).</t>
+          <t>Suggs averages 16.7 pts in 3 meetings (+4.2 vs line) — marginally supports the UNDER. H2H avg 3.8 pts above season L30; TS% shifts +17.0% in this matchup. Opponent is elite defense (#2) at slow pace (#24). Mixed signals: 4/10 agree (HR L10, Context, Defense); counter-signals: Volume, HR L30, Trend. Projection model targets 10.8 pts (1.7 pts below line; 54% blended confidence [T3]).</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Brandon Ingram</t>
+          <t>Desmond Bane</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>BKN @ TOR</t>
+          <t>ORL @ BOS</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>LEAN UNDER</t>
+          <t>UNDER</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>T3_LEAN</t>
+          <t>T2</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>0.493</v>
+        <v>0.581</v>
       </c>
       <c r="F13" t="n">
         <v>6</v>
       </c>
       <c r="G13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H13" t="n">
-        <v>20.6</v>
+        <v>14.2</v>
       </c>
       <c r="I13" t="n">
-        <v>0.1</v>
+        <v>3.3</v>
       </c>
       <c r="J13" t="n">
-        <v>1.99</v>
+        <v>1.741</v>
       </c>
       <c r="K13" t="n">
-        <v>1.781</v>
+        <v>2</v>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>[Low conviction — lean only] Ingram's L30 average of 21.3 pts vs the 20.5 line — supports the lean UNDER. TS% shifts -7.1% in this matchup. Opponent is below-average defense (#20) at slow pace (#30). 6/10 signals agree — HR L30, HR L10, Context, Pace support the UNDER; Volume, Trend, Defense dissent. Projection model targets 20.6 pts (0.1 pts above line; 49% blended confidence [T3_LEAN]). Risk: L3 has surged to 25.7 after a 20-pt outing (4.4 above L30) — momentum could push over the under line.</t>
+          <t>Bane's L30 of 21.8 pts sits 4.3 above the 17.5 line — supports the UNDER. H2H avg 6.8 pts below season L30; TS% shifts -3.2% in this matchup. Opponent is elite defense (#2) at slow pace (#24). 6/10 signals agree — Trend, Defense, H2H, Pace support the UNDER; Volume, HR L30, HR L10 dissent. Projection model targets 14.2 pts (3.3 pts below line; 58% blended confidence [T2]). Risk: high variance (σ=7.5) makes the outcome difficult to call with confidence.</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>LaMelo Ball</t>
+          <t>Franz Wagner</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>CHA @ NYK</t>
+          <t>ORL @ BOS</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>OVER</t>
+          <t>UNDER</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -5226,94 +5226,94 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>0.525</v>
+        <v>0.5679999999999999</v>
       </c>
       <c r="F14" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
       </c>
       <c r="H14" t="n">
-        <v>23</v>
+        <v>14.3</v>
       </c>
       <c r="I14" t="n">
-        <v>0.5</v>
+        <v>2.2</v>
       </c>
       <c r="J14" t="n">
-        <v>1.971</v>
+        <v>1.8</v>
       </c>
       <c r="K14" t="n">
-        <v>1.8</v>
+        <v>1.952</v>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>Recent scoring trending up 4.8 pts (L5 vs L30) — marginally supports the OVER. H2H avg 1.6 pts above season L30. Opponent is elite defense (#4) at slow pace (#26). Mixed signals: 4/10 agree (Trend, H2H, FG Trend); counter-signals: Volume, HR L30, HR L10. Projection model targets 23.0 pts (0.5 pts above line; 52% blended confidence [T3]). Risk: high variance (σ=7.7) makes the outcome difficult to call with confidence.</t>
+          <t>Wagner averages 21.2 pts in 4 meetings (+4.7 vs line) — marginally supports the UNDER. Minutes down 9.6 recently (L10=20.0 vs L30=29.6). Opponent is elite defense (#2) at slow pace (#24). Mixed signals: 5/10 agree (HR L10, Trend, Defense); counter-signals: Volume, HR L30, Context. Projection model targets 14.3 pts (2.2 pts below line; 56% blended confidence [T3]). Risk: 77% over-rate on L30 suggests scoring tendency that could threaten the under.</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Miles Bridges</t>
+          <t>Immanuel Quickley</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>CHA @ NYK</t>
+          <t>BKN @ TOR</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>UNDER</t>
+          <t>OVER</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>T2</t>
+          <t>T3</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>0.577</v>
+        <v>0.537</v>
       </c>
       <c r="F15" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H15" t="n">
-        <v>11.5</v>
+        <v>15.6</v>
       </c>
       <c r="I15" t="n">
-        <v>3</v>
+        <v>1.1</v>
       </c>
       <c r="J15" t="n">
-        <v>1.82</v>
+        <v>2.04</v>
       </c>
       <c r="K15" t="n">
-        <v>1.943</v>
+        <v>1.741</v>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>Recent scoring trending up 3.3 pts (L5 vs L30) — supports the UNDER. TS% shifts -11.2% in this matchup; FG% +5.8% trending (L10 vs L30). Opponent is strong defense (#8) at slow pace (#26). 6/10 signals agree — HR L30, Context, Defense, H2H support the UNDER; Volume, HR L10, Trend dissent. Projection model targets 11.5 pts (3.0 pts below line; 57% blended confidence [T2]).</t>
+          <t>Recent scoring trending down 6.8 pts (L5 vs L30) — marginally supports the OVER. H2H avg 2.0 pts above season L30; FG% -8.6% trending (L10 vs L30). Opponent is below-average defense (#18) at slow pace (#30). Mixed signals: 5/10 agree (Volume, HR L30, Context); counter-signals: HR L10, Trend, Pace. Projection model targets 15.6 pts (1.1 pts above line; 53% blended confidence [T3]). Risk: L3 has dropped to 8.3 (8.5 below L30) — deepening slump makes the over vulnerable.</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Brandon Miller</t>
+          <t>Brandon Ingram</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>CHA @ NYK</t>
+          <t>BKN @ TOR</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>UNDER</t>
+          <t>OVER</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -5322,41 +5322,41 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>0.545</v>
+        <v>0.52</v>
       </c>
       <c r="F16" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>19.3</v>
+        <v>20.6</v>
       </c>
       <c r="I16" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="J16" t="n">
-        <v>1.917</v>
+        <v>1.641</v>
       </c>
       <c r="K16" t="n">
-        <v>1.84</v>
+        <v>2.21</v>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>Recent scoring trending down 2.1 pts (L5 vs L30) — supports the UNDER. H2H avg 1.5 pts above season L30. Opponent is strong defense (#8) at slow pace (#26). 6/10 signals agree — Volume, Trend, Context, Defense support the UNDER; HR L30, HR L10, H2H dissent. Projection model targets 19.3 pts (1.2 pts below line; 54% blended confidence [T3]).</t>
+          <t>Ingram's L30 average of 21.3 pts vs the 19.5 line — marginally supports the OVER. TS% shifts -7.1% in this matchup. Opponent is below-average defense (#20) at slow pace (#30). Mixed signals: 5/10 agree (Volume, Trend, Context); counter-signals: HR L30, HR L10, Pace. Projection model targets 20.6 pts (1.1 pts above line; 52% blended confidence [T3]). Risk: high variance (σ=8.3) makes the outcome difficult to call with confidence.</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Moussa Diabaté</t>
+          <t>Scottie Barnes</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>CHA @ NYK</t>
+          <t>BKN @ TOR</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -5370,36 +5370,36 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>0.536</v>
+        <v>0.592</v>
       </c>
       <c r="F17" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>6.2</v>
+        <v>13.5</v>
       </c>
       <c r="I17" t="n">
-        <v>1.3</v>
+        <v>3</v>
       </c>
       <c r="J17" t="n">
-        <v>1.769</v>
+        <v>1.8</v>
       </c>
       <c r="K17" t="n">
-        <v>2</v>
+        <v>1.971</v>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>Diabaté averages 4.2 pts in 6 meetings (-3.3 vs line) — supports the UNDER. H2H avg 3.5 pts below season L30; FG% +11.2% trending (L10 vs L30). Opponent is strong defense (#8) at slow pace (#26). 6/10 signals agree — Trend, Context, Defense, H2H support the UNDER; Volume, HR L30, HR L10 dissent. Projection model targets 6.2 pts (1.3 pts below line; 53% blended confidence [T3]).</t>
+          <t>Barnes's L30 average of 15.9 pts vs the 16.5 line — supports the UNDER. TS% shifts +3.8% in this matchup. Opponent is below-average defense (#20) at slow pace (#30). 8/10 signals agree — Volume, HR L30, HR L10, Trend support the UNDER; Defense, H2H dissent. Projection model targets 13.5 pts (3.0 pts below line; 59% blended confidence [T3]).</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Kon Knueppel</t>
+          <t>LaMelo Ball</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -5409,50 +5409,50 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>UNDER</t>
+          <t>OVER</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>T1</t>
+          <t>T3</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>0.642</v>
+        <v>0.525</v>
       </c>
       <c r="F18" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="G18" t="n">
+        <v>0</v>
+      </c>
+      <c r="H18" t="n">
+        <v>23</v>
+      </c>
+      <c r="I18" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J18" t="n">
         <v>2</v>
       </c>
-      <c r="H18" t="n">
-        <v>12.9</v>
-      </c>
-      <c r="I18" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="J18" t="n">
-        <v>1.952</v>
-      </c>
       <c r="K18" t="n">
-        <v>1.813</v>
+        <v>1.769</v>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>Recent scoring trending down 3.5 pts (L5 vs L30) — supports the UNDER. H2H avg 3.3 pts below season L30; TS% shifts -14.5% in this matchup. Opponent is elite defense (#4) at slow pace (#26). 7/10 signals agree — HR L10, Trend, Context, Defense support the UNDER; Volume, HR L30, Min Trend dissent. Projection model targets 12.9 pts (4.6 pts below line; 64% blended confidence [T1]).</t>
+          <t>Recent scoring trending up 4.8 pts (L5 vs L30) — marginally supports the OVER. H2H avg 1.6 pts above season L30. Opponent is elite defense (#4) at slow pace (#26). Mixed signals: 4/10 agree (Trend, H2H, FG Trend); counter-signals: Volume, HR L30, HR L10. Projection model targets 23.0 pts (0.5 pts above line; 52% blended confidence [T3]). Risk: high variance (σ=7.7) makes the outcome difficult to call with confidence.</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Quenton Jackson</t>
+          <t>Miles Bridges</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>DET @ IND</t>
+          <t>CHA @ NYK</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -5462,45 +5462,45 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>T1</t>
+          <t>T2</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>0.645</v>
+        <v>0.577</v>
       </c>
       <c r="F19" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G19" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H19" t="n">
-        <v>10.3</v>
+        <v>11.5</v>
       </c>
       <c r="I19" t="n">
-        <v>4.2</v>
+        <v>3</v>
       </c>
       <c r="J19" t="n">
-        <v>1.877</v>
+        <v>1.862</v>
       </c>
       <c r="K19" t="n">
-        <v>1.877</v>
+        <v>1.901</v>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>Jackson's L30 of 9.8 pts sits 4.7 below the 14.5 line — supports the UNDER. Opponent is elite defense (#4) at slow pace (#22). 7/10 signals agree — Volume, HR L30, HR L10, Context support the UNDER; Trend, H2H, Min Trend dissent. Projection model targets 10.3 pts (4.2 pts below line; 64% blended confidence [T1]).</t>
+          <t>Recent scoring trending up 3.3 pts (L5 vs L30) — supports the UNDER. TS% shifts -11.2% in this matchup; FG% +5.8% trending (L10 vs L30). Opponent is strong defense (#8) at slow pace (#26). 6/10 signals agree — HR L30, Context, Defense, H2H support the UNDER; Volume, HR L10, Trend dissent. Projection model targets 11.5 pts (3.0 pts below line; 57% blended confidence [T2]).</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Ausar Thompson</t>
+          <t>Kon Knueppel</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>DET @ IND</t>
+          <t>CHA @ NYK</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -5510,88 +5510,88 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>T3</t>
+          <t>T1</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>0.58</v>
+        <v>0.642</v>
       </c>
       <c r="F20" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="G20" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H20" t="n">
-        <v>6.7</v>
+        <v>12.9</v>
       </c>
       <c r="I20" t="n">
-        <v>2.8</v>
+        <v>4.6</v>
       </c>
       <c r="J20" t="n">
-        <v>2.07</v>
+        <v>1.847</v>
       </c>
       <c r="K20" t="n">
-        <v>1.719</v>
+        <v>1.909</v>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>Low scoring variance (σ=4.0) — highly predictable output near line — marginally supports the UNDER. FG% +10.6% trending (L10 vs L30). Opponent is below-average defense (#22) at above-average pace (#11). Mixed signals: 4/10 agree (Volume, HR L30, Context); counter-signals: HR L10, Trend, Defense. Projection model targets 6.7 pts (2.8 pts below line; 57% blended confidence [T3]).</t>
+          <t>Recent scoring trending down 3.5 pts (L5 vs L30) — supports the UNDER. H2H avg 3.3 pts below season L30; TS% shifts -14.5% in this matchup. Opponent is elite defense (#4) at slow pace (#26). 7/10 signals agree — HR L10, Trend, Context, Defense support the UNDER; Volume, HR L30, Min Trend dissent. Projection model targets 12.9 pts (4.6 pts below line; 64% blended confidence [T1]).</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Cade Cunningham</t>
+          <t>Brandon Miller</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>DET @ IND</t>
+          <t>CHA @ NYK</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>UNDER</t>
+          <t>LEAN UNDER</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>T3</t>
+          <t>T3_LEAN</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>0.5669999999999999</v>
+        <v>0.504</v>
       </c>
       <c r="F21" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>16.6</v>
+        <v>19.6</v>
       </c>
       <c r="I21" t="n">
-        <v>2.9</v>
+        <v>0.1</v>
       </c>
       <c r="J21" t="n">
+        <v>1.787</v>
+      </c>
+      <c r="K21" t="n">
         <v>1.98</v>
       </c>
-      <c r="K21" t="n">
-        <v>1.787</v>
-      </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>Recent scoring trending down 4.8 pts (L5 vs L30) — marginally supports the UNDER. H2H avg 2.6 pts above season L30; FG% +4.5% trending (L10 vs L30). Opponent is below-average defense (#22) at above-average pace (#11). Mixed signals: 3/10 agree (HR L10, Trend, Min Trend); counter-signals: Volume, HR L30, Context. Projection model targets 16.6 pts (2.9 pts below line; 56% blended confidence [T3]). Risk: high variance (σ=8.9) makes the outcome difficult to call with confidence.</t>
+          <t>[Low conviction — lean only] Recent scoring trending down 2.1 pts (L5 vs L30) — marginally supports the lean UNDER. H2H avg 1.5 pts above season L30. Opponent is strong defense (#8) at slow pace (#26). Mixed signals: 5/10 agree (Trend, Context, Defense); counter-signals: Volume, HR L30, HR L10. Projection model targets 19.6 pts (0.1 pts above line; 50% blended confidence [T3_LEAN]).</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Tobias Harris</t>
+          <t>Jarace Walker</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -5601,45 +5601,45 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>LEAN OVER</t>
+          <t>UNDER</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>T3_LEAN</t>
+          <t>T3</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>0.541</v>
+        <v>0.6860000000000001</v>
       </c>
       <c r="F22" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>10.4</v>
+        <v>14.8</v>
       </c>
       <c r="I22" t="n">
-        <v>0.1</v>
+        <v>4.7</v>
       </c>
       <c r="J22" t="n">
-        <v>2.06</v>
+        <v>2.07</v>
       </c>
       <c r="K22" t="n">
-        <v>1.73</v>
+        <v>1.699</v>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>[Low conviction — lean only] Harris averages 12.8 pts in 6 meetings (+2.3 vs line) — supports the lean OVER. FG% +8.7% trending (L10 vs L30). Opponent is below-average defense (#20) at above-average pace (#11). 8/10 signals agree — Volume, HR L30, HR L10, Context support the OVER; Trend, Min Trend dissent. Projection model targets 10.4 pts (0.1 pts below line; 54% blended confidence [T3_LEAN]).</t>
+          <t>Walker averages 9.4 pts in 7 meetings (-10.1 vs line) — supports the UNDER. H2H avg 5.3 pts below season L30; TS% shifts +13.1% in this matchup. Opponent is average defense (#14) at slow pace (#22). 9/10 signals agree — Volume, HR L30, HR L10, Trend support the UNDER; FG Trend dissents. Projection model targets 14.8 pts (4.7 pts below line; 68% blended confidence [T3]).</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Micah Potter</t>
+          <t>Quenton Jackson</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -5654,40 +5654,40 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>T3</t>
+          <t>T1</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>0.75</v>
+        <v>0.645</v>
       </c>
       <c r="F23" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="G23" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H23" t="n">
-        <v>3.1</v>
+        <v>10.3</v>
       </c>
       <c r="I23" t="n">
-        <v>9.4</v>
+        <v>4.2</v>
       </c>
       <c r="J23" t="n">
-        <v>1.813</v>
+        <v>1.877</v>
       </c>
       <c r="K23" t="n">
-        <v>1.952</v>
+        <v>1.877</v>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>Recent scoring trending up 2.3 pts (L5 vs L30) — marginally supports the UNDER. Opponent is elite defense (#5) at slow pace (#22). Mixed signals: 5/10 agree (Volume, HR L30, Context); counter-signals: HR L10, Trend, H2H. Projection model targets 3.1 pts (9.4 pts below line; 75% blended confidence [T3]).</t>
+          <t>Jackson's L30 of 9.8 pts sits 4.7 below the 14.5 line — supports the UNDER. Opponent is elite defense (#4) at slow pace (#22). 7/10 signals agree — Volume, HR L30, HR L10, Context support the UNDER; Trend, H2H, Min Trend dissent. Projection model targets 10.3 pts (4.2 pts below line; 64% blended confidence [T1]).</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Jarace Walker</t>
+          <t>Ausar Thompson</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -5706,84 +5706,84 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>0.6860000000000001</v>
+        <v>0.58</v>
       </c>
       <c r="F24" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>14.8</v>
+        <v>6.7</v>
       </c>
       <c r="I24" t="n">
-        <v>4.7</v>
+        <v>2.8</v>
       </c>
       <c r="J24" t="n">
-        <v>2.1</v>
+        <v>2.09</v>
       </c>
       <c r="K24" t="n">
-        <v>1.699</v>
+        <v>1.709</v>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>Walker averages 9.4 pts in 7 meetings (-10.1 vs line) — supports the UNDER. H2H avg 5.3 pts below season L30; TS% shifts +13.1% in this matchup. Opponent is average defense (#14) at slow pace (#22). 9/10 signals agree — Volume, HR L30, HR L10, Trend support the UNDER; FG Trend dissents. Projection model targets 14.8 pts (4.7 pts below line; 68% blended confidence [T3]).</t>
+          <t>Low scoring variance (σ=4.0) — highly predictable output near line — marginally supports the UNDER. FG% +10.6% trending (L10 vs L30). Opponent is below-average defense (#22) at above-average pace (#11). Mixed signals: 4/10 agree (Volume, HR L30, Context); counter-signals: HR L10, Trend, Defense. Projection model targets 6.7 pts (2.8 pts below line; 57% blended confidence [T3]).</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Tyrese Maxey</t>
+          <t>Micah Potter</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>MIL @ PHI</t>
+          <t>DET @ IND</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>LEAN UNDER</t>
+          <t>UNDER</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>T3_LEAN</t>
+          <t>T2</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>0.524</v>
+        <v>0.781</v>
       </c>
       <c r="F25" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H25" t="n">
-        <v>28.6</v>
+        <v>3.1</v>
       </c>
       <c r="I25" t="n">
-        <v>0.1</v>
+        <v>10.4</v>
       </c>
       <c r="J25" t="n">
-        <v>1.952</v>
+        <v>1.98</v>
       </c>
       <c r="K25" t="n">
-        <v>1.813</v>
+        <v>1.787</v>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>[Low conviction — lean only] Recent scoring trending down 3.2 pts (L5 vs L30) — marginally supports the lean UNDER. H2H avg 5.5 pts above season L30; TS% shifts +3.0% in this matchup. Opponent is weak defense (#24) at moderate pace (#14). Mixed signals: 5/10 agree (Volume, HR L30, HR L10); counter-signals: Defense, H2H, Pace. Projection model targets 28.6 pts (0.1 pts above line; 52% blended confidence [T3_LEAN]).</t>
+          <t>Potter's L30 of 11.1 pts sits 2.4 below the 13.5 line — supports the UNDER. Opponent is elite defense (#5) at slow pace (#22). 6/10 signals agree — Volume, HR L30, HR L10, Context support the UNDER; Trend, H2H, FG Trend dissent. Projection model targets 3.1 pts (10.4 pts below line; 78% blended confidence [T2]).</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>AJ Green</t>
+          <t>Tyrese Maxey</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -5793,45 +5793,45 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>UNDER</t>
+          <t>LEAN UNDER</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>T3</t>
+          <t>T3_LEAN</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>0.762</v>
+        <v>0.524</v>
       </c>
       <c r="F26" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>9.5</v>
+        <v>28.6</v>
       </c>
       <c r="I26" t="n">
-        <v>10</v>
+        <v>0.1</v>
       </c>
       <c r="J26" t="n">
-        <v>2.12</v>
+        <v>2.03</v>
       </c>
       <c r="K26" t="n">
-        <v>1.69</v>
+        <v>1.752</v>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>Green averages 6.7 pts in 6 meetings (-12.8 vs line) — supports the UNDER. H2H avg 3.0 pts below season L30; TS% shifts +10.1% in this matchup. Opponent is below-average defense (#16) at moderate pace (#18). 6/10 signals agree — Volume, HR L30, HR L10, Context support the UNDER; Trend, Defense, FG Trend dissent. Projection model targets 9.5 pts (10.0 pts below line; 76% blended confidence [T3]). Risk: L3 has surged to 22.7 after a 7-pt outing (13.0 above L30) — momentum could push over the under line.</t>
+          <t>[Low conviction — lean only] Recent scoring trending down 3.2 pts (L5 vs L30) — marginally supports the lean UNDER. H2H avg 5.5 pts above season L30; TS% shifts +3.0% in this matchup. Opponent is weak defense (#24) at moderate pace (#14). Mixed signals: 5/10 agree (Volume, HR L30, HR L10); counter-signals: Defense, H2H, Pace. Projection model targets 28.6 pts (0.1 pts above line; 52% blended confidence [T3_LEAN]).</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Paul George</t>
+          <t>AJ Green</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -5841,7 +5841,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>OVER</t>
+          <t>UNDER</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -5850,36 +5850,36 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>0.508</v>
+        <v>0.762</v>
       </c>
       <c r="F27" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>20.2</v>
+        <v>9.5</v>
       </c>
       <c r="I27" t="n">
-        <v>0.7</v>
+        <v>10</v>
       </c>
       <c r="J27" t="n">
-        <v>1.901</v>
+        <v>2.12</v>
       </c>
       <c r="K27" t="n">
-        <v>1.862</v>
+        <v>1.69</v>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>George's L30 average of 18.3 pts vs the 19.5 line — marginally supports the OVER. H2H avg 2.9 pts above season L30; TS% shifts +14.8% in this matchup. Opponent is weak defense (#23) at moderate pace (#14). Mixed signals: 5/10 agree (HR L10, Defense, H2H); counter-signals: Volume, HR L30, Trend. Projection model targets 20.2 pts (0.7 pts above line; 50% blended confidence [T3]). Risk: high variance (σ=8.6) makes the outcome difficult to call with confidence.</t>
+          <t>Green averages 6.7 pts in 6 meetings (-12.8 vs line) — supports the UNDER. H2H avg 3.0 pts below season L30; TS% shifts +10.1% in this matchup. Opponent is below-average defense (#16) at moderate pace (#18). 6/10 signals agree — Volume, HR L30, HR L10, Context support the UNDER; Trend, Defense, FG Trend dissent. Projection model targets 9.5 pts (10.0 pts below line; 76% blended confidence [T3]). Risk: L3 has surged to 22.7 after a 7-pt outing (13.0 above L30) — momentum could push over the under line.</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>VJ Edgecombe</t>
+          <t>Paul George</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -5889,7 +5889,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>UNDER</t>
+          <t>OVER</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -5898,41 +5898,41 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>0.641</v>
+        <v>0.508</v>
       </c>
       <c r="F28" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>12.8</v>
+        <v>20.2</v>
       </c>
       <c r="I28" t="n">
-        <v>5.7</v>
+        <v>0.7</v>
       </c>
       <c r="J28" t="n">
-        <v>1.952</v>
+        <v>1.893</v>
       </c>
       <c r="K28" t="n">
-        <v>1.813</v>
+        <v>1.87</v>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>Edgecombe averages 12.0 pts in 3 meetings (-6.5 vs line) — marginally supports the UNDER. H2H avg 5.5 pts below season L30; TS% shifts +3.8% in this matchup. Opponent is weak defense (#24) at moderate pace (#14). Mixed signals: 4/10 agree (Volume, Trend, Context); counter-signals: HR L30, HR L10, Defense. Projection model targets 12.8 pts (5.7 pts below line; 64% blended confidence [T3]). Risk: high variance (σ=7.5) makes the outcome difficult to call with confidence.</t>
+          <t>George's L30 average of 18.3 pts vs the 19.5 line — marginally supports the OVER. H2H avg 2.9 pts above season L30; TS% shifts +14.8% in this matchup. Opponent is weak defense (#23) at moderate pace (#14). Mixed signals: 5/10 agree (HR L10, Defense, H2H); counter-signals: Volume, HR L30, Trend. Projection model targets 20.2 pts (0.7 pts above line; 50% blended confidence [T3]). Risk: high variance (σ=8.6) makes the outcome difficult to call with confidence.</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Kawhi Leonard</t>
+          <t>VJ Edgecombe</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>GSW @ LAC</t>
+          <t>MIL @ PHI</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -5942,50 +5942,50 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>T2</t>
+          <t>T3</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>0.598</v>
+        <v>0.641</v>
       </c>
       <c r="F29" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="G29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>27.3</v>
+        <v>12.8</v>
       </c>
       <c r="I29" t="n">
-        <v>2.2</v>
+        <v>5.7</v>
       </c>
       <c r="J29" t="n">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="K29" t="n">
-        <v>1.769</v>
+        <v>1.787</v>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>Leonard averages 24.5 pts in 4 meetings (-5.0 vs line) — supports the UNDER. H2H avg 3.7 pts below season L30. Opponent is average defense (#14) at moderate pace (#13). 9/10 signals agree — Volume, HR L30, HR L10, Trend support the UNDER; Pace dissents. Projection model targets 27.3 pts (2.2 pts below line; 59% blended confidence [T2]).</t>
+          <t>Edgecombe averages 12.0 pts in 3 meetings (-6.5 vs line) — marginally supports the UNDER. H2H avg 5.5 pts below season L30; TS% shifts +3.8% in this matchup. Opponent is weak defense (#24) at moderate pace (#14). Mixed signals: 4/10 agree (Volume, Trend, Context); counter-signals: HR L30, HR L10, Defense. Projection model targets 12.8 pts (5.7 pts below line; 64% blended confidence [T3]). Risk: high variance (σ=7.5) makes the outcome difficult to call with confidence.</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Darius Garland</t>
+          <t>Nikola Jokić</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>GSW @ LAC</t>
+          <t>DEN @ SAS</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>UNDER</t>
+          <t>OVER</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -5994,41 +5994,41 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>0.552</v>
+        <v>0.797</v>
       </c>
       <c r="F30" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>17</v>
+        <v>27.1</v>
       </c>
       <c r="I30" t="n">
-        <v>2.5</v>
+        <v>10.6</v>
       </c>
       <c r="J30" t="n">
-        <v>1.847</v>
+        <v>1.877</v>
       </c>
       <c r="K30" t="n">
-        <v>1.909</v>
+        <v>1.877</v>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>Recent scoring trending down 2.2 pts (L5 vs L30) — marginally supports the UNDER. Opponent is below-average defense (#16) at moderate pace (#13). Mixed signals: 3/10 agree (Volume, Trend, Context); counter-signals: HR L30, HR L10, Defense. Projection model targets 17.0 pts (2.5 pts below line; 55% blended confidence [T3]). Risk: high variance (σ=8.8) makes the outcome difficult to call with confidence.</t>
+          <t>Jokić averages 35.8 pts in 5 meetings (+19.3 vs line) — supports the OVER. H2H avg 9.8 pts above season L30; TS% shifts -6.0% in this matchup. Opponent is below-average defense (#18) at above-average pace (#9). 9/10 signals agree — Volume, HR L30, HR L10, Context support the OVER; Trend dissents. Projection model targets 27.1 pts (10.6 pts above line; 79% blended confidence [T3]). Risk: high variance (σ=8.4) makes the outcome difficult to call with confidence.</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Tari Eason</t>
+          <t>Bruce Brown</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>MEM @ HOU</t>
+          <t>DEN @ SAS</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -6042,41 +6042,41 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>0.576</v>
+        <v>0.52</v>
       </c>
       <c r="F31" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>12.9</v>
+        <v>7.8</v>
       </c>
       <c r="I31" t="n">
-        <v>1.6</v>
+        <v>0.7</v>
       </c>
       <c r="J31" t="n">
-        <v>1.952</v>
+        <v>2.28</v>
       </c>
       <c r="K31" t="n">
-        <v>1.8</v>
+        <v>1.599</v>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>Eason's L30 of 8.3 pts sits 6.2 below the 14.5 line — marginally supports the UNDER. H2H avg 6.7 pts above season L30; FG% +3.4% trending (L10 vs L30). Opponent is weak defense (#23) at above-average pace (#7). Mixed signals: 4/10 agree (Volume, HR L30, Context); counter-signals: HR L10, Trend, Defense. Projection model targets 12.9 pts (1.6 pts below line; 57% blended confidence [T3]).</t>
+          <t>Low scoring variance (σ=3.5) — highly predictable output near line — supports the UNDER. TS% shifts -7.2% in this matchup. Opponent is strong defense (#8) at above-average pace (#9). 6/10 signals agree — Volume, HR L30, Context, Defense support the UNDER; HR L10, Trend, Pace dissent. Projection model targets 7.8 pts (0.7 pts below line; 52% blended confidence [T3]).</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>LeBron James</t>
+          <t>Julian Strawther</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>UTA @ LAL</t>
+          <t>DEN @ SAS</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -6086,45 +6086,45 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>T2</t>
+          <t>T3</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>0.766</v>
+        <v>0.742</v>
       </c>
       <c r="F32" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>18.6</v>
+        <v>8.5</v>
       </c>
       <c r="I32" t="n">
-        <v>8.9</v>
+        <v>7</v>
       </c>
       <c r="J32" t="n">
-        <v>1.87</v>
+        <v>1.877</v>
       </c>
       <c r="K32" t="n">
-        <v>1.893</v>
+        <v>1.877</v>
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>James's L30 of 20.0 pts sits 7.5 below the 27.5 line — supports the UNDER. H2H avg 1.6 pts above season L30; TS% shifts -3.6% in this matchup. Opponent is weak defense (#27) at above-average pace (#6). 6/10 signals agree — Volume, HR L30, HR L10, Context support the UNDER; Trend, Defense, Pace dissent. Projection model targets 18.6 pts (8.9 pts below line; 76% blended confidence [T2]). Risk: L3 has surged to 28.0 after a 15-pt outing (8.0 above L30) — momentum could push over the under line.</t>
+          <t>Strawther averages 8.0 pts in 4 meetings (-7.5 vs line) — supports the UNDER. TS% shifts +4.7% in this matchup; FG% -5.0% trending (L10 vs L30). Opponent is strong defense (#8) at above-average pace (#9). 8/10 signals agree — Volume, HR L30, HR L10, Context support the UNDER; Trend, Pace dissent. Projection model targets 8.5 pts (7.0 pts below line; 74% blended confidence [T3]). Risk: L3 has surged to 14.3 (5.3 above L30) — momentum could push over the under line.</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Brice Sensabaugh</t>
+          <t>Kawhi Leonard</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>UTA @ LAL</t>
+          <t>GSW @ LAC</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -6134,45 +6134,45 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>T3</t>
+          <t>T2</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>0.736</v>
+        <v>0.5610000000000001</v>
       </c>
       <c r="F33" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="G33" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H33" t="n">
-        <v>9.800000000000001</v>
+        <v>27.3</v>
       </c>
       <c r="I33" t="n">
-        <v>11.7</v>
+        <v>1.2</v>
       </c>
       <c r="J33" t="n">
-        <v>1.87</v>
+        <v>1.971</v>
       </c>
       <c r="K33" t="n">
-        <v>1.87</v>
+        <v>1.8</v>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>Sensabaugh averages 5.3 pts in 6 meetings (-16.2 vs line) — marginally supports the UNDER. H2H avg 14.1 pts below season L30; TS% shifts -13.8% in this matchup. Opponent is average defense (#15) at slow pace (#23). Mixed signals: 5/10 agree (Volume, HR L30, Context); counter-signals: HR L10, Trend, Defense. Projection model targets 9.8 pts (11.7 pts below line; 73% blended confidence [T3]). Risk: L3 has surged to 24.0 after a 26-pt outing (4.6 above L30) — momentum could push over the under line.</t>
+          <t>Leonard averages 24.5 pts in 4 meetings (-4.0 vs line) — supports the UNDER. H2H avg 3.7 pts below season L30. Opponent is average defense (#14) at moderate pace (#13). 9/10 signals agree — Volume, HR L30, HR L10, Trend support the UNDER; Pace dissents. Projection model targets 27.3 pts (1.2 pts below line; 56% blended confidence [T2]).</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Cody Williams</t>
+          <t>Darius Garland</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>UTA @ LAL</t>
+          <t>GSW @ LAC</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -6186,7 +6186,7 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>0.75</v>
+        <v>0.593</v>
       </c>
       <c r="F34" t="n">
         <v>6</v>
@@ -6195,27 +6195,27 @@
         <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>8.6</v>
+        <v>16.8</v>
       </c>
       <c r="I34" t="n">
-        <v>8.9</v>
+        <v>3.7</v>
       </c>
       <c r="J34" t="n">
-        <v>1.833</v>
+        <v>1.943</v>
       </c>
       <c r="K34" t="n">
-        <v>1.926</v>
+        <v>1.82</v>
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>Williams averages 2.8 pts in 4 meetings (-14.7 vs line) — supports the UNDER. H2H avg 9.4 pts below season L30; TS% shifts +3.8% in this matchup. Opponent is average defense (#15) at slow pace (#23). 6/10 signals agree — Volume, HR L30, Context, H2H support the UNDER; HR L10, Trend, Defense dissent. Projection model targets 8.6 pts (8.9 pts below line; 74% blended confidence [T3]). Risk: high variance (σ=9.0) makes the outcome difficult to call with confidence.</t>
+          <t>Recent scoring trending down 2.2 pts (L5 vs L30) — supports the UNDER. Opponent is below-average defense (#16) at moderate pace (#13). 6/10 signals agree — Volume, HR L30, HR L10, Trend support the UNDER; Defense, Pace, FG Trend dissent. Projection model targets 16.8 pts (3.7 pts below line; 59% blended confidence [T3]). Risk: high variance (σ=8.8) makes the outcome difficult to call with confidence.</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Jake LaRavia</t>
+          <t>Brice Sensabaugh</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -6234,7 +6234,7 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>0.643</v>
+        <v>0.749</v>
       </c>
       <c r="F35" t="n">
         <v>5</v>
@@ -6243,20 +6243,20 @@
         <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>7</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="I35" t="n">
-        <v>4.5</v>
+        <v>12.7</v>
       </c>
       <c r="J35" t="n">
-        <v>1.926</v>
+        <v>1.893</v>
       </c>
       <c r="K35" t="n">
-        <v>1.833</v>
+        <v>1.87</v>
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>LaRavia's L30 of 6.5 pts sits 5.0 below the 11.5 line — marginally supports the UNDER. TS% shifts +3.4% in this matchup; FG% +6.6% trending (L10 vs L30). Opponent is weak defense (#27) at above-average pace (#6). Mixed signals: 5/10 agree (Volume, HR L30, HR L10); counter-signals: Trend, Defense, Pace. Projection model targets 7.0 pts (4.5 pts below line; 64% blended confidence [T3]).</t>
+          <t>Sensabaugh averages 5.3 pts in 6 meetings (-17.2 vs line) — marginally supports the UNDER. H2H avg 14.1 pts below season L30; TS% shifts -13.8% in this matchup. Opponent is average defense (#15) at slow pace (#23). Mixed signals: 5/10 agree (Volume, HR L30, Context); counter-signals: HR L10, Trend, Defense. Projection model targets 9.8 pts (12.7 pts below line; 74% blended confidence [T3]). Risk: L3 has surged to 24.0 after a 26-pt outing (4.6 above L30) — momentum could push over the under line.</t>
         </is>
       </c>
     </row>
@@ -6282,7 +6282,7 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>0.582</v>
+        <v>0.616</v>
       </c>
       <c r="F36" t="n">
         <v>7</v>
@@ -6294,34 +6294,34 @@
         <v>17.5</v>
       </c>
       <c r="I36" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J36" t="n">
-        <v>1.901</v>
+        <v>1.971</v>
       </c>
       <c r="K36" t="n">
-        <v>1.862</v>
+        <v>1.8</v>
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>Bailey averages 14.0 pts in 3 meetings (-5.5 vs line) — supports the UNDER. H2H avg 3.1 pts below season L30; TS% shifts +3.4% in this matchup. Opponent is average defense (#15) at slow pace (#23). 7/10 signals agree — Volume, HR L30, HR L10, Context support the UNDER; Trend, Defense, Min Trend dissent. Projection model targets 17.5 pts (2.0 pts below line; 58% blended confidence [T3]). Risk: high variance (σ=7.6) makes the outcome difficult to call with confidence.</t>
+          <t>Bailey averages 14.0 pts in 3 meetings (-6.5 vs line) — supports the UNDER. H2H avg 3.1 pts below season L30; TS% shifts +3.4% in this matchup. Opponent is average defense (#15) at slow pace (#23). 7/10 signals agree — Volume, HR L30, HR L10, Context support the UNDER; Trend, Defense, Min Trend dissent. Projection model targets 17.5 pts (3.0 pts below line; 61% blended confidence [T3]). Risk: high variance (σ=7.6) makes the outcome difficult to call with confidence.</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Luguentz Dort</t>
+          <t>Jake LaRavia</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>PHX @ OKC</t>
+          <t>UTA @ LAL</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>OVER</t>
+          <t>UNDER</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -6330,7 +6330,7 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>0.551</v>
+        <v>0.668</v>
       </c>
       <c r="F37" t="n">
         <v>5</v>
@@ -6339,32 +6339,32 @@
         <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>9.5</v>
+        <v>7</v>
       </c>
       <c r="I37" t="n">
-        <v>2</v>
+        <v>5.5</v>
       </c>
       <c r="J37" t="n">
-        <v>1.952</v>
+        <v>1.813</v>
       </c>
       <c r="K37" t="n">
-        <v>1.813</v>
+        <v>1.962</v>
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>Dort averages 10.5 pts in 6 meetings (+3.0 vs line) — marginally supports the OVER. H2H avg 2.6 pts above season L30; TS% shifts +4.1% in this matchup. Opponent is elite defense (#4) at moderate pace (#20). Mixed signals: 5/10 agree (Volume, Trend, Context); counter-signals: HR L30, HR L10, Defense. Projection model targets 9.5 pts (2.0 pts above line; 55% blended confidence [T3]). Risk: minutes trending down (21.6 L10 vs 26.0 L30) — role reduction would suppress counting stats.</t>
+          <t>LaRavia's L30 of 6.5 pts sits 6.0 below the 12.5 line — marginally supports the UNDER. TS% shifts +3.4% in this matchup; FG% +6.6% trending (L10 vs L30). Opponent is weak defense (#27) at above-average pace (#6). Mixed signals: 5/10 agree (Volume, HR L30, HR L10); counter-signals: Trend, Defense, Pace. Projection model targets 7.0 pts (5.5 pts below line; 66% blended confidence [T3]).</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Nikola Topić</t>
+          <t>LeBron James</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>PHX @ OKC</t>
+          <t>UTA @ LAL</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -6374,45 +6374,45 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>T1_PREMIUM</t>
+          <t>T2</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>0.819</v>
+        <v>0.742</v>
       </c>
       <c r="F38" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G38" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H38" t="n">
-        <v>3.7</v>
+        <v>18.6</v>
       </c>
       <c r="I38" t="n">
-        <v>10.8</v>
+        <v>7.9</v>
       </c>
       <c r="J38" t="n">
-        <v>1.813</v>
+        <v>1.862</v>
       </c>
       <c r="K38" t="n">
-        <v>1.962</v>
+        <v>1.901</v>
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>Topić's L30 of 3.8 pts sits 10.7 below the 14.5 line — supports the UNDER. Opponent is elite defense (#4) at moderate pace (#20). 7/10 signals agree — Volume, HR L30, HR L10, Trend support the UNDER; H2H, FG Trend, Min Trend dissent. Projection model targets 3.7 pts (10.8 pts below line; 81% blended confidence [T1_PREMIUM]).</t>
+          <t>James's L30 of 20.0 pts sits 6.5 below the 26.5 line — supports the UNDER. H2H avg 1.6 pts above season L30; TS% shifts -3.6% in this matchup. Opponent is weak defense (#27) at above-average pace (#6). 6/10 signals agree — Volume, HR L30, HR L10, Context support the UNDER; Trend, Defense, Pace dissent. Projection model targets 18.6 pts (7.9 pts below line; 74% blended confidence [T2]). Risk: L3 has surged to 28.0 after a 15-pt outing (8.0 above L30) — momentum could push over the under line.</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Aaron Wiggins</t>
+          <t>Bronny James</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>PHX @ OKC</t>
+          <t>UTA @ LAL</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -6422,40 +6422,40 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>T1_ULTRA</t>
+          <t>T3</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>0.8120000000000001</v>
+        <v>0.625</v>
       </c>
       <c r="F39" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="G39" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>7.8</v>
+        <v>6.4</v>
       </c>
       <c r="I39" t="n">
-        <v>9.699999999999999</v>
+        <v>4.1</v>
       </c>
       <c r="J39" t="n">
-        <v>2.06</v>
+        <v>2.1</v>
       </c>
       <c r="K39" t="n">
-        <v>1.73</v>
+        <v>1.699</v>
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>Wiggins's L30 of 8.4 pts sits 9.1 below the 17.5 line — supports the UNDER. H2H avg 2.4 pts above season L30; FG% +8.9% trending (L10 vs L30). Opponent is elite defense (#4) at moderate pace (#20). 9/10 signals agree — Volume, HR L30, HR L10, Trend support the UNDER; FG Trend dissents. Projection model targets 7.8 pts (9.7 pts below line; 81% blended confidence [T1_ULTRA]).</t>
+          <t>James's L30 of 3.0 pts sits 7.5 below the 10.5 line — marginally supports the UNDER. FG% +6.1% trending (L10 vs L30); Minutes up 5.3 recently (L10=13.5 vs L30=8.2). Opponent is weak defense (#30) at above-average pace (#6). Mixed signals: 4/10 agree (Volume, HR L30, HR L10); counter-signals: Trend, Defense, H2H. Projection model targets 6.4 pts (4.1 pts below line; 62% blended confidence [T3]).</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Kenrich Williams</t>
+          <t>Luguentz Dort</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -6465,7 +6465,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>UNDER</t>
+          <t>OVER</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -6474,36 +6474,36 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>0.8159999999999999</v>
+        <v>0.551</v>
       </c>
       <c r="F40" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="G40" t="n">
         <v>0</v>
       </c>
       <c r="H40" t="n">
-        <v>6.2</v>
+        <v>9.5</v>
       </c>
       <c r="I40" t="n">
-        <v>9.300000000000001</v>
+        <v>2</v>
       </c>
       <c r="J40" t="n">
-        <v>2.15</v>
+        <v>1.99</v>
       </c>
       <c r="K40" t="n">
-        <v>1.671</v>
+        <v>1.781</v>
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>Williams's L30 of 6.8 pts sits 8.7 below the 15.5 line — supports the UNDER. TS% shifts +4.5% in this matchup; FG% -4.9% trending (L10 vs L30). Opponent is elite defense (#4) at moderate pace (#20). Full consensus: 10/10 signals aligned (Volume, HR L30, HR L10, Trend). Projection model targets 6.2 pts (9.3 pts below line; 81% blended confidence [T3]). Risk: minutes trending down (11.2 L10 vs 15.5 L30) — role reduction would suppress counting stats.</t>
+          <t>Dort averages 10.5 pts in 6 meetings (+3.0 vs line) — marginally supports the OVER. H2H avg 2.6 pts above season L30; TS% shifts +4.1% in this matchup. Opponent is elite defense (#4) at moderate pace (#20). Mixed signals: 5/10 agree (Volume, Trend, Context); counter-signals: HR L30, HR L10, Defense. Projection model targets 9.5 pts (2.0 pts above line; 55% blended confidence [T3]). Risk: minutes trending down (21.6 L10 vs 26.0 L30) — role reduction would suppress counting stats.</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Jared McCain</t>
+          <t>Nikola Topić</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -6518,45 +6518,45 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>T3</t>
+          <t>T1_PREMIUM</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>0.821</v>
+        <v>0.819</v>
       </c>
       <c r="F41" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="G41" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H41" t="n">
-        <v>6.3</v>
+        <v>3.7</v>
       </c>
       <c r="I41" t="n">
-        <v>12.2</v>
+        <v>10.8</v>
       </c>
       <c r="J41" t="n">
-        <v>1.926</v>
+        <v>1.769</v>
       </c>
       <c r="K41" t="n">
-        <v>1.833</v>
+        <v>2</v>
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>McCain's L30 of 10.1 pts sits 8.4 below the 18.5 line — supports the UNDER. Minutes down 2.6 recently (L10=14.8 vs L30=17.4). Opponent is elite defense (#4) at moderate pace (#20). 9/10 signals agree — Volume, HR L30, HR L10, Trend support the UNDER; H2H dissents. Projection model targets 6.3 pts (12.2 pts below line; 82% blended confidence [T3]).</t>
+          <t>Topić's L30 of 3.8 pts sits 10.7 below the 14.5 line — supports the UNDER. Opponent is elite defense (#4) at moderate pace (#20). 7/10 signals agree — Volume, HR L30, HR L10, Trend support the UNDER; H2H, FG Trend, Min Trend dissent. Projection model targets 3.7 pts (10.8 pts below line; 81% blended confidence [T1_PREMIUM]).</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Jrue Holiday</t>
+          <t>Kenrich Williams</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>SAC @ POR</t>
+          <t>PHX @ OKC</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -6570,36 +6570,36 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>0.744</v>
+        <v>0.8159999999999999</v>
       </c>
       <c r="F42" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="G42" t="n">
         <v>0</v>
       </c>
       <c r="H42" t="n">
-        <v>6.3</v>
+        <v>6.2</v>
       </c>
       <c r="I42" t="n">
-        <v>9.199999999999999</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="J42" t="n">
-        <v>1.952</v>
+        <v>1.909</v>
       </c>
       <c r="K42" t="n">
-        <v>1.813</v>
+        <v>1.847</v>
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>Holiday's L30 of 17.5 pts sits 2.0 above the 15.5 line — marginally supports the UNDER. FG% -3.8% trending (L10 vs L30). Opponent is weak defense (#25) at moderate pace (#15). Mixed signals: 2/10 agree (HR L10, FG Trend); counter-signals: Volume, HR L30, Trend. Projection model targets 6.3 pts (9.2 pts below line; 74% blended confidence [T3]). Risk: high variance (σ=7.7) makes the outcome difficult to call with confidence.</t>
+          <t>Williams's L30 of 6.8 pts sits 8.7 below the 15.5 line — supports the UNDER. TS% shifts +4.5% in this matchup; FG% -4.9% trending (L10 vs L30). Opponent is elite defense (#4) at moderate pace (#20). Full consensus: 10/10 signals aligned (Volume, HR L30, HR L10, Trend). Projection model targets 6.2 pts (9.3 pts below line; 81% blended confidence [T3]). Risk: minutes trending down (11.2 L10 vs 15.5 L30) — role reduction would suppress counting stats.</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Donovan Clingan</t>
+          <t>Jrue Holiday</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -6618,19 +6618,19 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>0.556</v>
+        <v>0.744</v>
       </c>
       <c r="F43" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="G43" t="n">
         <v>0</v>
       </c>
       <c r="H43" t="n">
-        <v>11.3</v>
+        <v>6.3</v>
       </c>
       <c r="I43" t="n">
-        <v>2.2</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="J43" t="n">
         <v>2</v>
@@ -6640,7 +6640,7 @@
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>Clingan averages 9.7 pts in 6 meetings (-3.8 vs line) — supports the UNDER. H2H avg 4.0 pts below season L30; TS% shifts +10.7% in this matchup. Opponent is weak defense (#29) at moderate pace (#15). 6/10 signals agree — HR L10, Trend, Context, H2H support the UNDER; Volume, HR L30, Defense dissent. Projection model targets 11.3 pts (2.2 pts below line; 55% blended confidence [T3]).</t>
+          <t>Holiday's L30 of 17.5 pts sits 2.0 above the 15.5 line — marginally supports the UNDER. FG% -3.8% trending (L10 vs L30). Opponent is weak defense (#25) at moderate pace (#15). Mixed signals: 2/10 agree (HR L10, FG Trend); counter-signals: Volume, HR L30, Trend. Projection model targets 6.3 pts (9.2 pts below line; 74% blended confidence [T3]). Risk: high variance (σ=7.7) makes the outcome difficult to call with confidence.</t>
         </is>
       </c>
     </row>
@@ -6666,10 +6666,10 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>0.54</v>
+        <v>0.583</v>
       </c>
       <c r="F44" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G44" t="n">
         <v>0</v>
@@ -6678,7 +6678,7 @@
         <v>24.4</v>
       </c>
       <c r="I44" t="n">
-        <v>1.1</v>
+        <v>2.1</v>
       </c>
       <c r="J44" t="n">
         <v>1.909</v>
@@ -6688,14 +6688,14 @@
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>Recent scoring trending up 6.2 pts (L5 vs L30) — marginally supports the UNDER. TS% shifts +6.4% in this matchup; FG% +4.2% trending (L10 vs L30). Opponent is below-average defense (#16) at moderate pace (#15). Mixed signals: 4/10 agree (Volume, HR L30, Context); counter-signals: HR L10, Trend, Defense. Projection model targets 24.4 pts (1.1 pts below line; 53% blended confidence [T3]). Risk: L3 has surged to 30.0 after a 11-pt outing (7.4 above L30) — momentum could push over the under line.</t>
+          <t>Avdija averages 21.6 pts in 7 meetings (-4.9 vs line) — marginally supports the UNDER. TS% shifts +6.4% in this matchup; FG% +4.2% trending (L10 vs L30). Opponent is below-average defense (#16) at moderate pace (#15). Mixed signals: 5/10 agree (Volume, HR L30, HR L10); counter-signals: Trend, Defense, Pace. Projection model targets 24.4 pts (2.1 pts below line; 58% blended confidence [T3]). Risk: L3 has surged to 30.0 after a 11-pt outing (7.4 above L30) — momentum could push over the under line.</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Scoot Henderson</t>
+          <t>Donovan Clingan</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -6714,29 +6714,29 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>0.638</v>
+        <v>0.556</v>
       </c>
       <c r="F45" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G45" t="n">
         <v>0</v>
       </c>
       <c r="H45" t="n">
-        <v>8.800000000000001</v>
+        <v>11.3</v>
       </c>
       <c r="I45" t="n">
-        <v>5.7</v>
+        <v>2.2</v>
       </c>
       <c r="J45" t="n">
-        <v>1.649</v>
+        <v>2.03</v>
       </c>
       <c r="K45" t="n">
-        <v>2.18</v>
+        <v>1.752</v>
       </c>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>Henderson averages 9.7 pts in 3 meetings (-4.8 vs line) — marginally supports the UNDER. H2H avg 4.2 pts below season L30; TS% shifts -3.5% in this matchup. Opponent is weak defense (#25) at moderate pace (#15). Mixed signals: 4/10 agree (Volume, HR L30, Context); counter-signals: HR L10, Trend, Defense. Projection model targets 8.8 pts (5.7 pts below line; 63% blended confidence [T3]).</t>
+          <t>Clingan averages 9.7 pts in 6 meetings (-3.8 vs line) — supports the UNDER. H2H avg 4.0 pts below season L30; TS% shifts +10.7% in this matchup. Opponent is weak defense (#29) at moderate pace (#15). 6/10 signals agree — HR L10, Trend, Context, H2H support the UNDER; Volume, HR L30, Defense dissent. Projection model targets 11.3 pts (2.2 pts below line; 55% blended confidence [T3]).</t>
         </is>
       </c>
     </row>
@@ -6777,10 +6777,10 @@
         <v>3.9</v>
       </c>
       <c r="J46" t="n">
-        <v>1.877</v>
+        <v>1.917</v>
       </c>
       <c r="K46" t="n">
-        <v>1.877</v>
+        <v>1.84</v>
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
@@ -6825,10 +6825,10 @@
         <v>15.2</v>
       </c>
       <c r="J47" t="n">
-        <v>1.971</v>
+        <v>2.02</v>
       </c>
       <c r="K47" t="n">
-        <v>1.8</v>
+        <v>1.758</v>
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
@@ -6873,10 +6873,10 @@
         <v>1.9</v>
       </c>
       <c r="J48" t="n">
-        <v>2.03</v>
+        <v>2.07</v>
       </c>
       <c r="K48" t="n">
-        <v>1.752</v>
+        <v>1.719</v>
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
@@ -6921,10 +6921,10 @@
         <v>8.300000000000001</v>
       </c>
       <c r="J49" t="n">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="K49" t="n">
-        <v>1.769</v>
+        <v>1.741</v>
       </c>
       <c r="L49" s="2" t="inlineStr">
         <is>
@@ -6935,7 +6935,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Precious Achiuwa</t>
+          <t>Scoot Henderson</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -6950,33 +6950,33 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>T2</t>
+          <t>T3</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>0.739</v>
+        <v>0.704</v>
       </c>
       <c r="F50" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G50" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H50" t="n">
-        <v>5.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="I50" t="n">
-        <v>8.9</v>
+        <v>7.7</v>
       </c>
       <c r="J50" t="n">
-        <v>2.09</v>
+        <v>2</v>
       </c>
       <c r="K50" t="n">
-        <v>1.709</v>
+        <v>1.769</v>
       </c>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>Achiuwa averages 3.6 pts in 5 meetings (-10.9 vs line) — supports the UNDER. H2H avg 9.6 pts below season L30; TS% shifts -15.1% in this matchup. Opponent is below-average defense (#20) at moderate pace (#17). 6/10 signals agree — Volume, HR L30, HR L10, Context support the UNDER; Trend, Defense, FG Trend dissent. Projection model targets 5.6 pts (8.9 pts below line; 73% blended confidence [T2]).</t>
+          <t>Henderson averages 9.7 pts in 3 meetings (-6.8 vs line) — marginally supports the UNDER. H2H avg 4.2 pts below season L30; TS% shifts -3.5% in this matchup. Opponent is weak defense (#25) at moderate pace (#15). Mixed signals: 5/10 agree (Volume, HR L30, HR L10); counter-signals: Trend, Defense, Pace. Projection model targets 8.8 pts (7.7 pts below line; 70% blended confidence [T3]).</t>
         </is>
       </c>
     </row>
@@ -7049,7 +7049,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Jalen Johnson</t>
+          <t>Bam Adebayo</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -7059,17 +7059,17 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>OVER</t>
+          <t>UNDER</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>22.5</v>
+        <v>21.5</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Nickeil Alexander-Walker</t>
+          <t>Jalen Johnson</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -7079,11 +7079,11 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>UNDER</t>
+          <t>OVER</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>24.5</v>
+        <v>22.5</v>
       </c>
     </row>
     <row r="4">
@@ -7129,7 +7129,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Bam Adebayo</t>
+          <t>Nickeil Alexander-Walker</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -7139,17 +7139,17 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>UNDER</t>
+          <t>OVER</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>23.5</v>
+        <v>22.5</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Andrew Wiggins</t>
+          <t>Dyson Daniels</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -7163,18 +7163,18 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>18.5</v>
+        <v>12.5</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Paolo Banchero</t>
+          <t>Onyeka Okongwu</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>ORL @ BOS</t>
+          <t>ATL @ MIA</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -7183,33 +7183,33 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>20.5</v>
+        <v>15.5</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Desmond Bane</t>
+          <t>Andrew Wiggins</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>ORL @ BOS</t>
+          <t>ATL @ MIA</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>UNDER</t>
+          <t>LEAN UNDER</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>19.5</v>
+        <v>15.5</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Wendell Carter Jr.</t>
+          <t>Paolo Banchero</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -7219,22 +7219,22 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>OVER</t>
+          <t>UNDER</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>11.5</v>
+        <v>20.5</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Immanuel Quickley</t>
+          <t>Wendell Carter Jr.</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>BKN @ TOR</t>
+          <t>ORL @ BOS</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -7243,18 +7243,18 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>14.5</v>
+        <v>10.5</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Scottie Barnes</t>
+          <t>Jalen Suggs</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>BKN @ TOR</t>
+          <t>ORL @ BOS</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -7263,63 +7263,63 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>19.5</v>
+        <v>12.5</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Brandon Ingram</t>
+          <t>Desmond Bane</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>BKN @ TOR</t>
+          <t>ORL @ BOS</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>LEAN UNDER</t>
+          <t>UNDER</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>20.5</v>
+        <v>17.5</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>LaMelo Ball</t>
+          <t>Franz Wagner</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>CHA @ NYK</t>
+          <t>ORL @ BOS</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>OVER</t>
+          <t>UNDER</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>22.5</v>
+        <v>16.5</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Miles Bridges</t>
+          <t>Immanuel Quickley</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>CHA @ NYK</t>
+          <t>BKN @ TOR</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>UNDER</t>
+          <t>OVER</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -7329,32 +7329,32 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Brandon Miller</t>
+          <t>Brandon Ingram</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>CHA @ NYK</t>
+          <t>BKN @ TOR</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>UNDER</t>
+          <t>OVER</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>20.5</v>
+        <v>19.5</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Moussa Diabaté</t>
+          <t>Scottie Barnes</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>CHA @ NYK</t>
+          <t>BKN @ TOR</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -7363,13 +7363,13 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>7.5</v>
+        <v>16.5</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Kon Knueppel</t>
+          <t>LaMelo Ball</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -7379,22 +7379,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>UNDER</t>
+          <t>OVER</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>17.5</v>
+        <v>22.5</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Quenton Jackson</t>
+          <t>Miles Bridges</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>DET @ IND</t>
+          <t>CHA @ NYK</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -7409,12 +7409,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Ausar Thompson</t>
+          <t>Kon Knueppel</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>DET @ IND</t>
+          <t>CHA @ NYK</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -7423,23 +7423,23 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>9.5</v>
+        <v>17.5</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Cade Cunningham</t>
+          <t>Brandon Miller</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>DET @ IND</t>
+          <t>CHA @ NYK</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>UNDER</t>
+          <t>LEAN UNDER</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -7449,7 +7449,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Tobias Harris</t>
+          <t>Jarace Walker</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -7459,17 +7459,17 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>LEAN OVER</t>
+          <t>UNDER</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>10.5</v>
+        <v>19.5</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Micah Potter</t>
+          <t>Quenton Jackson</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -7483,13 +7483,13 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>12.5</v>
+        <v>14.5</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Jarace Walker</t>
+          <t>Ausar Thompson</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -7503,33 +7503,33 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>19.5</v>
+        <v>9.5</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Tyrese Maxey</t>
+          <t>Micah Potter</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>MIL @ PHI</t>
+          <t>DET @ IND</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>LEAN UNDER</t>
+          <t>UNDER</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>28.5</v>
+        <v>13.5</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>AJ Green</t>
+          <t>Tyrese Maxey</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -7539,17 +7539,17 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>UNDER</t>
+          <t>LEAN UNDER</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>19.5</v>
+        <v>28.5</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Paul George</t>
+          <t>AJ Green</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -7559,7 +7559,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>OVER</t>
+          <t>UNDER</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -7569,7 +7569,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>VJ Edgecombe</t>
+          <t>Paul George</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -7579,22 +7579,22 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>UNDER</t>
+          <t>OVER</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>18.5</v>
+        <v>19.5</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Kawhi Leonard</t>
+          <t>VJ Edgecombe</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>GSW @ LAC</t>
+          <t>MIL @ PHI</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -7603,38 +7603,38 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>29.5</v>
+        <v>18.5</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Darius Garland</t>
+          <t>Nikola Jokić</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>GSW @ LAC</t>
+          <t>DEN @ SAS</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>UNDER</t>
+          <t>OVER</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>19.5</v>
+        <v>16.5</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Tari Eason</t>
+          <t>Bruce Brown</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>MEM @ HOU</t>
+          <t>DEN @ SAS</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -7643,18 +7643,18 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>14.5</v>
+        <v>8.5</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>LeBron James</t>
+          <t>Julian Strawther</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>UTA @ LAL</t>
+          <t>DEN @ SAS</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -7663,18 +7663,18 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>27.5</v>
+        <v>15.5</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Brice Sensabaugh</t>
+          <t>Kawhi Leonard</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>UTA @ LAL</t>
+          <t>GSW @ LAC</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -7683,18 +7683,18 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>21.5</v>
+        <v>28.5</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Cody Williams</t>
+          <t>Darius Garland</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>UTA @ LAL</t>
+          <t>GSW @ LAC</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -7703,13 +7703,13 @@
         </is>
       </c>
       <c r="D34" t="n">
-        <v>17.5</v>
+        <v>20.5</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Jake LaRavia</t>
+          <t>Brice Sensabaugh</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -7723,7 +7723,7 @@
         </is>
       </c>
       <c r="D35" t="n">
-        <v>11.5</v>
+        <v>22.5</v>
       </c>
     </row>
     <row r="36">
@@ -7743,38 +7743,38 @@
         </is>
       </c>
       <c r="D36" t="n">
-        <v>19.5</v>
+        <v>20.5</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Luguentz Dort</t>
+          <t>Jake LaRavia</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>PHX @ OKC</t>
+          <t>UTA @ LAL</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>OVER</t>
+          <t>UNDER</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>7.5</v>
+        <v>12.5</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Nikola Topić</t>
+          <t>LeBron James</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>PHX @ OKC</t>
+          <t>UTA @ LAL</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -7783,18 +7783,18 @@
         </is>
       </c>
       <c r="D38" t="n">
-        <v>14.5</v>
+        <v>26.5</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Aaron Wiggins</t>
+          <t>Bronny James</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>PHX @ OKC</t>
+          <t>UTA @ LAL</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -7803,13 +7803,13 @@
         </is>
       </c>
       <c r="D39" t="n">
-        <v>17.5</v>
+        <v>10.5</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Kenrich Williams</t>
+          <t>Luguentz Dort</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -7819,17 +7819,17 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>UNDER</t>
+          <t>OVER</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>15.5</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Jared McCain</t>
+          <t>Nikola Topić</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -7843,18 +7843,18 @@
         </is>
       </c>
       <c r="D41" t="n">
-        <v>18.5</v>
+        <v>14.5</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Jrue Holiday</t>
+          <t>Kenrich Williams</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>SAC @ POR</t>
+          <t>PHX @ OKC</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -7869,7 +7869,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Donovan Clingan</t>
+          <t>Jrue Holiday</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -7883,7 +7883,7 @@
         </is>
       </c>
       <c r="D43" t="n">
-        <v>13.5</v>
+        <v>15.5</v>
       </c>
     </row>
     <row r="44">
@@ -7903,13 +7903,13 @@
         </is>
       </c>
       <c r="D44" t="n">
-        <v>25.5</v>
+        <v>26.5</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Scoot Henderson</t>
+          <t>Donovan Clingan</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -7923,7 +7923,7 @@
         </is>
       </c>
       <c r="D45" t="n">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
     </row>
     <row r="46">
@@ -8009,7 +8009,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Precious Achiuwa</t>
+          <t>Scoot Henderson</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -8023,7 +8023,7 @@
         </is>
       </c>
       <c r="D50" t="n">
-        <v>14.5</v>
+        <v>16.5</v>
       </c>
     </row>
   </sheetData>

--- a/daily/2026-04-12.xlsx
+++ b/daily/2026-04-12.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Props" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Predictions" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Graded" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Props" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Predictions" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Graded" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -32,7 +32,7 @@
       <color rgb="00E0E0E0"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -42,6 +42,21 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="001E1E2E"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00EF4444"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F59E0B"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="0022C55E"/>
       </patternFill>
     </fill>
   </fills>
@@ -57,7 +72,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
@@ -65,6 +80,9 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -2350,7 +2368,6 @@
       <c r="V23" t="n">
         <v>22</v>
       </c>
-      <c r="W23" t="inlineStr"/>
       <c r="X23" t="n">
         <v>-4.8</v>
       </c>
@@ -2510,7 +2527,6 @@
       <c r="V25" t="n">
         <v>22</v>
       </c>
-      <c r="W25" t="inlineStr"/>
       <c r="X25" t="n">
         <v>-23.3</v>
       </c>
@@ -3654,7 +3670,6 @@
       <c r="V39" t="n">
         <v>6</v>
       </c>
-      <c r="W39" t="inlineStr"/>
       <c r="X39" t="n">
         <v>56</v>
       </c>
@@ -3814,7 +3829,6 @@
       <c r="V41" t="n">
         <v>20</v>
       </c>
-      <c r="W41" t="inlineStr"/>
       <c r="X41" t="n">
         <v>0</v>
       </c>
@@ -3974,7 +3988,6 @@
       <c r="V43" t="n">
         <v>15</v>
       </c>
-      <c r="W43" t="inlineStr"/>
       <c r="X43" t="n">
         <v>-23.2</v>
       </c>
@@ -4298,7 +4311,6 @@
       <c r="V47" t="n">
         <v>17</v>
       </c>
-      <c r="W47" t="inlineStr"/>
       <c r="X47" t="n">
         <v>-42.9</v>
       </c>
@@ -4450,7 +4462,7 @@
         <v>1.6</v>
       </c>
       <c r="T49" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="U49" t="n">
         <v>20</v>
@@ -7047,983 +7059,2173 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="A2" s="3" t="inlineStr">
         <is>
           <t>Bam Adebayo</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B2" s="3" t="inlineStr">
         <is>
           <t>ATL @ MIA</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="C2" s="3" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D2" t="n">
+      <c r="D2" s="3" t="n">
         <v>21.5</v>
       </c>
+      <c r="E2" s="3" t="n">
+        <v>25</v>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>LOSS — Adebayo scored 25 pts vs 21.5 line (+3.5), UNDER missed by 3.5 pts. Adebayo played 29 min (-5.0 vs L10 avg of 34.2) — 15% less than expected. Shooting efficiency was hot: 61.1% FG (+21.8% vs L10 avg of 39.3%). 11/18 from the field. Counter-signals that proved correct: Volume, Context, Defense, Pace. Signals that were wrong: HR L30, HR L10, Trend. Projection model targeted 18.0 pts — actual 25 was 7.0 pts off (correct direction). Loss classification: MINUTES_SHORTFALL. Note: Minutes were the deciding factor, not scoring rate. Flag Adebayo for minutes risk in future props if role uncertainty exists.</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>MINUTES_SHORTFALL</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-13 14:18</t>
+        </is>
+      </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="A3" s="4" t="inlineStr">
         <is>
           <t>Jalen Johnson</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="B3" s="4" t="inlineStr">
         <is>
           <t>ATL @ MIA</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="C3" s="4" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D3" t="n">
+      <c r="D3" s="4" t="n">
         <v>22.5</v>
       </c>
+      <c r="E3" s="4" t="n"/>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>DNP</t>
+        </is>
+      </c>
+      <c r="G3" s="4" t="n"/>
+      <c r="H3" s="4" t="inlineStr"/>
+      <c r="I3" s="4" t="n"/>
+      <c r="J3" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-13 14:18</t>
+        </is>
+      </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
+      <c r="A4" s="4" t="inlineStr">
         <is>
           <t>CJ McCollum</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="B4" s="4" t="inlineStr">
         <is>
           <t>ATL @ MIA</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="C4" s="4" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D4" t="n">
+      <c r="D4" s="4" t="n">
         <v>19.5</v>
       </c>
+      <c r="E4" s="4" t="n"/>
+      <c r="F4" s="4" t="inlineStr">
+        <is>
+          <t>DNP</t>
+        </is>
+      </c>
+      <c r="G4" s="4" t="n"/>
+      <c r="H4" s="4" t="inlineStr"/>
+      <c r="I4" s="4" t="n"/>
+      <c r="J4" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-13 14:18</t>
+        </is>
+      </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
+      <c r="A5" s="5" t="inlineStr">
         <is>
           <t>Tyler Herro</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B5" s="5" t="inlineStr">
         <is>
           <t>ATL @ MIA</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C5" s="5" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D5" t="n">
+      <c r="D5" s="5" t="n">
         <v>22.5</v>
       </c>
+      <c r="E5" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="F5" s="5" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G5" s="5" t="n">
+        <v>-17.5</v>
+      </c>
+      <c r="H5" s="5" t="inlineStr">
+        <is>
+          <t>WIN — Herro scored 5 pts vs 22.5 line (-17.5), UNDER hit by 17.5 pts. Herro played 22 min (-11.3 vs L10 avg of 33.6) — 34% less than expected. Shooting efficiency was cold: 22.2% FG (-25.6% vs L10 avg of 47.8%). 2/9 from the field. Signals that called it correctly: Volume, HR L30, HR L10, Context (4/10 aligned). Counter-signals that were wrong: Trend, Defense, H2H. Projection model targeted 19.4 pts — actual 5 was 14.4 pts off (correct direction). Result classification: MODEL_CORRECT. Note: Result confirms Herro's consistency near this line level.</t>
+        </is>
+      </c>
+      <c r="I5" s="5" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J5" s="5" t="inlineStr">
+        <is>
+          <t>2026-04-13 14:18</t>
+        </is>
+      </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
+      <c r="A6" s="4" t="inlineStr">
         <is>
           <t>Nickeil Alexander-Walker</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B6" s="4" t="inlineStr">
         <is>
           <t>ATL @ MIA</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="C6" s="4" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D6" t="n">
+      <c r="D6" s="4" t="n">
         <v>22.5</v>
       </c>
+      <c r="E6" s="4" t="n"/>
+      <c r="F6" s="4" t="inlineStr">
+        <is>
+          <t>DNP</t>
+        </is>
+      </c>
+      <c r="G6" s="4" t="n"/>
+      <c r="H6" s="4" t="inlineStr"/>
+      <c r="I6" s="4" t="n"/>
+      <c r="J6" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-13 14:18</t>
+        </is>
+      </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
+      <c r="A7" s="4" t="inlineStr">
         <is>
           <t>Dyson Daniels</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B7" s="4" t="inlineStr">
         <is>
           <t>ATL @ MIA</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="C7" s="4" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D7" t="n">
+      <c r="D7" s="4" t="n">
         <v>12.5</v>
       </c>
+      <c r="E7" s="4" t="n"/>
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>DNP</t>
+        </is>
+      </c>
+      <c r="G7" s="4" t="n"/>
+      <c r="H7" s="4" t="inlineStr"/>
+      <c r="I7" s="4" t="n"/>
+      <c r="J7" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-13 14:18</t>
+        </is>
+      </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
+      <c r="A8" s="4" t="inlineStr">
         <is>
           <t>Onyeka Okongwu</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B8" s="4" t="inlineStr">
         <is>
           <t>ATL @ MIA</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="C8" s="4" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D8" t="n">
+      <c r="D8" s="4" t="n">
         <v>15.5</v>
       </c>
+      <c r="E8" s="4" t="n"/>
+      <c r="F8" s="4" t="inlineStr">
+        <is>
+          <t>DNP</t>
+        </is>
+      </c>
+      <c r="G8" s="4" t="n"/>
+      <c r="H8" s="4" t="inlineStr"/>
+      <c r="I8" s="4" t="n"/>
+      <c r="J8" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-13 14:18</t>
+        </is>
+      </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
+      <c r="A9" s="5" t="inlineStr">
         <is>
           <t>Andrew Wiggins</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B9" s="5" t="inlineStr">
         <is>
           <t>ATL @ MIA</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="C9" s="5" t="inlineStr">
         <is>
           <t>LEAN UNDER</t>
         </is>
       </c>
-      <c r="D9" t="n">
+      <c r="D9" s="5" t="n">
         <v>15.5</v>
       </c>
+      <c r="E9" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="F9" s="5" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G9" s="5" t="n">
+        <v>-11.5</v>
+      </c>
+      <c r="H9" s="5" t="inlineStr">
+        <is>
+          <t>WIN — Wiggins scored 4 pts vs 15.5 line (-11.5), UNDER hit by 11.5 pts. Minutes were as expected: 26 played vs L10 avg 27.2. Shooting efficiency was cold: 11.1% FG (-40.9% vs L10 avg of 52.0%). 1/9 from the field. Signals that called it correctly: Volume, HR L30, HR L10, Trend, Context (6/10 aligned). Counter-signals that were wrong: Defense, H2H, Pace. Projection model targeted 15.2 pts — actual 4 was 11.2 pts off (correct direction). Result classification: MODEL_CORRECT. Note: Result confirms Wiggins's consistency near this line level.</t>
+        </is>
+      </c>
+      <c r="I9" s="5" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J9" s="5" t="inlineStr">
+        <is>
+          <t>2026-04-13 14:18</t>
+        </is>
+      </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
+      <c r="A10" s="3" t="inlineStr">
         <is>
           <t>Paolo Banchero</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B10" s="3" t="inlineStr">
         <is>
           <t>ORL @ BOS</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="C10" s="3" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D10" t="n">
+      <c r="D10" s="3" t="n">
         <v>20.5</v>
       </c>
+      <c r="E10" s="3" t="n">
+        <v>23</v>
+      </c>
+      <c r="F10" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G10" s="3" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="H10" s="3" t="inlineStr">
+        <is>
+          <t>LOSS — Banchero scored 23 pts vs 20.5 line (+2.5), UNDER missed by 2.5 pts. Banchero played 38 min (+4.5 vs L10 avg of 33.4) — 13% more than expected. Shooting efficiency was cold: 31.8% FG (-15.0% vs L10 avg of 46.8%). 7/22 from the field. Counter-signals that proved correct: Volume, HR L30, Context, FG Trend. Signals that were wrong: HR L10, Trend, Defense. Projection model targeted 17.4 pts — actual 23 was 5.6 pts off (correct direction). Loss classification: SHOOTING_VARIANCE. Note: Volume and opportunity signals were correct but shooting efficiency diverged. Normal variance — per-minute output was on track.</t>
+        </is>
+      </c>
+      <c r="I10" s="3" t="inlineStr">
+        <is>
+          <t>SHOOTING_VARIANCE</t>
+        </is>
+      </c>
+      <c r="J10" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-13 14:18</t>
+        </is>
+      </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
+      <c r="A11" s="3" t="inlineStr">
         <is>
           <t>Wendell Carter Jr.</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B11" s="3" t="inlineStr">
         <is>
           <t>ORL @ BOS</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="C11" s="3" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D11" t="n">
+      <c r="D11" s="3" t="n">
         <v>10.5</v>
       </c>
+      <c r="E11" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="F11" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G11" s="3" t="n">
+        <v>-7.5</v>
+      </c>
+      <c r="H11" s="3" t="inlineStr">
+        <is>
+          <t>LOSS — Jr. scored 3 pts vs 10.5 line (-7.5), OVER missed by 7.5 pts. Jr. played 31 min (+3.6 vs L10 avg of 27.5) — 13% more than expected. Shooting efficiency was cold: 0.0% FG (-55.1% vs L10 avg of 55.1%). 0/5 from the field. Counter-signals that proved correct: Defense, Pace, Min Trend. Signals that were wrong: Volume, HR L30, HR L10. Projection model targeted 12.7 pts — actual 3 was 9.7 pts off (correct direction). Loss classification: SHOOTING_VARIANCE. Note: Volume and opportunity signals were correct but shooting efficiency diverged. Normal variance — per-minute output was on track.</t>
+        </is>
+      </c>
+      <c r="I11" s="3" t="inlineStr">
+        <is>
+          <t>SHOOTING_VARIANCE</t>
+        </is>
+      </c>
+      <c r="J11" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-13 14:18</t>
+        </is>
+      </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
+      <c r="A12" s="3" t="inlineStr">
         <is>
           <t>Jalen Suggs</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B12" s="3" t="inlineStr">
         <is>
           <t>ORL @ BOS</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="C12" s="3" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D12" t="n">
+      <c r="D12" s="3" t="n">
         <v>12.5</v>
       </c>
+      <c r="E12" s="3" t="n">
+        <v>23</v>
+      </c>
+      <c r="F12" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G12" s="3" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="H12" s="3" t="inlineStr">
+        <is>
+          <t>LOSS — Suggs scored 23 pts vs 12.5 line (+10.5), UNDER missed by 10.5 pts. Suggs played 38 min (+7.8 vs L10 avg of 30.2) — 26% more than expected. Shooting was in line with averages: 47.1% FG (8/17, L10 avg 45.3%). Counter-signals that proved correct: Volume, HR L30, Trend, H2H. Signals that were wrong: HR L10, Context, Defense. Projection model targeted 10.8 pts — actual 23 was 12.2 pts off (correct direction). Loss classification: BLOWOUT_EFFECT. Note: Game script invalidated the prop. Consider blowout probability when ORL is involved.</t>
+        </is>
+      </c>
+      <c r="I12" s="3" t="inlineStr">
+        <is>
+          <t>BLOWOUT_EFFECT</t>
+        </is>
+      </c>
+      <c r="J12" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-13 14:18</t>
+        </is>
+      </c>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr">
+      <c r="A13" s="5" t="inlineStr">
         <is>
           <t>Desmond Bane</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="B13" s="5" t="inlineStr">
         <is>
           <t>ORL @ BOS</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
+      <c r="C13" s="5" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D13" t="n">
+      <c r="D13" s="5" t="n">
         <v>17.5</v>
       </c>
+      <c r="E13" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="F13" s="5" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G13" s="5" t="n">
+        <v>-9.5</v>
+      </c>
+      <c r="H13" s="5" t="inlineStr">
+        <is>
+          <t>WIN — Bane scored 8 pts vs 17.5 line (-9.5), UNDER hit by 9.5 pts. Bane played 18 min (-13.5 vs L10 avg of 31.1) — 43% less than expected. Shooting efficiency was cold: 37.5% FG (-7.9% vs L10 avg of 45.4%). 3/8 from the field. Signals that called it correctly: Trend, Defense, H2H, Pace, FG Trend (6/10 aligned). Counter-signals that were wrong: Volume, HR L30, HR L10. Projection model targeted 14.2 pts — actual 8 was 6.2 pts off (correct direction). Result classification: MODEL_CORRECT. Note: Result confirms Bane's consistency near this line level.</t>
+        </is>
+      </c>
+      <c r="I13" s="5" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J13" s="5" t="inlineStr">
+        <is>
+          <t>2026-04-13 14:18</t>
+        </is>
+      </c>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr">
+      <c r="A14" s="3" t="inlineStr">
         <is>
           <t>Franz Wagner</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
+      <c r="B14" s="3" t="inlineStr">
         <is>
           <t>ORL @ BOS</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
+      <c r="C14" s="3" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D14" t="n">
+      <c r="D14" s="3" t="n">
         <v>16.5</v>
       </c>
+      <c r="E14" s="3" t="n">
+        <v>20</v>
+      </c>
+      <c r="F14" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G14" s="3" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="H14" s="3" t="inlineStr">
+        <is>
+          <t>LOSS — Wagner scored 20 pts vs 16.5 line (+3.5), UNDER missed by 3.5 pts. Wagner played 26 min (+6.2 vs L10 avg of 20.0) — 31% more than expected. Shooting efficiency was cold: 38.9% FG (-9.7% vs L10 avg of 48.6%). 7/18 from the field. Counter-signals that proved correct: Volume, HR L30, Context, H2H. Signals that were wrong: HR L10, Trend, Defense. Projection model targeted 14.3 pts — actual 20 was 5.7 pts off (correct direction). Loss classification: SHOOTING_VARIANCE. Note: Volume and opportunity signals were correct but shooting efficiency diverged. Normal variance — per-minute output was on track.</t>
+        </is>
+      </c>
+      <c r="I14" s="3" t="inlineStr">
+        <is>
+          <t>SHOOTING_VARIANCE</t>
+        </is>
+      </c>
+      <c r="J14" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-13 14:18</t>
+        </is>
+      </c>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr">
+      <c r="A15" s="3" t="inlineStr">
         <is>
           <t>Immanuel Quickley</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
+      <c r="B15" s="3" t="inlineStr">
         <is>
           <t>BKN @ TOR</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
+      <c r="C15" s="3" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D15" t="n">
+      <c r="D15" s="3" t="n">
         <v>14.5</v>
       </c>
+      <c r="E15" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="F15" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G15" s="3" t="n">
+        <v>-10.5</v>
+      </c>
+      <c r="H15" s="3" t="inlineStr">
+        <is>
+          <t>LOSS — Quickley scored 4 pts vs 14.5 line (-10.5), OVER missed by 10.5 pts. Quickley played 17 min (-13.1 vs L10 avg of 29.7) — 44% less than expected. Shooting was in line with averages: 33.3% FG (2/6, L10 avg 38.0%). Counter-signals that proved correct: HR L10, Trend, Pace, FG Trend. Signals that were wrong: Volume, HR L30, Context. Projection model targeted 15.6 pts — actual 4 was 11.6 pts off (correct direction). Loss classification: MINUTES_SHORTFALL. Note: Minutes were the deciding factor, not scoring rate. Flag Quickley for minutes risk in future props if role uncertainty exists.</t>
+        </is>
+      </c>
+      <c r="I15" s="3" t="inlineStr">
+        <is>
+          <t>MINUTES_SHORTFALL</t>
+        </is>
+      </c>
+      <c r="J15" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-13 14:18</t>
+        </is>
+      </c>
     </row>
     <row r="16">
-      <c r="A16" t="inlineStr">
+      <c r="A16" s="5" t="inlineStr">
         <is>
           <t>Brandon Ingram</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
+      <c r="B16" s="5" t="inlineStr">
         <is>
           <t>BKN @ TOR</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr">
+      <c r="C16" s="5" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D16" t="n">
+      <c r="D16" s="5" t="n">
         <v>19.5</v>
       </c>
+      <c r="E16" s="5" t="n">
+        <v>25</v>
+      </c>
+      <c r="F16" s="5" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G16" s="5" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="H16" s="5" t="inlineStr">
+        <is>
+          <t>WIN — Ingram scored 25 pts vs 19.5 line (+5.5), OVER hit by 5.5 pts. Minutes were as expected: 32 played vs L10 avg 32.1. Shooting efficiency was hot: 70.0% FG (+21.5% vs L10 avg of 48.5%). 7/10 from the field. Signals that called it correctly: Volume, Trend, Context, Defense, H2H (5/10 aligned). Counter-signals that were wrong: HR L30, HR L10, Pace. Projection model targeted 20.6 pts — actual 25 was 4.4 pts off (correct direction). Result classification: MODEL_CORRECT. Note: Result confirms Ingram's consistency near this line level.</t>
+        </is>
+      </c>
+      <c r="I16" s="5" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J16" s="5" t="inlineStr">
+        <is>
+          <t>2026-04-13 14:18</t>
+        </is>
+      </c>
     </row>
     <row r="17">
-      <c r="A17" t="inlineStr">
+      <c r="A17" s="3" t="inlineStr">
         <is>
           <t>Scottie Barnes</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
+      <c r="B17" s="3" t="inlineStr">
         <is>
           <t>BKN @ TOR</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr">
+      <c r="C17" s="3" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D17" t="n">
+      <c r="D17" s="3" t="n">
         <v>16.5</v>
       </c>
+      <c r="E17" s="3" t="n">
+        <v>18</v>
+      </c>
+      <c r="F17" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G17" s="3" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="H17" s="3" t="inlineStr">
+        <is>
+          <t>LOSS — Barnes scored 18 pts vs 16.5 line (+1.5), UNDER missed by 1.5 pts. Minutes were as expected: 32 played vs L10 avg 30.3. Shooting efficiency was hot: 72.7% FG (+21.7% vs L10 avg of 51.0%). 8/11 from the field. Counter-signals that proved correct: Defense, H2H. Signals that were wrong: Volume, HR L30, HR L10. Projection model targeted 13.5 pts — actual 18 was 4.5 pts off (correct direction). Loss classification: SHOOTING_VARIANCE. Note: Volume and opportunity signals were correct but shooting efficiency diverged. Normal variance — per-minute output was on track.</t>
+        </is>
+      </c>
+      <c r="I17" s="3" t="inlineStr">
+        <is>
+          <t>SHOOTING_VARIANCE</t>
+        </is>
+      </c>
+      <c r="J17" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-13 14:18</t>
+        </is>
+      </c>
     </row>
     <row r="18">
-      <c r="A18" t="inlineStr">
+      <c r="A18" s="3" t="inlineStr">
         <is>
           <t>LaMelo Ball</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
+      <c r="B18" s="3" t="inlineStr">
         <is>
           <t>CHA @ NYK</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr">
+      <c r="C18" s="3" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D18" t="n">
+      <c r="D18" s="3" t="n">
         <v>22.5</v>
       </c>
+      <c r="E18" s="3" t="n">
+        <v>19</v>
+      </c>
+      <c r="F18" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G18" s="3" t="n">
+        <v>-3.5</v>
+      </c>
+      <c r="H18" s="3" t="inlineStr">
+        <is>
+          <t>LOSS — Ball scored 19 pts vs 22.5 line (-3.5), OVER missed by 3.5 pts. Minutes were as expected: 29 played vs L10 avg 30.6. Shooting efficiency was cold: 36.8% FG (-5.3% vs L10 avg of 42.1%). 7/19 from the field. Counter-signals that proved correct: Volume, HR L30, HR L10, Context. Signals that were wrong: Trend, H2H, FG Trend. Projection model targeted 23.0 pts — actual 19 was 4.0 pts off (correct direction). Loss classification: SHOOTING_VARIANCE. Note: Volume and opportunity signals were correct but shooting efficiency diverged. Normal variance — per-minute output was on track.</t>
+        </is>
+      </c>
+      <c r="I18" s="3" t="inlineStr">
+        <is>
+          <t>SHOOTING_VARIANCE</t>
+        </is>
+      </c>
+      <c r="J18" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-13 14:18</t>
+        </is>
+      </c>
     </row>
     <row r="19">
-      <c r="A19" t="inlineStr">
+      <c r="A19" s="5" t="inlineStr">
         <is>
           <t>Miles Bridges</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
+      <c r="B19" s="5" t="inlineStr">
         <is>
           <t>CHA @ NYK</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr">
+      <c r="C19" s="5" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D19" t="n">
+      <c r="D19" s="5" t="n">
         <v>14.5</v>
       </c>
+      <c r="E19" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="F19" s="5" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G19" s="5" t="n">
+        <v>-7.5</v>
+      </c>
+      <c r="H19" s="5" t="inlineStr">
+        <is>
+          <t>WIN — Bridges scored 7 pts vs 14.5 line (-7.5), UNDER hit by 7.5 pts. Bridges played 24 min (-3.8 vs L10 avg of 28.0) — 14% less than expected. Shooting efficiency was cold: 37.5% FG (-16.8% vs L10 avg of 54.3%). 3/8 from the field. Signals that called it correctly: HR L30, Context, Defense, H2H, Pace (6/10 aligned). Counter-signals that were wrong: Volume, HR L10, Trend. Projection model targeted 11.5 pts — actual 7 was 4.5 pts off (correct direction). Result classification: MODEL_CORRECT. Note: Result confirms Bridges's consistency near this line level.</t>
+        </is>
+      </c>
+      <c r="I19" s="5" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J19" s="5" t="inlineStr">
+        <is>
+          <t>2026-04-13 14:18</t>
+        </is>
+      </c>
     </row>
     <row r="20">
-      <c r="A20" t="inlineStr">
+      <c r="A20" s="5" t="inlineStr">
         <is>
           <t>Kon Knueppel</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
+      <c r="B20" s="5" t="inlineStr">
         <is>
           <t>CHA @ NYK</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr">
+      <c r="C20" s="5" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D20" t="n">
+      <c r="D20" s="5" t="n">
         <v>17.5</v>
       </c>
+      <c r="E20" s="5" t="n">
+        <v>14</v>
+      </c>
+      <c r="F20" s="5" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G20" s="5" t="n">
+        <v>-3.5</v>
+      </c>
+      <c r="H20" s="5" t="inlineStr">
+        <is>
+          <t>WIN — Knueppel scored 14 pts vs 17.5 line (-3.5), UNDER hit by 3.5 pts. Minutes were as expected: 31 played vs L10 avg 30.9. Shooting was in line with averages: 35.7% FG (5/14, L10 avg 40.1%). Signals that called it correctly: HR L10, Trend, Context, Defense, H2H (7/10 aligned). Counter-signals that were wrong: Volume, HR L30, Min Trend. Projection model targeted 12.9 pts — actual 14 was 1.1 pts close (correct direction). Result classification: MODEL_CORRECT. Note: Projection model accuracy within 2 pts — GBR features are well-calibrated for Knueppel in this role.</t>
+        </is>
+      </c>
+      <c r="I20" s="5" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J20" s="5" t="inlineStr">
+        <is>
+          <t>2026-04-13 14:18</t>
+        </is>
+      </c>
     </row>
     <row r="21">
-      <c r="A21" t="inlineStr">
+      <c r="A21" s="5" t="inlineStr">
         <is>
           <t>Brandon Miller</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
+      <c r="B21" s="5" t="inlineStr">
         <is>
           <t>CHA @ NYK</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr">
+      <c r="C21" s="5" t="inlineStr">
         <is>
           <t>LEAN UNDER</t>
         </is>
       </c>
-      <c r="D21" t="n">
+      <c r="D21" s="5" t="n">
         <v>19.5</v>
       </c>
+      <c r="E21" s="5" t="n">
+        <v>19</v>
+      </c>
+      <c r="F21" s="5" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G21" s="5" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="H21" s="5" t="inlineStr">
+        <is>
+          <t>WIN — Miller scored 19 pts vs 19.5 line (-0.5), UNDER hit by 0.5 pts. Miller played 27 min (-4.1 vs L10 avg of 31.4) — 13% less than expected. Shooting was in line with averages: 41.7% FG (5/12, L10 avg 44.9%). Signals that called it correctly: Trend, Context, Defense, Pace, FG Trend (5/10 aligned). Counter-signals that were wrong: Volume, HR L30, HR L10. Projection model targeted 19.6 pts — actual 19 was 0.6 pts close (wrong direction). Result classification: CLOSE_CALL. Note: Projection model accuracy within 2 pts — GBR features are well-calibrated for Miller in this role.</t>
+        </is>
+      </c>
+      <c r="I21" s="5" t="inlineStr">
+        <is>
+          <t>CLOSE_CALL</t>
+        </is>
+      </c>
+      <c r="J21" s="5" t="inlineStr">
+        <is>
+          <t>2026-04-13 14:18</t>
+        </is>
+      </c>
     </row>
     <row r="22">
-      <c r="A22" t="inlineStr">
+      <c r="A22" s="4" t="inlineStr">
         <is>
           <t>Jarace Walker</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
+      <c r="B22" s="4" t="inlineStr">
         <is>
           <t>DET @ IND</t>
         </is>
       </c>
-      <c r="C22" t="inlineStr">
+      <c r="C22" s="4" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D22" t="n">
+      <c r="D22" s="4" t="n">
         <v>19.5</v>
       </c>
+      <c r="E22" s="4" t="n"/>
+      <c r="F22" s="4" t="inlineStr">
+        <is>
+          <t>DNP</t>
+        </is>
+      </c>
+      <c r="G22" s="4" t="n"/>
+      <c r="H22" s="4" t="inlineStr"/>
+      <c r="I22" s="4" t="n"/>
+      <c r="J22" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-13 14:18</t>
+        </is>
+      </c>
     </row>
     <row r="23">
-      <c r="A23" t="inlineStr">
+      <c r="A23" s="3" t="inlineStr">
         <is>
           <t>Quenton Jackson</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
+      <c r="B23" s="3" t="inlineStr">
         <is>
           <t>DET @ IND</t>
         </is>
       </c>
-      <c r="C23" t="inlineStr">
+      <c r="C23" s="3" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D23" t="n">
+      <c r="D23" s="3" t="n">
         <v>14.5</v>
       </c>
+      <c r="E23" s="3" t="n">
+        <v>21</v>
+      </c>
+      <c r="F23" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G23" s="3" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="H23" s="3" t="inlineStr">
+        <is>
+          <t>LOSS — Jackson scored 21 pts vs 14.5 line (+6.5), UNDER missed by 6.5 pts. Jackson played 30 min (+9.1 vs L10 avg of 20.6) — 44% more than expected. Shooting was in line with averages: 46.7% FG (7/15, L10 avg 45.8%). Counter-signals that proved correct: Trend, H2H, Min Trend. Signals that were wrong: Volume, HR L30, HR L10. Projection model targeted 10.3 pts — actual 21 was 10.7 pts off (correct direction). Loss classification: SHOOTING_VARIANCE. Note: Volume and opportunity signals were correct but shooting efficiency diverged. Normal variance — per-minute output was on track.</t>
+        </is>
+      </c>
+      <c r="I23" s="3" t="inlineStr">
+        <is>
+          <t>SHOOTING_VARIANCE</t>
+        </is>
+      </c>
+      <c r="J23" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-13 14:18</t>
+        </is>
+      </c>
     </row>
     <row r="24">
-      <c r="A24" t="inlineStr">
+      <c r="A24" s="5" t="inlineStr">
         <is>
           <t>Ausar Thompson</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
+      <c r="B24" s="5" t="inlineStr">
         <is>
           <t>DET @ IND</t>
         </is>
       </c>
-      <c r="C24" t="inlineStr">
+      <c r="C24" s="5" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D24" t="n">
+      <c r="D24" s="5" t="n">
         <v>9.5</v>
       </c>
+      <c r="E24" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="F24" s="5" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G24" s="5" t="n">
+        <v>-2.5</v>
+      </c>
+      <c r="H24" s="5" t="inlineStr">
+        <is>
+          <t>WIN — Thompson scored 7 pts vs 9.5 line (-2.5), UNDER hit by 2.5 pts. Thompson played 22 min (-6.1 vs L10 avg of 27.8) — 22% less than expected. Shooting efficiency was hot: 75.0% FG (+10.2% vs L10 avg of 64.8%). 3/4 from the field. Signals that called it correctly: Volume, HR L30, Context, H2H (4/10 aligned). Counter-signals that were wrong: HR L10, Trend, Defense. Projection model targeted 6.7 pts — actual 7 was 0.3 pts close (correct direction). Result classification: MODEL_CORRECT. Note: Projection model accuracy within 2 pts — GBR features are well-calibrated for Thompson in this role.</t>
+        </is>
+      </c>
+      <c r="I24" s="5" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J24" s="5" t="inlineStr">
+        <is>
+          <t>2026-04-13 14:18</t>
+        </is>
+      </c>
     </row>
     <row r="25">
-      <c r="A25" t="inlineStr">
+      <c r="A25" s="3" t="inlineStr">
         <is>
           <t>Micah Potter</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
+      <c r="B25" s="3" t="inlineStr">
         <is>
           <t>DET @ IND</t>
         </is>
       </c>
-      <c r="C25" t="inlineStr">
+      <c r="C25" s="3" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D25" t="n">
+      <c r="D25" s="3" t="n">
         <v>13.5</v>
       </c>
+      <c r="E25" s="3" t="n">
+        <v>15</v>
+      </c>
+      <c r="F25" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G25" s="3" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="H25" s="3" t="inlineStr">
+        <is>
+          <t>LOSS — Potter scored 15 pts vs 13.5 line (+1.5), UNDER missed by 1.5 pts. Potter played 34 min (+14.1 vs L10 avg of 20.2) — 70% more than expected. Shooting efficiency was cold: 46.2% FG (-13.3% vs L10 avg of 59.5%). 6/13 from the field. Counter-signals that proved correct: Trend, H2H, FG Trend, Min Trend. Signals that were wrong: Volume, HR L30, HR L10. Projection model targeted 3.1 pts — actual 15 was 11.9 pts off (correct direction). Loss classification: SHOOTING_VARIANCE. Note: Volume and opportunity signals were correct but shooting efficiency diverged. Normal variance — per-minute output was on track.</t>
+        </is>
+      </c>
+      <c r="I25" s="3" t="inlineStr">
+        <is>
+          <t>SHOOTING_VARIANCE</t>
+        </is>
+      </c>
+      <c r="J25" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-13 14:18</t>
+        </is>
+      </c>
     </row>
     <row r="26">
-      <c r="A26" t="inlineStr">
+      <c r="A26" s="5" t="inlineStr">
         <is>
           <t>Tyrese Maxey</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
+      <c r="B26" s="5" t="inlineStr">
         <is>
           <t>MIL @ PHI</t>
         </is>
       </c>
-      <c r="C26" t="inlineStr">
+      <c r="C26" s="5" t="inlineStr">
         <is>
           <t>LEAN UNDER</t>
         </is>
       </c>
-      <c r="D26" t="n">
+      <c r="D26" s="5" t="n">
         <v>28.5</v>
       </c>
+      <c r="E26" s="5" t="n">
+        <v>21</v>
+      </c>
+      <c r="F26" s="5" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G26" s="5" t="n">
+        <v>-7.5</v>
+      </c>
+      <c r="H26" s="5" t="inlineStr">
+        <is>
+          <t>WIN — Maxey scored 21 pts vs 28.5 line (-7.5), UNDER hit by 7.5 pts. Maxey played 27 min (-10.6 vs L10 avg of 37.6) — 28% less than expected. Shooting efficiency was hot: 61.5% FG (+15.1% vs L10 avg of 46.4%). 8/13 from the field. Signals that called it correctly: Volume, HR L30, HR L10, Trend, Context (5/10 aligned). Counter-signals that were wrong: Defense, H2H, Pace. Projection model targeted 28.6 pts — actual 21 was 7.6 pts off (wrong direction). Result classification: MODEL_CORRECT. Note: Result confirms Maxey's consistency near this line level.</t>
+        </is>
+      </c>
+      <c r="I26" s="5" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J26" s="5" t="inlineStr">
+        <is>
+          <t>2026-04-13 14:18</t>
+        </is>
+      </c>
     </row>
     <row r="27">
-      <c r="A27" t="inlineStr">
+      <c r="A27" s="5" t="inlineStr">
         <is>
           <t>AJ Green</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr">
+      <c r="B27" s="5" t="inlineStr">
         <is>
           <t>MIL @ PHI</t>
         </is>
       </c>
-      <c r="C27" t="inlineStr">
+      <c r="C27" s="5" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D27" t="n">
+      <c r="D27" s="5" t="n">
         <v>19.5</v>
       </c>
+      <c r="E27" s="5" t="n">
+        <v>19</v>
+      </c>
+      <c r="F27" s="5" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G27" s="5" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="H27" s="5" t="inlineStr">
+        <is>
+          <t>WIN — Green scored 19 pts vs 19.5 line (-0.5), UNDER hit by 0.5 pts. Green played 36 min (+3.3 vs L10 avg of 33.0) — 10% more than expected. Shooting was in line with averages: 43.8% FG (7/16, L10 avg 42.7%). Signals that called it correctly: Volume, HR L30, HR L10, Context, H2H (6/10 aligned). Counter-signals that were wrong: Trend, Defense, FG Trend. Projection model targeted 9.5 pts — actual 19 was 9.5 pts off (correct direction). Result classification: CLOSE_CALL. Note: Result confirms Green's consistency near this line level.</t>
+        </is>
+      </c>
+      <c r="I27" s="5" t="inlineStr">
+        <is>
+          <t>CLOSE_CALL</t>
+        </is>
+      </c>
+      <c r="J27" s="5" t="inlineStr">
+        <is>
+          <t>2026-04-13 14:18</t>
+        </is>
+      </c>
     </row>
     <row r="28">
-      <c r="A28" t="inlineStr">
+      <c r="A28" s="3" t="inlineStr">
         <is>
           <t>Paul George</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr">
+      <c r="B28" s="3" t="inlineStr">
         <is>
           <t>MIL @ PHI</t>
         </is>
       </c>
-      <c r="C28" t="inlineStr">
+      <c r="C28" s="3" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D28" t="n">
+      <c r="D28" s="3" t="n">
         <v>19.5</v>
       </c>
+      <c r="E28" s="3" t="n">
+        <v>11</v>
+      </c>
+      <c r="F28" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G28" s="3" t="n">
+        <v>-8.5</v>
+      </c>
+      <c r="H28" s="3" t="inlineStr">
+        <is>
+          <t>LOSS — George scored 11 pts vs 19.5 line (-8.5), OVER missed by 8.5 pts. George played 21 min (-11.3 vs L10 avg of 32.6) — 35% less than expected. Shooting efficiency was hot: 57.1% FG (+12.4% vs L10 avg of 44.7%). 4/7 from the field. Counter-signals that proved correct: Volume, HR L30, Trend, Context. Signals that were wrong: HR L10, Defense, H2H. Projection model targeted 20.2 pts — actual 11 was 9.2 pts off (correct direction). Loss classification: MINUTES_SHORTFALL. Note: Minutes were the deciding factor, not scoring rate. Flag George for minutes risk in future props if role uncertainty exists.</t>
+        </is>
+      </c>
+      <c r="I28" s="3" t="inlineStr">
+        <is>
+          <t>MINUTES_SHORTFALL</t>
+        </is>
+      </c>
+      <c r="J28" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-13 14:18</t>
+        </is>
+      </c>
     </row>
     <row r="29">
-      <c r="A29" t="inlineStr">
+      <c r="A29" s="5" t="inlineStr">
         <is>
           <t>VJ Edgecombe</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr">
+      <c r="B29" s="5" t="inlineStr">
         <is>
           <t>MIL @ PHI</t>
         </is>
       </c>
-      <c r="C29" t="inlineStr">
+      <c r="C29" s="5" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D29" t="n">
+      <c r="D29" s="5" t="n">
         <v>18.5</v>
       </c>
+      <c r="E29" s="5" t="n">
+        <v>9</v>
+      </c>
+      <c r="F29" s="5" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G29" s="5" t="n">
+        <v>-9.5</v>
+      </c>
+      <c r="H29" s="5" t="inlineStr">
+        <is>
+          <t>WIN — Edgecombe scored 9 pts vs 18.5 line (-9.5), UNDER hit by 9.5 pts. Edgecombe played 31 min (-4.3 vs L10 avg of 35.5) — 12% less than expected. Shooting efficiency was cold: 36.4% FG (-15.3% vs L10 avg of 51.7%). 4/11 from the field. Signals that called it correctly: Volume, Trend, Context, H2H (4/10 aligned). Counter-signals that were wrong: HR L30, HR L10, Defense. Projection model targeted 12.8 pts — actual 9 was 3.8 pts off (correct direction). Result classification: MODEL_CORRECT. Note: Result confirms Edgecombe's consistency near this line level.</t>
+        </is>
+      </c>
+      <c r="I29" s="5" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J29" s="5" t="inlineStr">
+        <is>
+          <t>2026-04-13 14:18</t>
+        </is>
+      </c>
     </row>
     <row r="30">
-      <c r="A30" t="inlineStr">
+      <c r="A30" s="5" t="inlineStr">
         <is>
           <t>Nikola Jokić</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr">
+      <c r="B30" s="5" t="inlineStr">
         <is>
           <t>DEN @ SAS</t>
         </is>
       </c>
-      <c r="C30" t="inlineStr">
+      <c r="C30" s="5" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D30" t="n">
+      <c r="D30" s="5" t="n">
         <v>16.5</v>
       </c>
+      <c r="E30" s="5" t="n">
+        <v>23</v>
+      </c>
+      <c r="F30" s="5" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G30" s="5" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="H30" s="5" t="inlineStr">
+        <is>
+          <t>WIN — Jokić scored 23 pts vs 16.5 line (+6.5), OVER hit by 6.5 pts. Jokić played 18 min (-18.9 vs L10 avg of 37.1) — 51% less than expected. Shooting was in line with averages: 58.3% FG (7/12, L10 avg 56.2%). Signals that called it correctly: Volume, HR L30, HR L10, Context, Defense (9/10 aligned). Counter-signals that were wrong: Trend. Projection model targeted 27.1 pts — actual 23 was 4.1 pts off (correct direction). Result classification: MODEL_CORRECT. Note: Strong signal alignment (9/10) with confirmed result — this player/matchup pattern is reliable for future predictions.</t>
+        </is>
+      </c>
+      <c r="I30" s="5" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J30" s="5" t="inlineStr">
+        <is>
+          <t>2026-04-13 14:18</t>
+        </is>
+      </c>
     </row>
     <row r="31">
-      <c r="A31" t="inlineStr">
+      <c r="A31" s="3" t="inlineStr">
         <is>
           <t>Bruce Brown</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr">
+      <c r="B31" s="3" t="inlineStr">
         <is>
           <t>DEN @ SAS</t>
         </is>
       </c>
-      <c r="C31" t="inlineStr">
+      <c r="C31" s="3" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D31" t="n">
+      <c r="D31" s="3" t="n">
         <v>8.5</v>
       </c>
+      <c r="E31" s="3" t="n">
+        <v>14</v>
+      </c>
+      <c r="F31" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G31" s="3" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="H31" s="3" t="inlineStr">
+        <is>
+          <t>LOSS — Brown scored 14 pts vs 8.5 line (+5.5), UNDER missed by 5.5 pts. Brown played 28 min (+5.9 vs L10 avg of 22.3) — 26% more than expected. Shooting efficiency was hot: 87.5% FG (+38.0% vs L10 avg of 49.5%). 7/8 from the field. Counter-signals that proved correct: HR L10, Trend, Pace, FG Trend. Signals that were wrong: Volume, HR L30, Context. Projection model targeted 7.8 pts — actual 14 was 6.2 pts off (correct direction). Loss classification: SHOOTING_VARIANCE. Note: Volume and opportunity signals were correct but shooting efficiency diverged. Normal variance — per-minute output was on track.</t>
+        </is>
+      </c>
+      <c r="I31" s="3" t="inlineStr">
+        <is>
+          <t>SHOOTING_VARIANCE</t>
+        </is>
+      </c>
+      <c r="J31" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-13 14:18</t>
+        </is>
+      </c>
     </row>
     <row r="32">
-      <c r="A32" t="inlineStr">
+      <c r="A32" s="3" t="inlineStr">
         <is>
           <t>Julian Strawther</t>
         </is>
       </c>
-      <c r="B32" t="inlineStr">
+      <c r="B32" s="3" t="inlineStr">
         <is>
           <t>DEN @ SAS</t>
         </is>
       </c>
-      <c r="C32" t="inlineStr">
+      <c r="C32" s="3" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D32" t="n">
+      <c r="D32" s="3" t="n">
         <v>15.5</v>
       </c>
+      <c r="E32" s="3" t="n">
+        <v>25</v>
+      </c>
+      <c r="F32" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G32" s="3" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="H32" s="3" t="inlineStr">
+        <is>
+          <t>LOSS — Strawther scored 25 pts vs 15.5 line (+9.5), UNDER missed by 9.5 pts. Strawther played 34 min (+20.9 vs L10 avg of 13.5) — 155% more than expected. Shooting efficiency was hot: 47.4% FG (+8.8% vs L10 avg of 38.6%). 9/19 from the field. Counter-signals that proved correct: Trend, Pace. Signals that were wrong: Volume, HR L30, HR L10. Projection model targeted 8.5 pts — actual 25 was 16.5 pts off (correct direction). Loss classification: SHOOTING_VARIANCE. Note: Volume and opportunity signals were correct but shooting efficiency diverged. Normal variance — per-minute output was on track.</t>
+        </is>
+      </c>
+      <c r="I32" s="3" t="inlineStr">
+        <is>
+          <t>SHOOTING_VARIANCE</t>
+        </is>
+      </c>
+      <c r="J32" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-13 14:18</t>
+        </is>
+      </c>
     </row>
     <row r="33">
-      <c r="A33" t="inlineStr">
+      <c r="A33" s="4" t="inlineStr">
         <is>
           <t>Kawhi Leonard</t>
         </is>
       </c>
-      <c r="B33" t="inlineStr">
+      <c r="B33" s="4" t="inlineStr">
         <is>
           <t>GSW @ LAC</t>
         </is>
       </c>
-      <c r="C33" t="inlineStr">
+      <c r="C33" s="4" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D33" t="n">
+      <c r="D33" s="4" t="n">
         <v>28.5</v>
       </c>
+      <c r="E33" s="4" t="n"/>
+      <c r="F33" s="4" t="inlineStr">
+        <is>
+          <t>DNP</t>
+        </is>
+      </c>
+      <c r="G33" s="4" t="n"/>
+      <c r="H33" s="4" t="inlineStr"/>
+      <c r="I33" s="4" t="n"/>
+      <c r="J33" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-13 14:18</t>
+        </is>
+      </c>
     </row>
     <row r="34">
-      <c r="A34" t="inlineStr">
+      <c r="A34" s="5" t="inlineStr">
         <is>
           <t>Darius Garland</t>
         </is>
       </c>
-      <c r="B34" t="inlineStr">
+      <c r="B34" s="5" t="inlineStr">
         <is>
           <t>GSW @ LAC</t>
         </is>
       </c>
-      <c r="C34" t="inlineStr">
+      <c r="C34" s="5" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D34" t="n">
+      <c r="D34" s="5" t="n">
         <v>20.5</v>
       </c>
+      <c r="E34" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="F34" s="5" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G34" s="5" t="n">
+        <v>-5.5</v>
+      </c>
+      <c r="H34" s="5" t="inlineStr">
+        <is>
+          <t>WIN — Garland scored 15 pts vs 20.5 line (-5.5), UNDER hit by 5.5 pts. Garland played 27 min (-4.2 vs L10 avg of 30.8) — 14% less than expected. Shooting efficiency was cold: 35.3% FG (-14.7% vs L10 avg of 50.0%). 6/17 from the field. Signals that called it correctly: Volume, HR L30, HR L10, Trend, Context (6/10 aligned). Counter-signals that were wrong: Defense, Pace, FG Trend. Projection model targeted 16.8 pts — actual 15 was 1.8 pts close (correct direction). Result classification: MODEL_CORRECT. Note: Projection model accuracy within 2 pts — GBR features are well-calibrated for Garland in this role.</t>
+        </is>
+      </c>
+      <c r="I34" s="5" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J34" s="5" t="inlineStr">
+        <is>
+          <t>2026-04-13 14:18</t>
+        </is>
+      </c>
     </row>
     <row r="35">
-      <c r="A35" t="inlineStr">
+      <c r="A35" s="5" t="inlineStr">
         <is>
           <t>Brice Sensabaugh</t>
         </is>
       </c>
-      <c r="B35" t="inlineStr">
+      <c r="B35" s="5" t="inlineStr">
         <is>
           <t>UTA @ LAL</t>
         </is>
       </c>
-      <c r="C35" t="inlineStr">
+      <c r="C35" s="5" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D35" t="n">
+      <c r="D35" s="5" t="n">
         <v>22.5</v>
       </c>
+      <c r="E35" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="F35" s="5" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G35" s="5" t="n">
+        <v>-7.5</v>
+      </c>
+      <c r="H35" s="5" t="inlineStr">
+        <is>
+          <t>WIN — Sensabaugh scored 15 pts vs 22.5 line (-7.5), UNDER hit by 7.5 pts. Sensabaugh played 13 min (-17.9 vs L10 avg of 31.1) — 58% less than expected. Shooting efficiency was cold: 40.0% FG (-10.6% vs L10 avg of 50.6%). 4/10 from the field. Signals that called it correctly: Volume, HR L30, Context, H2H, Pace (5/10 aligned). Counter-signals that were wrong: HR L10, Trend, Defense. Projection model targeted 9.8 pts — actual 15 was 5.2 pts off (correct direction). Result classification: MODEL_CORRECT. Note: Result confirms Sensabaugh's consistency near this line level.</t>
+        </is>
+      </c>
+      <c r="I35" s="5" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J35" s="5" t="inlineStr">
+        <is>
+          <t>2026-04-13 14:18</t>
+        </is>
+      </c>
     </row>
     <row r="36">
-      <c r="A36" t="inlineStr">
+      <c r="A36" s="5" t="inlineStr">
         <is>
           <t>Ace Bailey</t>
         </is>
       </c>
-      <c r="B36" t="inlineStr">
+      <c r="B36" s="5" t="inlineStr">
         <is>
           <t>UTA @ LAL</t>
         </is>
       </c>
-      <c r="C36" t="inlineStr">
+      <c r="C36" s="5" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D36" t="n">
+      <c r="D36" s="5" t="n">
         <v>20.5</v>
       </c>
+      <c r="E36" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="F36" s="5" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G36" s="5" t="n">
+        <v>-5.5</v>
+      </c>
+      <c r="H36" s="5" t="inlineStr">
+        <is>
+          <t>WIN — Bailey scored 15 pts vs 20.5 line (-5.5), UNDER hit by 5.5 pts. Minutes were as expected: 29 played vs L10 avg 32.2. Shooting efficiency was cold: 33.3% FG (-10.6% vs L10 avg of 43.9%). 7/21 from the field. Signals that called it correctly: Volume, HR L30, HR L10, Context, H2H (7/10 aligned). Counter-signals that were wrong: Trend, Defense, Min Trend. Projection model targeted 17.5 pts — actual 15 was 2.5 pts off (correct direction). Result classification: MODEL_CORRECT. Note: Result confirms Bailey's consistency near this line level.</t>
+        </is>
+      </c>
+      <c r="I36" s="5" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J36" s="5" t="inlineStr">
+        <is>
+          <t>2026-04-13 14:18</t>
+        </is>
+      </c>
     </row>
     <row r="37">
-      <c r="A37" t="inlineStr">
+      <c r="A37" s="5" t="inlineStr">
         <is>
           <t>Jake LaRavia</t>
         </is>
       </c>
-      <c r="B37" t="inlineStr">
+      <c r="B37" s="5" t="inlineStr">
         <is>
           <t>UTA @ LAL</t>
         </is>
       </c>
-      <c r="C37" t="inlineStr">
+      <c r="C37" s="5" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D37" t="n">
+      <c r="D37" s="5" t="n">
         <v>12.5</v>
       </c>
+      <c r="E37" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="F37" s="5" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G37" s="5" t="n">
+        <v>-10.5</v>
+      </c>
+      <c r="H37" s="5" t="inlineStr">
+        <is>
+          <t>WIN — LaRavia scored 2 pts vs 12.5 line (-10.5), UNDER hit by 10.5 pts. LaRavia played 25 min (-4.3 vs L10 avg of 29.1) — 15% less than expected. Shooting efficiency was cold: 33.3% FG (-26.6% vs L10 avg of 59.9%). 1/3 from the field. Signals that called it correctly: Volume, HR L30, HR L10, Context, H2H (5/10 aligned). Counter-signals that were wrong: Trend, Defense, Pace. Projection model targeted 7.0 pts — actual 2 was 5.0 pts off (correct direction). Result classification: MODEL_CORRECT. Note: Result confirms LaRavia's consistency near this line level.</t>
+        </is>
+      </c>
+      <c r="I37" s="5" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J37" s="5" t="inlineStr">
+        <is>
+          <t>2026-04-13 14:18</t>
+        </is>
+      </c>
     </row>
     <row r="38">
-      <c r="A38" t="inlineStr">
+      <c r="A38" s="5" t="inlineStr">
         <is>
           <t>LeBron James</t>
         </is>
       </c>
-      <c r="B38" t="inlineStr">
+      <c r="B38" s="5" t="inlineStr">
         <is>
           <t>UTA @ LAL</t>
         </is>
       </c>
-      <c r="C38" t="inlineStr">
+      <c r="C38" s="5" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D38" t="n">
+      <c r="D38" s="5" t="n">
         <v>26.5</v>
       </c>
+      <c r="E38" s="5" t="n">
+        <v>18</v>
+      </c>
+      <c r="F38" s="5" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G38" s="5" t="n">
+        <v>-8.5</v>
+      </c>
+      <c r="H38" s="5" t="inlineStr">
+        <is>
+          <t>WIN — James scored 18 pts vs 26.5 line (-8.5), UNDER hit by 8.5 pts. James played 17 min (-17.1 vs L10 avg of 33.7) — 51% less than expected. Shooting efficiency was cold: 40.0% FG (-10.2% vs L10 avg of 50.2%). 6/15 from the field. Signals that called it correctly: Volume, HR L30, HR L10, Context, H2H (6/10 aligned). Counter-signals that were wrong: Trend, Defense, Pace. Projection model targeted 18.6 pts — actual 18 was 0.6 pts close (correct direction). Result classification: MODEL_CORRECT. Note: Projection model accuracy within 2 pts — GBR features are well-calibrated for James in this role.</t>
+        </is>
+      </c>
+      <c r="I38" s="5" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J38" s="5" t="inlineStr">
+        <is>
+          <t>2026-04-13 14:18</t>
+        </is>
+      </c>
     </row>
     <row r="39">
-      <c r="A39" t="inlineStr">
+      <c r="A39" s="3" t="inlineStr">
         <is>
           <t>Bronny James</t>
         </is>
       </c>
-      <c r="B39" t="inlineStr">
+      <c r="B39" s="3" t="inlineStr">
         <is>
           <t>UTA @ LAL</t>
         </is>
       </c>
-      <c r="C39" t="inlineStr">
+      <c r="C39" s="3" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D39" t="n">
+      <c r="D39" s="3" t="n">
         <v>10.5</v>
       </c>
+      <c r="E39" s="3" t="n">
+        <v>11</v>
+      </c>
+      <c r="F39" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G39" s="3" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H39" s="3" t="inlineStr">
+        <is>
+          <t>LOSS — James scored 11 pts vs 10.5 line (+0.5), UNDER missed by 0.5 pts. James played 19 min (+5.4 vs L10 avg of 13.5) — 40% more than expected. Shooting efficiency was hot: 57.1% FG (+20.5% vs L10 avg of 36.6%). 4/7 from the field. Counter-signals that proved correct: Trend, Defense, H2H, Pace. Signals that were wrong: Volume, HR L30, HR L10. Projection model targeted 6.4 pts — actual 11 was 4.6 pts off (correct direction). Loss classification: SHOOTING_VARIANCE. Note: Volume and opportunity signals were correct but shooting efficiency diverged. Normal variance — per-minute output was on track.</t>
+        </is>
+      </c>
+      <c r="I39" s="3" t="inlineStr">
+        <is>
+          <t>SHOOTING_VARIANCE</t>
+        </is>
+      </c>
+      <c r="J39" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-13 14:18</t>
+        </is>
+      </c>
     </row>
     <row r="40">
-      <c r="A40" t="inlineStr">
+      <c r="A40" s="3" t="inlineStr">
         <is>
           <t>Luguentz Dort</t>
         </is>
       </c>
-      <c r="B40" t="inlineStr">
+      <c r="B40" s="3" t="inlineStr">
         <is>
           <t>PHX @ OKC</t>
         </is>
       </c>
-      <c r="C40" t="inlineStr">
+      <c r="C40" s="3" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D40" t="n">
+      <c r="D40" s="3" t="n">
         <v>7.5</v>
       </c>
+      <c r="E40" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="F40" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G40" s="3" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="H40" s="3" t="inlineStr">
+        <is>
+          <t>LOSS — Dort scored 6 pts vs 7.5 line (-1.5), OVER missed by 1.5 pts. Minutes were as expected: 20 played vs L10 avg 21.6. Shooting efficiency was cold: 33.3% FG (-11.2% vs L10 avg of 44.5%). 2/6 from the field. Counter-signals that proved correct: HR L30, HR L10, Defense, Pace. Signals that were wrong: Volume, Trend, Context. Projection model targeted 9.5 pts — actual 6 was 3.5 pts off (correct direction). Loss classification: SHOOTING_VARIANCE. Note: Volume and opportunity signals were correct but shooting efficiency diverged. Normal variance — per-minute output was on track.</t>
+        </is>
+      </c>
+      <c r="I40" s="3" t="inlineStr">
+        <is>
+          <t>SHOOTING_VARIANCE</t>
+        </is>
+      </c>
+      <c r="J40" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-13 14:18</t>
+        </is>
+      </c>
     </row>
     <row r="41">
-      <c r="A41" t="inlineStr">
+      <c r="A41" s="3" t="inlineStr">
         <is>
           <t>Nikola Topić</t>
         </is>
       </c>
-      <c r="B41" t="inlineStr">
+      <c r="B41" s="3" t="inlineStr">
         <is>
           <t>PHX @ OKC</t>
         </is>
       </c>
-      <c r="C41" t="inlineStr">
+      <c r="C41" s="3" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D41" t="n">
+      <c r="D41" s="3" t="n">
         <v>14.5</v>
       </c>
+      <c r="E41" s="3" t="n">
+        <v>18</v>
+      </c>
+      <c r="F41" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G41" s="3" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="H41" s="3" t="inlineStr">
+        <is>
+          <t>LOSS — Topić scored 18 pts vs 14.5 line (+3.5), UNDER missed by 3.5 pts. Topić played 39 min (+26.1 vs L10 avg of 13.3) — 196% more than expected. Shooting efficiency was hot: 50.0% FG (+16.7% vs L10 avg of 33.3%). 8/16 from the field. Counter-signals that proved correct: H2H, FG Trend, Min Trend. Signals that were wrong: Volume, HR L30, HR L10. Projection model targeted 3.7 pts — actual 18 was 14.3 pts off (correct direction). Loss classification: SHOOTING_VARIANCE. Note: Volume and opportunity signals were correct but shooting efficiency diverged. Normal variance — per-minute output was on track.</t>
+        </is>
+      </c>
+      <c r="I41" s="3" t="inlineStr">
+        <is>
+          <t>SHOOTING_VARIANCE</t>
+        </is>
+      </c>
+      <c r="J41" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-13 14:18</t>
+        </is>
+      </c>
     </row>
     <row r="42">
-      <c r="A42" t="inlineStr">
+      <c r="A42" s="5" t="inlineStr">
         <is>
           <t>Kenrich Williams</t>
         </is>
       </c>
-      <c r="B42" t="inlineStr">
+      <c r="B42" s="5" t="inlineStr">
         <is>
           <t>PHX @ OKC</t>
         </is>
       </c>
-      <c r="C42" t="inlineStr">
+      <c r="C42" s="5" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D42" t="n">
+      <c r="D42" s="5" t="n">
         <v>15.5</v>
       </c>
+      <c r="E42" s="5" t="n">
+        <v>13</v>
+      </c>
+      <c r="F42" s="5" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G42" s="5" t="n">
+        <v>-2.5</v>
+      </c>
+      <c r="H42" s="5" t="inlineStr">
+        <is>
+          <t>WIN — Williams scored 13 pts vs 15.5 line (-2.5), UNDER hit by 2.5 pts. Williams played 33 min (+21.7 vs L10 avg of 11.2) — 194% more than expected. Shooting efficiency was hot: 41.7% FG (+5.9% vs L10 avg of 35.8%). 5/12 from the field. Signals that called it correctly: Volume, HR L30, HR L10, Trend, Context (10/10 aligned). Projection model targeted 6.2 pts — actual 13 was 6.8 pts off (correct direction). Result classification: MODEL_CORRECT. Note: Strong signal alignment (10/10) with confirmed result — this player/matchup pattern is reliable for future predictions.</t>
+        </is>
+      </c>
+      <c r="I42" s="5" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J42" s="5" t="inlineStr">
+        <is>
+          <t>2026-04-13 14:18</t>
+        </is>
+      </c>
     </row>
     <row r="43">
-      <c r="A43" t="inlineStr">
+      <c r="A43" s="3" t="inlineStr">
         <is>
           <t>Jrue Holiday</t>
         </is>
       </c>
-      <c r="B43" t="inlineStr">
+      <c r="B43" s="3" t="inlineStr">
         <is>
           <t>SAC @ POR</t>
         </is>
       </c>
-      <c r="C43" t="inlineStr">
+      <c r="C43" s="3" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D43" t="n">
+      <c r="D43" s="3" t="n">
         <v>15.5</v>
       </c>
+      <c r="E43" s="3" t="n">
+        <v>23</v>
+      </c>
+      <c r="F43" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G43" s="3" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="H43" s="3" t="inlineStr">
+        <is>
+          <t>LOSS — Holiday scored 23 pts vs 15.5 line (+7.5), UNDER missed by 7.5 pts. Minutes were as expected: 32 played vs L10 avg 31.0. Shooting was in line with averages: 44.4% FG (8/18, L10 avg 42.3%). Counter-signals that proved correct: Volume, HR L30, Trend, Context. Signals that were wrong: HR L10, FG Trend. Projection model targeted 6.3 pts — actual 23 was 16.7 pts off (correct direction). Loss classification: MODEL_FAILURE. Note: Model signals were misleading for this matchup — review Holiday's recent role and usage for pattern shifts.</t>
+        </is>
+      </c>
+      <c r="I43" s="3" t="inlineStr">
+        <is>
+          <t>MODEL_FAILURE</t>
+        </is>
+      </c>
+      <c r="J43" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-13 14:18</t>
+        </is>
+      </c>
     </row>
     <row r="44">
-      <c r="A44" t="inlineStr">
+      <c r="A44" s="5" t="inlineStr">
         <is>
           <t>Deni Avdija</t>
         </is>
       </c>
-      <c r="B44" t="inlineStr">
+      <c r="B44" s="5" t="inlineStr">
         <is>
           <t>SAC @ POR</t>
         </is>
       </c>
-      <c r="C44" t="inlineStr">
+      <c r="C44" s="5" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D44" t="n">
+      <c r="D44" s="5" t="n">
         <v>26.5</v>
       </c>
+      <c r="E44" s="5" t="n">
+        <v>25</v>
+      </c>
+      <c r="F44" s="5" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G44" s="5" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="H44" s="5" t="inlineStr">
+        <is>
+          <t>WIN — Avdija scored 25 pts vs 26.5 line (-1.5), UNDER hit by 1.5 pts. Minutes were as expected: 33 played vs L10 avg 32.8. Shooting was in line with averages: 47.4% FG (9/19, L10 avg 48.3%). Signals that called it correctly: Volume, HR L30, HR L10, Context, H2H (5/10 aligned). Counter-signals that were wrong: Trend, Defense, Pace. Projection model targeted 24.4 pts — actual 25 was 0.6 pts close (correct direction). Result classification: CLOSE_CALL. Note: Projection model accuracy within 2 pts — GBR features are well-calibrated for Avdija in this role.</t>
+        </is>
+      </c>
+      <c r="I44" s="5" t="inlineStr">
+        <is>
+          <t>CLOSE_CALL</t>
+        </is>
+      </c>
+      <c r="J44" s="5" t="inlineStr">
+        <is>
+          <t>2026-04-13 14:18</t>
+        </is>
+      </c>
     </row>
     <row r="45">
-      <c r="A45" t="inlineStr">
+      <c r="A45" s="5" t="inlineStr">
         <is>
           <t>Donovan Clingan</t>
         </is>
       </c>
-      <c r="B45" t="inlineStr">
+      <c r="B45" s="5" t="inlineStr">
         <is>
           <t>SAC @ POR</t>
         </is>
       </c>
-      <c r="C45" t="inlineStr">
+      <c r="C45" s="5" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D45" t="n">
+      <c r="D45" s="5" t="n">
         <v>13.5</v>
       </c>
+      <c r="E45" s="5" t="n">
+        <v>13</v>
+      </c>
+      <c r="F45" s="5" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G45" s="5" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="H45" s="5" t="inlineStr">
+        <is>
+          <t>WIN — Clingan scored 13 pts vs 13.5 line (-0.5), UNDER hit by 0.5 pts. Minutes were as expected: 24 played vs L10 avg 26.4. Shooting efficiency was hot: 60.0% FG (+12.6% vs L10 avg of 47.4%). 6/10 from the field. Signals that called it correctly: HR L10, Trend, Context, H2H, FG Trend (6/10 aligned). Counter-signals that were wrong: Volume, HR L30, Defense. Projection model targeted 11.3 pts — actual 13 was 1.7 pts close (correct direction). Result classification: CLOSE_CALL. Note: Projection model accuracy within 2 pts — GBR features are well-calibrated for Clingan in this role.</t>
+        </is>
+      </c>
+      <c r="I45" s="5" t="inlineStr">
+        <is>
+          <t>CLOSE_CALL</t>
+        </is>
+      </c>
+      <c r="J45" s="5" t="inlineStr">
+        <is>
+          <t>2026-04-13 14:18</t>
+        </is>
+      </c>
     </row>
     <row r="46">
-      <c r="A46" t="inlineStr">
+      <c r="A46" s="3" t="inlineStr">
         <is>
           <t>Toumani Camara</t>
         </is>
       </c>
-      <c r="B46" t="inlineStr">
+      <c r="B46" s="3" t="inlineStr">
         <is>
           <t>SAC @ POR</t>
         </is>
       </c>
-      <c r="C46" t="inlineStr">
+      <c r="C46" s="3" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D46" t="n">
+      <c r="D46" s="3" t="n">
         <v>14.5</v>
       </c>
+      <c r="E46" s="3" t="n">
+        <v>15</v>
+      </c>
+      <c r="F46" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G46" s="3" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H46" s="3" t="inlineStr">
+        <is>
+          <t>LOSS — Camara scored 15 pts vs 14.5 line (+0.5), UNDER missed by 0.5 pts. Minutes were as expected: 34 played vs L10 avg 32.9. Shooting efficiency was cold: 42.9% FG (-9.1% vs L10 avg of 52.0%). 6/14 from the field. Counter-signals that proved correct: HR L10, Trend, Defense, Pace. Signals that were wrong: Volume, HR L30, Context. Projection model targeted 10.6 pts — actual 15 was 4.4 pts off (correct direction). Loss classification: SHOOTING_VARIANCE. Note: Volume and opportunity signals were correct but shooting efficiency diverged. Normal variance — per-minute output was on track.</t>
+        </is>
+      </c>
+      <c r="I46" s="3" t="inlineStr">
+        <is>
+          <t>SHOOTING_VARIANCE</t>
+        </is>
+      </c>
+      <c r="J46" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-13 14:18</t>
+        </is>
+      </c>
     </row>
     <row r="47">
-      <c r="A47" t="inlineStr">
+      <c r="A47" s="5" t="inlineStr">
         <is>
           <t>Devin Carter</t>
         </is>
       </c>
-      <c r="B47" t="inlineStr">
+      <c r="B47" s="5" t="inlineStr">
         <is>
           <t>SAC @ POR</t>
         </is>
       </c>
-      <c r="C47" t="inlineStr">
+      <c r="C47" s="5" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D47" t="n">
+      <c r="D47" s="5" t="n">
         <v>17.5</v>
       </c>
+      <c r="E47" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="F47" s="5" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G47" s="5" t="n">
+        <v>-9.5</v>
+      </c>
+      <c r="H47" s="5" t="inlineStr">
+        <is>
+          <t>WIN — Carter scored 8 pts vs 17.5 line (-9.5), UNDER hit by 9.5 pts. Carter played 34 min (+6.5 vs L10 avg of 27.9) — 23% more than expected. Shooting efficiency was cold: 21.4% FG (-23.3% vs L10 avg of 44.7%). 3/14 from the field. Signals that called it correctly: Volume, HR L30, HR L10, Context, Pace (5/10 aligned). Counter-signals that were wrong: Trend, Defense, H2H. Projection model targeted 2.3 pts — actual 8 was 5.7 pts off (correct direction). Result classification: MODEL_CORRECT. Note: Result confirms Carter's consistency near this line level.</t>
+        </is>
+      </c>
+      <c r="I47" s="5" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J47" s="5" t="inlineStr">
+        <is>
+          <t>2026-04-13 14:18</t>
+        </is>
+      </c>
     </row>
     <row r="48">
-      <c r="A48" t="inlineStr">
+      <c r="A48" s="5" t="inlineStr">
         <is>
           <t>Maxime Raynaud</t>
         </is>
       </c>
-      <c r="B48" t="inlineStr">
+      <c r="B48" s="5" t="inlineStr">
         <is>
           <t>SAC @ POR</t>
         </is>
       </c>
-      <c r="C48" t="inlineStr">
+      <c r="C48" s="5" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D48" t="n">
+      <c r="D48" s="5" t="n">
         <v>17.5</v>
       </c>
+      <c r="E48" s="5" t="n">
+        <v>21</v>
+      </c>
+      <c r="F48" s="5" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G48" s="5" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="H48" s="5" t="inlineStr">
+        <is>
+          <t>WIN — Raynaud scored 21 pts vs 17.5 line (+3.5), OVER hit by 3.5 pts. Raynaud played 37 min (+5.7 vs L10 avg of 31.7) — 18% more than expected. Shooting efficiency was hot: 70.0% FG (+13.8% vs L10 avg of 56.2%). 7/10 from the field. Signals that called it correctly: Trend, Defense, Min Trend (3/10 aligned). Counter-signals that were wrong: Volume, HR L30, HR L10. Projection model targeted 19.4 pts — actual 21 was 1.6 pts close (correct direction). Result classification: MODEL_CORRECT. Note: Projection model accuracy within 2 pts — GBR features are well-calibrated for Raynaud in this role.</t>
+        </is>
+      </c>
+      <c r="I48" s="5" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J48" s="5" t="inlineStr">
+        <is>
+          <t>2026-04-13 14:18</t>
+        </is>
+      </c>
     </row>
     <row r="49">
-      <c r="A49" t="inlineStr">
+      <c r="A49" s="3" t="inlineStr">
         <is>
           <t>Nique Clifford</t>
         </is>
       </c>
-      <c r="B49" t="inlineStr">
+      <c r="B49" s="3" t="inlineStr">
         <is>
           <t>SAC @ POR</t>
         </is>
       </c>
-      <c r="C49" t="inlineStr">
+      <c r="C49" s="3" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D49" t="n">
+      <c r="D49" s="3" t="n">
         <v>17.5</v>
       </c>
+      <c r="E49" s="3" t="n">
+        <v>24</v>
+      </c>
+      <c r="F49" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G49" s="3" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="H49" s="3" t="inlineStr">
+        <is>
+          <t>LOSS — Clifford scored 24 pts vs 17.5 line (+6.5), UNDER missed by 6.5 pts. Clifford played 39 min (+5.5 vs L10 avg of 33.3) — 17% more than expected. Shooting efficiency was hot: 76.9% FG (+34.7% vs L10 avg of 42.2%). 10/13 from the field. Counter-signals that proved correct: Trend, Defense, FG Trend, Min Trend. Signals that were wrong: Volume, HR L30, HR L10. Projection model targeted 9.2 pts — actual 24 was 14.8 pts off (correct direction). Loss classification: SHOOTING_VARIANCE. Note: Volume and opportunity signals were correct but shooting efficiency diverged. Normal variance — per-minute output was on track.</t>
+        </is>
+      </c>
+      <c r="I49" s="3" t="inlineStr">
+        <is>
+          <t>SHOOTING_VARIANCE</t>
+        </is>
+      </c>
+      <c r="J49" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-13 14:18</t>
+        </is>
+      </c>
     </row>
     <row r="50">
-      <c r="A50" t="inlineStr">
+      <c r="A50" s="5" t="inlineStr">
         <is>
           <t>Scoot Henderson</t>
         </is>
       </c>
-      <c r="B50" t="inlineStr">
+      <c r="B50" s="5" t="inlineStr">
         <is>
           <t>SAC @ POR</t>
         </is>
       </c>
-      <c r="C50" t="inlineStr">
+      <c r="C50" s="5" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D50" t="n">
+      <c r="D50" s="5" t="n">
         <v>16.5</v>
+      </c>
+      <c r="E50" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="F50" s="5" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G50" s="5" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="H50" s="5" t="inlineStr">
+        <is>
+          <t>WIN — Henderson scored 15 pts vs 16.5 line (-1.5), UNDER hit by 1.5 pts. Minutes were as expected: 27 played vs L10 avg 27.6. Shooting efficiency was hot: 50.0% FG (+7.8% vs L10 avg of 42.2%). 6/12 from the field. Signals that called it correctly: Volume, HR L30, HR L10, Context, H2H (5/10 aligned). Counter-signals that were wrong: Trend, Defense, Pace. Projection model targeted 8.8 pts — actual 15 was 6.2 pts off (correct direction). Result classification: CLOSE_CALL. Note: Result confirms Henderson's consistency near this line level.</t>
+        </is>
+      </c>
+      <c r="I50" s="5" t="inlineStr">
+        <is>
+          <t>CLOSE_CALL</t>
+        </is>
+      </c>
+      <c r="J50" s="5" t="inlineStr">
+        <is>
+          <t>2026-04-13 14:18</t>
+        </is>
       </c>
     </row>
   </sheetData>
